--- a/test_results/test_lagrangian_od_ov_3b_8envs.xlsx
+++ b/test_results/test_lagrangian_od_ov_3b_8envs.xlsx
@@ -505,17 +505,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (Vec in_1_1 (+ in_1_2 in_1_1) in_1_2 (+ in_2_1 in_2_0) (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_2_2 in_2_1) in_2_1 (+ in_2_2 in_2_1) in_2_2) (Vec in_1_0 (+ in_1_0 in_0_2) in_1_1 (+ in_1_1 in_1_0) (+ in_1_2 in_1_1) (+ in_1_2 in_1_1) in_2_0 (+ in_2_0 in_1_2) in_2_1)) (VecAdd (Vec in_0_1 in_0_1 in_0_2 in_0_1 (+ in_1_0 in_0_2) in_0_2 in_1_1 in_1_1 in_1_2) (Vec in_0_0 in_0_0 in_0_1 in_0_0 (+ in_0_1 in_0_0) in_0_1 in_1_0 in_1_0 in_1_1)))</t>
+          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 0 in_2_1 in_2_2 in_2_2 0 in_2_2 0) (Vec in_1_1 in_1_1 in_1_2 in_2_0 (+ in_2_1 in_2_0) in_2_1 in_2_1 in_2_1 in_2_2)) (VecAdd (Vec 0 in_1_0 0 in_1_1 in_1_2 in_1_2 0 in_2_0 0) (Vec in_1_0 in_0_2 in_1_1 in_1_0 in_1_1 in_1_1 in_2_0 in_1_2 in_2_1))) (VecAdd (Vec in_0_1 in_0_1 in_0_2 in_0_1 (+ in_1_0 in_0_2) in_0_2 in_1_1 in_1_1 in_1_2) (Vec in_0_0 in_0_0 in_0_1 in_0_0 (+ in_0_1 in_0_0) in_0_1 in_1_0 in_1_0 in_1_1)))</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>10006</v>
       </c>
       <c r="F2" t="n">
-        <v>3259</v>
+        <v>761</v>
       </c>
       <c r="G2" t="n">
-        <v>67.43000000000001</v>
+        <v>92.39</v>
       </c>
       <c r="H2" t="n">
         <v>7.19</v>
@@ -530,7 +530,7 @@
         <v>232.81</v>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -547,17 +547,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_2 in_3_3 in_3_4 in_3_4 in_4_1 in_4_2 in_4_3 in_4_4 in_4_4 0 in_4_2 in_4_3 in_4_4 0) (VecAdd (Vec 0 0 0 0 0 0 in_2_1 in_2_2 in_2_3 0 0 in_3_1 in_3_2 in_3_3 0 0 in_4_1 in_4_2 in_4_3 0 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_1_4 in_2_0 in_2_0 in_2_1 in_2_2 in_2_3 in_3_0 in_3_0 in_3_1 in_3_2 in_3_3 in_4_0 in_4_0 in_4_1 in_4_2 in_4_3 in_4_1 in_4_1 in_4_2 in_4_3 in_4_4))) (VecAdd (Vec 0 in_1_0 in_1_1 in_1_2 0 in_1_1 in_1_2 in_1_3 in_1_4 in_1_4 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_2 in_3_3 in_3_4 in_3_4 0 in_4_0 in_4_1 in_4_2 0) (Vec in_1_0 in_0_2 in_0_3 in_0_4 in_1_3 in_1_0 in_1_1 in_1_2 in_1_3 in_1_3 in_2_0 in_2_1 in_2_2 in_2_3 in_2_3 in_3_0 in_3_1 in_3_2 in_3_3 in_3_3 in_4_0 in_3_2 in_3_3 in_3_4 in_4_3))) (VecAdd (Vec in_0_1 in_0_1 in_0_2 in_0_3 in_0_4 in_0_1 (+ in_1_0 in_0_2) (+ in_1_1 in_0_3) (+ in_1_2 in_0_4) in_0_4 in_1_1 (+ in_2_0 in_1_2) (+ in_2_1 in_1_3) (+ in_2_2 in_1_4) in_1_4 in_2_1 (+ in_3_0 in_2_2) (+ in_3_1 in_2_3) (+ in_3_2 in_2_4) in_2_4 in_3_1 in_3_1 in_3_2 in_3_3 in_3_4) (Vec in_0_0 in_0_0 in_0_1 in_0_2 in_0_3 in_0_0 (+ in_0_1 in_0_0) (+ in_0_2 in_0_1) (+ in_0_3 in_0_2) in_0_3 in_1_0 (+ in_1_1 in_1_0) (+ in_1_2 in_1_1) (+ in_1_3 in_1_2) in_1_3 in_2_0 (+ in_2_1 in_2_0) (+ in_2_2 in_2_1) (+ in_2_3 in_2_2) in_2_3 in_3_0 in_3_0 in_3_1 in_3_2 in_3_3)))</t>
+          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_2 in_3_3 in_3_4 in_3_4 in_4_1 in_4_2 in_4_3 in_4_4 in_4_4 0 in_4_2 in_4_3 in_4_4 0) (VecAdd (Vec 0 0 0 0 0 0 in_2_1 in_2_2 in_2_3 0 0 in_3_1 in_3_2 in_3_3 0 0 in_4_1 in_4_2 in_4_3 0 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_1_4 in_2_0 in_2_0 in_2_1 in_2_2 in_2_3 in_3_0 in_3_0 in_3_1 in_3_2 in_3_3 in_4_0 in_4_0 in_4_1 in_4_2 in_4_3 in_4_1 in_4_1 in_4_2 in_4_3 in_4_4))) (VecAdd (Vec 0 in_1_0 in_1_1 in_1_2 0 in_1_1 in_1_2 in_1_3 in_1_4 in_1_4 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_2 in_3_3 in_3_4 in_3_4 0 in_4_0 in_4_1 in_4_2 0) (Vec in_1_0 in_0_2 in_0_3 in_0_4 in_1_3 in_1_0 in_1_1 in_1_2 in_1_3 in_1_3 in_2_0 in_2_1 in_2_2 in_2_3 in_2_3 in_3_0 in_3_1 in_3_2 in_3_3 in_3_3 in_4_0 in_3_2 in_3_3 in_3_4 in_4_3))) (VecAdd (VecAdd (Vec 0 0 0 0 0 0 in_1_0 in_1_1 in_1_2 0 0 in_2_0 in_2_1 in_2_2 0 0 in_3_0 in_3_1 in_3_2 0 0 0 0 0 0) (Vec in_0_1 in_0_1 in_0_2 in_0_3 in_0_4 in_0_1 in_0_2 in_0_3 in_0_4 in_0_4 in_1_1 in_1_2 in_1_3 in_1_4 in_1_4 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_1 in_3_2 in_3_3 in_3_4)) (VecAdd (Vec 0 0 0 0 0 0 in_0_1 in_0_2 in_0_3 0 0 in_1_1 in_1_2 in_1_3 0 0 in_2_1 in_2_2 in_2_3 0 0 0 0 0 0) (Vec in_0_0 in_0_0 in_0_1 in_0_2 in_0_3 in_0_0 in_0_0 in_0_1 in_0_2 in_0_3 in_1_0 in_1_0 in_1_1 in_1_2 in_1_3 in_2_0 in_2_0 in_2_1 in_2_2 in_2_3 in_3_0 in_3_0 in_3_1 in_3_2 in_3_3))))</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>36006</v>
       </c>
       <c r="F3" t="n">
-        <v>4512</v>
+        <v>14</v>
       </c>
       <c r="G3" t="n">
-        <v>87.47</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="H3" t="n">
         <v>7.19</v>
@@ -572,7 +572,7 @@
         <v>232.81</v>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -589,17 +589,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3 v2_4 v2_5 v2_6 v2_7) (VecAdd (Vec 2 2 2 2 2 2 2 2) (Vec (* v1_0 5) (* v1_1 5) (* v1_2 5) (* v1_3 5) (* v1_4 5) (* v1_5 5) (* v1_6 5) (* v1_7 5))))</t>
+          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3 v2_4 v2_5 v2_6 v2_7) (VecAdd (Vec 2 2 2 2 2 2 2 2) (VecMul (Vec v1_0 v1_1 v1_2 v1_3 v1_4 v1_5 v1_6 v1_7) (Vec 5 5 5 5 5 5 5 5))))</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>6006</v>
       </c>
       <c r="F4" t="n">
-        <v>2008</v>
+        <v>108</v>
       </c>
       <c r="G4" t="n">
-        <v>66.56999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="H4" t="n">
         <v>39.37</v>
@@ -614,7 +614,7 @@
         <v>200.63</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -673,32 +673,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( - ( + v1_0 v2_0 ) ( * ( * v1_0 v2_0 ) 2 ) ) ( - ( + v1_1 v2_1 ) ( * 2 ( * v1_1 v2_1 ) ) ) ) ( + ( - ( + v1_2 v2_2 ) ( * 2 ( * v1_2 v2_2 ) ) ) ( - ( + v1_3 v2_3 ) ( * 2 ( * v1_3 v2_3 ) ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2) (Vec v2_0 v2_2)) (VecMul (VecMul (Vec v1_0 2 v2_0 1) (&lt;&lt; (Vec v1_0 2 v2_0 1) 2)) (VecMul (Vec 2 v1_2 1 v2_2) (&lt;&lt; (Vec 2 v1_2 1 v2_2) 2)))) (VecMinus (VecAdd (Vec v1_1 v1_3) (Vec v2_1 v2_3)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_3) (Vec v2_1 v2_3))))) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2) (Vec v2_0 v2_2)) (VecMul (VecMul (Vec v1_0 2 v2_0 1) (&lt;&lt; (Vec v1_0 2 v2_0 1) 2)) (VecMul (Vec 2 v1_2 1 v2_2) (&lt;&lt; (Vec 2 v1_2 1 v2_2) 2)))) (VecMinus (VecAdd (Vec v1_1 v1_3) (Vec v2_1 v2_3)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_3) (Vec v2_1 v2_3))))) 1))</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>4759</v>
       </c>
       <c r="F6" t="n">
-        <v>4759</v>
+        <v>676</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>85.8</v>
       </c>
       <c r="H6" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>75.15000000000001</v>
+        <v>77.55</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>164.85</v>
+        <v>162.45</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -715,17 +715,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (Vec (* v1_0 v2_0) 2) (Vec 2 (* v1_4 v2_4)))) (VecMinus (VecAdd (Vec v1_1 v1_5) (Vec v2_1 v2_5)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_5) (Vec v2_1 v2_5))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_6) (Vec v2_2 v2_6)))) (VecMinus (VecAdd (Vec v1_3 v1_7) (Vec v2_3 v2_7)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_7) (Vec v2_3 v2_7))))) (&lt;&lt; (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (Vec (* v1_0 v2_0) 2) (Vec 2 (* v1_4 v2_4)))) (VecMinus (VecAdd (Vec v1_1 v1_5) (Vec v2_1 v2_5)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_5) (Vec v2_1 v2_5))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_6) (Vec v2_2 v2_6)))) (VecMinus (VecAdd (Vec v1_3 v1_7) (Vec v2_3 v2_7)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_7) (Vec v2_3 v2_7)))))) 1)))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (VecMul (Vec v1_0 2 v2_0 1) (&lt;&lt; (Vec v1_0 2 v2_0 1) 2)) (VecMul (Vec 2 v1_4 1 v2_4) (&lt;&lt; (Vec 2 v1_4 1 v2_4) 2)))) (VecMinus (VecAdd (Vec v1_1 v1_5) (Vec v2_1 v2_5)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_5) (Vec v2_1 v2_5))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_6) (Vec v2_2 v2_6)))) (VecMinus (VecAdd (Vec v1_3 v1_7) (Vec v2_3 v2_7)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_7) (Vec v2_3 v2_7)))))) (&lt;&lt; (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (VecMul (Vec v1_0 2 v2_0 1) (&lt;&lt; (Vec v1_0 2 v2_0 1) 2)) (VecMul (Vec 2 v1_4 1 v2_4) (&lt;&lt; (Vec 2 v1_4 1 v2_4) 2)))) (VecMinus (VecAdd (Vec v1_1 v1_5) (Vec v2_1 v2_5)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_5) (Vec v2_1 v2_5))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_6) (Vec v2_2 v2_6)))) (VecMinus (VecAdd (Vec v1_3 v1_7) (Vec v2_3 v2_7)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_7) (Vec v2_3 v2_7)))))) 1))</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>9760</v>
       </c>
       <c r="F7" t="n">
-        <v>1275</v>
+        <v>1083</v>
       </c>
       <c r="G7" t="n">
-        <v>86.94</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H7" t="n">
         <v>76.34999999999999</v>
@@ -740,7 +740,7 @@
         <v>161.25</v>
       </c>
       <c r="L7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -757,17 +757,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec (* v1_0 v2_0) 2) (Vec 2 (* v1_16 v2_16)))) (VecMinus (VecAdd (Vec v1_1 v1_17) (Vec v2_1 v2_17)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_17) (Vec v2_1 v2_17))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_18) (Vec v2_2 v2_18)))) (VecMinus (VecAdd (Vec v1_3 v1_19) (Vec v2_3 v2_19)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_19) (Vec v2_3 v2_19)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (Vec 2 2) (VecMul (Vec v1_4 v1_20) (Vec v2_4 v2_20)))) (VecMinus (VecAdd (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecMul (Vec 2 2) (VecMul (Vec v1_5 v1_21) (Vec v2_5 v2_21))))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (Vec 2 2) (VecMul (Vec v1_6 v1_22) (Vec v2_6 v2_22)))) (VecMinus (VecAdd (Vec v1_7 v1_23) (Vec v2_7 v2_23)) (VecMul (Vec 2 2) (VecMul (Vec v1_7 v1_23) (Vec v2_7 v2_23))))))) (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (Vec 2 2) (VecMul (Vec v1_8 v1_24) (Vec v2_8 v2_24)))) (VecMinus (VecAdd (Vec v1_9 v1_25) (Vec v2_9 v2_25)) (VecMul (Vec 2 2) (VecMul (Vec v1_9 v1_25) (Vec v2_9 v2_25))))) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (Vec 2 2) (VecMul (Vec v1_10 v1_26) (Vec v2_10 v2_26)))) (VecMinus (VecAdd (Vec v1_11 v1_27) (Vec v2_11 v2_27)) (VecMul (Vec 2 2) (VecMul (Vec v1_11 v1_27) (Vec v2_11 v2_27)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec 2 2) (VecMul (Vec v1_12 v1_28) (Vec v2_12 v2_28)))) (VecMinus (VecAdd (Vec v1_13 v1_29) (Vec v2_13 v2_29)) (VecMul (Vec 2 2) (Vec (* v1_13 v2_13) (* v1_29 v2_29))))) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (Vec (* 2 (* v1_14 v2_14)) (* 2 (* v1_30 v2_30)))) (VecMinus (VecAdd (Vec v1_15 v1_31) (Vec v2_15 v2_31)) (Vec (* 2 (* v1_15 v2_15)) (* 2 (* v1_31 v2_31)))))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec (* v1_0 v2_0) 2) (Vec 2 (* v1_16 v2_16)))) (VecMinus (VecAdd (Vec v1_1 v1_17) (Vec v2_1 v2_17)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_17) (Vec v2_1 v2_17))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_18) (Vec v2_2 v2_18)))) (VecMinus (VecAdd (Vec v1_3 v1_19) (Vec v2_3 v2_19)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_19) (Vec v2_3 v2_19)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (Vec 2 2) (VecMul (Vec v1_4 v1_20) (Vec v2_4 v2_20)))) (VecMinus (VecAdd (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecMul (Vec 2 2) (VecMul (Vec v1_5 v1_21) (Vec v2_5 v2_21))))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (Vec 2 2) (VecMul (Vec v1_6 v1_22) (Vec v2_6 v2_22)))) (VecMinus (VecAdd (Vec v1_7 v1_23) (Vec v2_7 v2_23)) (VecMul (Vec 2 2) (VecMul (Vec v1_7 v1_23) (Vec v2_7 v2_23))))))) (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (Vec 2 2) (VecMul (Vec v1_8 v1_24) (Vec v2_8 v2_24)))) (VecMinus (VecAdd (Vec v1_9 v1_25) (Vec v2_9 v2_25)) (VecMul (Vec 2 2) (VecMul (Vec v1_9 v1_25) (Vec v2_9 v2_25))))) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (Vec 2 2) (VecMul (Vec v1_10 v1_26) (Vec v2_10 v2_26)))) (VecMinus (VecAdd (Vec v1_11 v1_27) (Vec v2_11 v2_27)) (VecMul (Vec 2 2) (VecMul (Vec v1_11 v1_27) (Vec v2_11 v2_27)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec 2 2) (VecMul (Vec v1_12 v1_28) (Vec v2_12 v2_28)))) (VecMinus (VecAdd (Vec v1_13 v1_29) (Vec v2_13 v2_29)) (VecMul (Vec 2 2) (Vec (* v1_13 v2_13) (* v1_29 v2_29))))) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (Vec (* 2 (* v1_14 v2_14)) (* 2 (* v1_30 v2_30)))) (VecMinus (VecAdd (Vec v1_15 v1_31) (Vec v2_15 v2_31)) (Vec (* 2 (* v1_15 v2_15)) (* 2 (* v1_31 v2_31)))))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec (* v1_0 v2_0) 2) (Vec 2 (* v1_16 v2_16)))) (VecMinus (VecAdd (Vec v1_1 v1_17) (Vec v2_1 v2_17)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_17) (Vec v2_1 v2_17))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_18) (Vec v2_2 v2_18)))) (VecMinus (VecAdd (Vec v1_3 v1_19) (Vec v2_3 v2_19)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_19) (Vec v2_3 v2_19)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (Vec 2 2) (VecMul (Vec v1_4 v1_20) (Vec v2_4 v2_20)))) (VecMinus (VecAdd (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecMul (Vec 2 2) (VecMul (Vec v1_5 v1_21) (Vec v2_5 v2_21))))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (Vec 2 2) (VecMul (Vec v1_6 v1_22) (Vec v2_6 v2_22)))) (VecMinus (VecAdd (Vec v1_7 v1_23) (Vec v2_7 v2_23)) (VecMul (Vec 2 2) (VecMul (Vec v1_7 v1_23) (Vec v2_7 v2_23))))))) (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (Vec 2 2) (VecMul (Vec v1_8 v1_24) (Vec v2_8 v2_24)))) (VecMinus (VecAdd (Vec v1_9 v1_25) (Vec v2_9 v2_25)) (VecMul (Vec 2 2) (VecMul (Vec v1_9 v1_25) (Vec v2_9 v2_25))))) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (Vec 2 2) (VecMul (Vec v1_10 v1_26) (Vec v2_10 v2_26)))) (VecMinus (VecAdd (Vec v1_11 v1_27) (Vec v2_11 v2_27)) (VecMul (Vec 2 2) (VecMul (Vec v1_11 v1_27) (Vec v2_11 v2_27)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec 2 2) (VecMul (Vec v1_12 v1_28) (Vec v2_12 v2_28)))) (VecMinus (VecAdd (Vec v1_13 v1_29) (Vec v2_13 v2_29)) (VecMul (Vec 2 2) (VecMul (Vec v1_13 v1_29) (Vec v2_13 v2_29))))) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (VecMul (Vec 2 2) (Vec (* v1_14 v2_14) (* v1_30 v2_30)))) (Vec (- (+ v1_15 v2_15) (* 2 (* v1_15 v2_15))) (- (+ v1_31 v2_31) (* 2 (* v1_31 v2_31)))))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec (* v1_0 v2_0) 2) (Vec 2 (* v1_16 v2_16)))) (VecMinus (VecAdd (Vec v1_1 v1_17) (Vec v2_1 v2_17)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_17) (Vec v2_1 v2_17))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_18) (Vec v2_2 v2_18)))) (VecMinus (VecAdd (Vec v1_3 v1_19) (Vec v2_3 v2_19)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_19) (Vec v2_3 v2_19)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (Vec 2 2) (VecMul (Vec v1_4 v1_20) (Vec v2_4 v2_20)))) (VecMinus (VecAdd (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecMul (Vec 2 2) (VecMul (Vec v1_5 v1_21) (Vec v2_5 v2_21))))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (Vec 2 2) (VecMul (Vec v1_6 v1_22) (Vec v2_6 v2_22)))) (VecMinus (VecAdd (Vec v1_7 v1_23) (Vec v2_7 v2_23)) (VecMul (Vec 2 2) (VecMul (Vec v1_7 v1_23) (Vec v2_7 v2_23))))))) (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (Vec 2 2) (VecMul (Vec v1_8 v1_24) (Vec v2_8 v2_24)))) (VecMinus (VecAdd (Vec v1_9 v1_25) (Vec v2_9 v2_25)) (VecMul (Vec 2 2) (VecMul (Vec v1_9 v1_25) (Vec v2_9 v2_25))))) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (Vec 2 2) (VecMul (Vec v1_10 v1_26) (Vec v2_10 v2_26)))) (VecMinus (VecAdd (Vec v1_11 v1_27) (Vec v2_11 v2_27)) (VecMul (Vec 2 2) (VecMul (Vec v1_11 v1_27) (Vec v2_11 v2_27)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec 2 2) (VecMul (Vec v1_12 v1_28) (Vec v2_12 v2_28)))) (VecMinus (VecAdd (Vec v1_13 v1_29) (Vec v2_13 v2_29)) (VecMul (Vec 2 2) (VecMul (Vec v1_13 v1_29) (Vec v2_13 v2_29))))) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (VecMul (Vec 2 2) (Vec (* v1_14 v2_14) (* v1_30 v2_30)))) (Vec (- (+ v1_15 v2_15) (* 2 (* v1_15 v2_15))) (- (+ v1_31 v2_31) (* 2 (* v1_31 v2_31)))))))) 1))</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>39762</v>
       </c>
       <c r="F8" t="n">
-        <v>5712</v>
+        <v>5910</v>
       </c>
       <c r="G8" t="n">
-        <v>85.63</v>
+        <v>85.14</v>
       </c>
       <c r="H8" t="n">
         <v>78.75</v>
@@ -799,17 +799,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>(VecAdd (Vec c1_0 c1_1 c1_2 c1_3 c1_4 c1_5 c1_6 c1_7) (VecAdd (Vec c2_0 c2_1 c2_2 c2_3 c2_4 c2_5 c2_6 c2_7) (VecMul (Vec c0_0 c0_1 c0_2 c0_3 c0_4 c0_5 c0_6 c0_7) (VecAdd (Vec c3_0 c3_1 c3_2 c3_3 c3_4 c3_5 c3_6 c3_7) (Vec (* c0_0 c4_0) (* c0_1 c4_1) (* c0_2 c4_2) (* c0_3 c4_3) (* c0_4 c4_4) (* c0_5 c4_5) (* c0_6 c4_6) (* c0_7 c4_7))))))</t>
+          <t>(VecAdd (Vec c1_0 c1_1 c1_2 c1_3 c1_4 c1_5 c1_6 c1_7) (VecAdd (Vec c2_0 c2_1 c2_2 c2_3 c2_4 c2_5 c2_6 c2_7) (VecMul (Vec c0_0 c0_1 c0_2 c0_3 c0_4 c0_5 c0_6 c0_7) (VecAdd (Vec c3_0 c3_1 c3_2 c3_3 c3_4 c3_5 c3_6 c3_7) (VecMul (Vec c0_0 c0_1 c0_2 c0_3 c0_4 c0_5 c0_6 c0_7) (Vec c4_0 c4_1 c4_2 c4_3 c4_4 c4_5 c4_6 c4_7))))))</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>10009</v>
       </c>
       <c r="F9" t="n">
-        <v>2112</v>
+        <v>212</v>
       </c>
       <c r="G9" t="n">
-        <v>78.90000000000001</v>
+        <v>97.88</v>
       </c>
       <c r="H9" t="n">
         <v>75.15000000000001</v>
@@ -824,7 +824,7 @@
         <v>164.85</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -883,32 +883,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( + ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ( * ( - c2_3 c1_3 ) ( - c2_3 c1_3 ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2) (Vec c1_0 c1_2)) (VecMinus (Vec c2_0 c2_2) (Vec c1_0 c1_2))) (VecMul (VecMinus (Vec c2_1 c2_3) (Vec c1_1 c1_3)) (VecMinus (Vec c2_1 c2_3) (Vec c1_1 c1_3)))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2) (Vec c1_0 c1_2)) (VecMinus (Vec c2_0 c2_2) (Vec c1_0 c1_2))) (VecMul (VecMinus (Vec c2_1 c2_3) (Vec c1_1 c1_3)) (VecMinus (Vec c2_1 c2_3) (Vec c1_1 c1_3)))) 1))</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>3757</v>
       </c>
       <c r="F11" t="n">
-        <v>3757</v>
+        <v>265</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>92.95</v>
       </c>
       <c r="H11" t="n">
         <v>40.57</v>
       </c>
       <c r="I11" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>199.43</v>
+        <v>198.23</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -925,32 +925,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( + ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ( * ( - c2_3 c1_3 ) ( - c2_3 c1_3 ) ) ) ) ( + ( + ( * ( - c2_4 c1_4 ) ( - c2_4 c1_4 ) ) ( * ( - c2_5 c1_5 ) ( - c2_5 c1_5 ) ) ) ( + ( * ( - c2_6 c1_6 ) ( - c2_6 c1_6 ) ) ( * ( - c2_7 c1_7 ) ( - c2_7 c1_7 ) ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4) (Vec c1_0 c1_4)) (VecMinus (Vec c2_0 c2_4) (Vec c1_0 c1_4))) (VecMul (VecMinus (Vec c2_1 c2_5) (Vec c1_1 c1_5)) (VecMinus (Vec c2_1 c2_5) (Vec c1_1 c1_5)))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6) (Vec c1_2 c1_6)) (VecMinus (Vec c2_2 c2_6) (Vec c1_2 c1_6))) (VecMul (VecMinus (Vec c2_3 c2_7) (Vec c1_3 c1_7)) (VecMinus (Vec c2_3 c2_7) (Vec c1_3 c1_7))))) (&lt;&lt; (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4) (Vec c1_0 c1_4)) (VecMinus (Vec c2_0 c2_4) (Vec c1_0 c1_4))) (VecMul (VecMinus (Vec c2_1 c2_5) (Vec c1_1 c1_5)) (VecMinus (Vec c2_1 c2_5) (Vec c1_1 c1_5)))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6) (Vec c1_2 c1_6)) (VecMinus (Vec c2_2 c2_6) (Vec c1_2 c1_6))) (VecMul (VecMinus (Vec c2_3 c2_7) (Vec c1_3 c1_7)) (VecMinus (Vec c2_3 c2_7) (Vec c1_3 c1_7))))) 1))</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>7758</v>
       </c>
       <c r="F12" t="n">
-        <v>7758</v>
+        <v>472</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>93.92</v>
       </c>
       <c r="H12" t="n">
         <v>41.77</v>
       </c>
       <c r="I12" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>198.23</v>
+        <v>197.03</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -967,14 +967,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16) (Vec c1_0 c1_16)) (VecMinus (Vec c2_0 c2_16) (Vec c1_0 c1_16))) (VecMul (VecMinus (Vec c2_1 c2_17) (Vec c1_1 c1_17)) (VecMinus (Vec c2_1 c2_17) (Vec c1_1 c1_17)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18) (Vec c1_2 c1_18)) (VecMinus (Vec c2_2 c2_18) (Vec c1_2 c1_18))) (VecMul (VecMinus (Vec c2_3 c2_19) (Vec c1_3 c1_19)) (VecMinus (Vec c2_3 c2_19) (Vec c1_3 c1_19)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_20) (Vec c1_4 c1_20)) (VecMinus (Vec c2_4 c2_20) (Vec c1_4 c1_20))) (VecMul (VecMinus (Vec c2_5 c2_21) (Vec c1_5 c1_21)) (VecMinus (Vec c2_5 c2_21) (Vec c1_5 c1_21)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22) (Vec c1_6 c1_22)) (VecMinus (Vec c2_6 c2_22) (Vec c1_6 c1_22))) (VecMul (VecMinus (Vec c2_7 c2_23) (Vec c1_7 c1_23)) (VecMinus (Vec c2_7 c2_23) (Vec c1_7 c1_23)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_8 c2_24) (Vec c1_8 c1_24)) (VecMinus (Vec c2_8 c2_24) (Vec c1_8 c1_24))) (VecMul (VecMinus (Vec c2_9 c2_25) (Vec c1_9 c1_25)) (VecMinus (Vec c2_9 c2_25) (Vec c1_9 c1_25)))) (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26) (Vec c1_10 c1_26)) (VecMinus (Vec c2_10 c2_26) (Vec c1_10 c1_26))) (VecMul (VecMinus (Vec c2_11 c2_27) (Vec c1_11 c1_27)) (VecMinus (Vec c2_11 c2_27) (Vec c1_11 c1_27)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28) (Vec c1_12 c1_28)) (VecMinus (Vec c2_12 c2_28) (Vec c1_12 c1_28))) (VecMul (VecMinus (Vec c2_13 c2_29) (Vec c1_13 c1_29)) (VecMinus (Vec c2_13 c2_29) (Vec c1_13 c1_29)))) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30) (Vec c1_14 c1_30)) (VecMinus (Vec c2_14 c2_30) (Vec c1_14 c1_30))) (VecMul (VecMinus (Vec c2_15 c2_31) (Vec c1_15 c1_31)) (VecMinus (Vec c2_15 c2_31) (Vec c1_15 c1_31)))))) (&lt;&lt; (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16) (Vec c1_0 c1_16)) (VecMinus (Vec c2_0 c2_16) (Vec c1_0 c1_16))) (VecMul (VecMinus (Vec c2_1 c2_17) (Vec c1_1 c1_17)) (VecMinus (Vec c2_1 c2_17) (Vec c1_1 c1_17)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18) (Vec c1_2 c1_18)) (VecMinus (Vec c2_2 c2_18) (Vec c1_2 c1_18))) (VecMul (VecMinus (Vec c2_3 c2_19) (Vec c1_3 c1_19)) (VecMinus (Vec c2_3 c2_19) (Vec c1_3 c1_19)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_20) (Vec c1_4 c1_20)) (VecMinus (Vec c2_4 c2_20) (Vec c1_4 c1_20))) (VecMul (VecMinus (Vec c2_5 c2_21) (Vec c1_5 c1_21)) (VecMinus (Vec c2_5 c2_21) (Vec c1_5 c1_21)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22) (Vec c1_6 c1_22)) (VecMinus (Vec c2_6 c2_22) (Vec c1_6 c1_22))) (VecMul (VecMinus (Vec c2_7 c2_23) (Vec c1_7 c1_23)) (VecMinus (Vec c2_7 c2_23) (Vec c1_7 c1_23)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_8 c2_24) (Vec c1_8 c1_24)) (VecMinus (Vec c2_8 c2_24) (Vec c1_8 c1_24))) (VecMul (VecMinus (Vec c2_9 c2_25) (Vec c1_9 c1_25)) (VecMinus (Vec c2_9 c2_25) (Vec c1_9 c1_25)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26) (Vec c1_10 c1_26)) (VecMinus (Vec c2_10 c2_26) (Vec c1_10 c1_26))) (VecMul (VecMinus (Vec c2_11 c2_27) (Vec c1_11 c1_27)) (VecMinus (Vec c2_11 c2_27) (Vec c1_11 c1_27)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28) (Vec c1_12 c1_28)) (VecMinus (Vec c2_12 c2_28) (Vec c1_12 c1_28))) (VecMul (VecMinus (Vec c2_13 c2_29) (Vec c1_13 c1_29)) (VecMinus (Vec c2_13 c2_29) (Vec c1_13 c1_29)))) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30) (Vec c1_14 c1_30)) (VecMinus (Vec c2_14 c2_30) (Vec c1_14 c1_30))) (VecMul (VecMinus (Vec c2_15 c2_31) (Vec c1_15 c1_31)) (VecMinus (Vec c2_15 c2_31) (Vec c1_15 c1_31))))))))))) 1)))))))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16) (Vec c1_0 c1_16)) (VecMinus (Vec c2_0 c2_16) (Vec c1_0 c1_16))) (VecMul (VecMinus (Vec c2_1 c2_17) (Vec c1_1 c1_17)) (VecMinus (Vec c2_1 c2_17) (Vec c1_1 c1_17)))) (VecMul (VecMinus (Vec c2_2 c2_18) (Vec c1_2 c1_18)) (VecMinus (Vec c2_2 c2_18) (Vec c1_2 c1_18)))) (VecAdd (VecMul (VecMinus (Vec c2_3 c2_19) (Vec c1_3 c1_19)) (VecMinus (Vec c2_3 c2_19) (Vec c1_3 c1_19))) (VecMul (VecMinus (Vec c2_4 c2_20) (Vec c1_4 c1_20)) (VecMinus (Vec c2_4 c2_20) (Vec c1_4 c1_20))))) (VecMul (VecMinus (Vec c2_5 c2_21) (Vec c1_5 c1_21)) (VecMinus (Vec c2_5 c2_21) (Vec c1_5 c1_21)))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22) (Vec c1_6 c1_22)) (VecMinus (Vec c2_6 c2_22) (Vec c1_6 c1_22))) (VecAdd (VecMul (VecMinus (Vec c2_7 c2_23) (Vec c1_7 c1_23)) (VecMinus (Vec c2_7 c2_23) (Vec c1_7 c1_23))) (VecAdd (VecMul (VecMinus (Vec c2_8 c2_24) (Vec c1_8 c1_24)) (VecMinus (Vec c2_8 c2_24) (Vec c1_8 c1_24))) (VecAdd (VecMul (VecMinus (Vec c2_9 c2_25) (Vec c1_9 c1_25)) (VecMinus (Vec c2_9 c2_25) (Vec c1_9 c1_25))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26) (Vec c1_10 c1_26)) (VecMinus (Vec c2_10 c2_26) (Vec c1_10 c1_26))) (VecMul (VecMinus (Vec c2_11 c2_27) (Vec c1_11 c1_27)) (VecMinus (Vec c2_11 c2_27) (Vec c1_11 c1_27)))) (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28) (Vec c1_12 c1_28)) (VecMinus (Vec c2_12 c2_28) (Vec c1_12 c1_28))) (VecMul (VecMinus (Vec c2_13 c2_29) (Vec c1_13 c1_29)) (VecMinus (Vec c2_13 c2_29) (Vec c1_13 c1_29)))) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30) (Vec c1_14 c1_30)) (VecMinus (Vec c2_14 c2_30) (Vec c1_14 c1_30))) (VecMul (VecMinus (Vec c2_15 c2_31) (Vec c1_15 c1_31)) (VecMinus (Vec c2_15 c2_31) (Vec c1_15 c1_31))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16) (Vec c1_0 c1_16)) (VecMinus (Vec c2_0 c2_16) (Vec c1_0 c1_16))) (VecMul (VecMinus (Vec c2_1 c2_17) (Vec c1_1 c1_17)) (VecMinus (Vec c2_1 c2_17) (Vec c1_1 c1_17)))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18) (Vec c1_2 c1_18)) (VecMinus (Vec c2_2 c2_18) (Vec c1_2 c1_18))) (VecMul (VecMinus (Vec c2_3 c2_19) (Vec c1_3 c1_19)) (VecMinus (Vec c2_3 c2_19) (Vec c1_3 c1_19))))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_20) (Vec c1_4 c1_20)) (VecMinus (Vec c2_4 c2_20) (Vec c1_4 c1_20))) (VecMul (VecMinus (Vec c2_5 c2_21) (Vec c1_5 c1_21)) (VecMinus (Vec c2_5 c2_21) (Vec c1_5 c1_21)))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22) (Vec c1_6 c1_22)) (VecMinus (Vec c2_6 c2_22) (Vec c1_6 c1_22))) (VecMul (VecMinus (Vec c2_7 c2_23) (Vec c1_7 c1_23)) (VecMinus (Vec c2_7 c2_23) (Vec c1_7 c1_23)))))) (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_8 c2_24) (Vec c1_8 c1_24)) (VecMinus (Vec c2_8 c2_24) (Vec c1_8 c1_24))) (VecMul (VecMinus (Vec c2_9 c2_25) (Vec c1_9 c1_25)) (VecMinus (Vec c2_9 c2_25) (Vec c1_9 c1_25)))) (VecMul (VecMinus (Vec c2_10 c2_26) (Vec c1_10 c1_26)) (VecMinus (Vec c2_10 c2_26) (Vec c1_10 c1_26)))) (VecAdd (VecMul (VecMinus (Vec c2_11 c2_27) (Vec c1_11 c1_27)) (VecMinus (Vec c2_11 c2_27) (Vec c1_11 c1_27))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28) (Vec c1_12 c1_28)) (VecMinus (Vec c2_12 c2_28) (Vec c1_12 c1_28))) (VecMul (VecMinus (Vec c2_13 c2_29) (Vec c1_13 c1_29)) (VecMinus (Vec c2_13 c2_29) (Vec c1_13 c1_29)))) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30) (Vec c1_14 c1_30)) (VecMinus (Vec c2_14 c2_30) (Vec c1_14 c1_30))) (VecMul (VecMinus (Vec c2_15 c2_31) (Vec c1_15 c1_31)) (VecMinus (Vec c2_15 c2_31) (Vec c1_15 c1_31)))))))) 1))))))))</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>31760</v>
       </c>
       <c r="F13" t="n">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="G13" t="n">
         <v>94.59</v>
@@ -983,13 +983,13 @@
         <v>44.16</v>
       </c>
       <c r="I13" t="n">
-        <v>56.14</v>
+        <v>53.75</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>183.86</v>
+        <v>186.25</v>
       </c>
       <c r="L13" t="n">
         <v>75</v>
@@ -1009,32 +1009,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( + ( * v1_2 v2_2 ) ( * v1_3 v2_3 ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMul (Vec v1_0 v1_2) (Vec v2_0 v2_2)) (VecMul (Vec v1_1 v1_3) (Vec v2_1 v2_3))) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_2) (Vec v2_0 v2_2)) (VecMul (Vec v1_1 v1_3) (Vec v2_1 v2_3))) 1))</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>1756</v>
       </c>
       <c r="F14" t="n">
-        <v>1756</v>
+        <v>260</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>85.19</v>
       </c>
       <c r="H14" t="n">
         <v>39.37</v>
       </c>
       <c r="I14" t="n">
-        <v>39.37</v>
+        <v>40.57</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>200.63</v>
+        <v>199.43</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -1051,32 +1051,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( + ( * v1_2 v2_2 ) ( * v1_3 v2_3 ) ) ) ( + ( + ( * v1_4 v2_4 ) ( * v1_5 v2_5 ) ) ( + ( * v1_6 v2_6 ) ( * v1_7 v2_7 ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (Vec v1_1 v1_5) (Vec v2_1 v2_5))) (VecAdd (VecMul (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (Vec v1_3 v1_7) (Vec v2_3 v2_7)))) (&lt;&lt; (VecAdd (VecAdd (VecMul (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (Vec v1_1 v1_5) (Vec v2_1 v2_5))) (VecAdd (VecMul (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (Vec v1_3 v1_7) (Vec v2_3 v2_7)))) 1))</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>3757</v>
       </c>
       <c r="F15" t="n">
-        <v>3757</v>
+        <v>463</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="H15" t="n">
         <v>40.57</v>
       </c>
       <c r="I15" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>199.43</v>
+        <v>198.23</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -1093,32 +1093,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMul (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec v1_1 v1_17) (Vec v2_1 v2_17))) (VecAdd (VecAdd (VecMul (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (Vec v1_3 v1_19) (Vec v2_3 v2_19))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (Vec v1_5 v1_21) (Vec v2_5 v2_21))) (VecAdd (VecAdd (VecMul (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (Vec v1_7 v1_23) (Vec v2_7 v2_23))) (VecAdd (VecAdd (VecMul (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (Vec v1_9 v1_25) (Vec v2_9 v2_25))) (VecAdd (VecAdd (VecMul (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (Vec v1_11 v1_27) (Vec v2_11 v2_27))) (VecAdd (VecAdd (VecMul (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec v1_13 v1_29) (Vec v2_13 v2_29))) (VecAdd (VecAdd (VecMul (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (VecMul (Vec v1_15 v1_31) (Vec v2_15 v2_31))) (&lt;&lt; (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec v1_1 v1_17) (Vec v2_1 v2_17))) (VecAdd (VecAdd (VecMul (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (Vec v1_3 v1_19) (Vec v2_3 v2_19))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (Vec v1_5 v1_21) (Vec v2_5 v2_21))) (VecAdd (VecAdd (VecMul (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (Vec v1_7 v1_23) (Vec v2_7 v2_23))) (VecAdd (VecAdd (VecMul (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (Vec v1_9 v1_25) (Vec v2_9 v2_25))) (VecAdd (VecAdd (VecMul (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (Vec v1_11 v1_27) (Vec v2_11 v2_27))) (VecAdd (VecAdd (VecMul (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec v1_13 v1_29) (Vec v2_13 v2_29))) (VecAdd (VecMul (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (VecMul (Vec v1_15 v1_31) (Vec v2_15 v2_31)))))))))) 1)))))))))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec v1_1 v1_17) (Vec v2_1 v2_17))) (VecMul (Vec v1_2 v1_18) (Vec v2_2 v2_18))) (VecMul (Vec v1_3 v1_19) (Vec v2_3 v2_19))) (VecMul (Vec v1_4 v1_20) (Vec v2_4 v2_20))) (VecAdd (VecMul (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecAdd (VecMul (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecAdd (VecMul (Vec v1_7 v1_23) (Vec v2_7 v2_23)) (VecAdd (VecMul (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecAdd (VecMul (Vec v1_9 v1_25) (Vec v2_9 v2_25)) (VecAdd (VecAdd (VecMul (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (Vec v1_11 v1_27) (Vec v2_11 v2_27))) (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec v1_13 v1_29) (Vec v2_13 v2_29))) (VecMul (Vec v1_14 v1_30) (Vec v2_14 v2_30))) (VecAdd (VecMul (Vec v1_15 v1_31) (Vec v2_15 v2_31)) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec v1_1 v1_17) (Vec v2_1 v2_17))) (VecMul (Vec v1_2 v1_18) (Vec v2_2 v2_18))) (VecMul (Vec v1_3 v1_19) (Vec v2_3 v2_19))) (VecAdd (VecMul (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecAdd (VecMul (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecAdd (VecAdd (VecMul (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (Vec v1_7 v1_23) (Vec v2_7 v2_23))) (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (Vec v1_9 v1_25) (Vec v2_9 v2_25))) (VecMul (Vec v1_10 v1_26) (Vec v2_10 v2_26))) (VecAdd (VecMul (Vec v1_11 v1_27) (Vec v2_11 v2_27)) (VecAdd (VecAdd (VecMul (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec v1_13 v1_29) (Vec v2_13 v2_29))) (VecAdd (VecMul (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (VecMul (Vec v1_15 v1_31) (Vec v2_15 v2_31)))))))))) 1))))))))))</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>15759</v>
       </c>
       <c r="F16" t="n">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="G16" t="n">
-        <v>89.29000000000001</v>
+        <v>89.28</v>
       </c>
       <c r="H16" t="n">
         <v>42.97</v>
       </c>
       <c r="I16" t="n">
-        <v>57.34</v>
+        <v>58.54</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>182.66</v>
+        <v>181.46</v>
       </c>
       <c r="L16" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1135,29 +1135,29 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 0 in_2_2 in_2_3 0 0 in_3_2 in_3_3 0 0 in_2_2 in_2_3 0) (Vec in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2))) (VecMul (Vec in_0_1 1 1 in_0_2 1 1 1 1 1 1 1 1 in_3_1 1 1 in_3_2) (VecAdd (VecMul (Vec 1 in_0_2 in_0_3 1 1 1 1 1 1 1 1 1 1 in_3_2 in_3_3 1) (VecAdd (Vec 0 0 0 0 0 in_0_2 in_0_3 0 0 in_1_2 in_1_3 0 0 0 0 0) (Vec 0 2 2 0 in_0_1 (- in_0_0) (- in_0_1) (- in_0_2) in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) 0 2 2 0))) (VecMul (Vec 1 in_0_0 in_0_1 1 in_1_1 1 1 in_1_2 in_2_1 1 1 in_2_2 1 in_3_0 in_3_1 1) (Vec 2 -2 -2 -2 2 (+ (* in_1_2 2) (* in_1_0 -2)) (+ (* in_1_3 2) (* in_1_1 -2)) -2 2 (+ (* in_2_2 2) (* in_2_0 -2)) (+ (* in_2_3 2) (* in_2_1 -2)) -2 2 -2 -2 -2)))))</t>
+          <t>(VecAdd (VecAdd (Vec in_1_1 in_1_2 in_1_3 (- in_1_2) in_2_1 in_2_2 in_2_3 (- in_2_2) in_3_1 in_3_2 in_3_3 (- in_3_2) in_2_1 in_2_2 in_2_3 (- in_2_2) 0 (- in_1_0) (- in_1_1) 0 0 (- in_2_0) (- in_2_1) 0 0 (- in_3_0) (- in_3_1) 0 0 (- in_2_0) (- in_2_1) 0) (&lt;&lt; (Vec in_1_1 in_1_2 in_1_3 (- in_1_2) in_2_1 in_2_2 in_2_3 (- in_2_2) in_3_1 in_3_2 in_3_3 (- in_3_2) in_2_1 in_2_2 in_2_3 (- in_2_2) 0 (- in_1_0) (- in_1_1) 0 0 (- in_2_0) (- in_2_1) 0 0 (- in_3_0) (- in_3_1) 0 0 (- in_2_0) (- in_2_1) 0) 16)) (VecAdd (VecMul (Vec in_0_1 in_0_2 in_0_3 in_0_2 1 1 1 1 1 1 1 1 in_3_1 in_3_2 in_3_3 in_3_2 1 in_0_0 in_0_1 1 in_1_1 1 1 in_1_2 in_2_1 1 1 in_2_2 1 in_3_0 in_3_1 1) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_1_2 in_1_3 1 1 in_2_2 in_2_3 1 1 1 1 1) (Vec 0 0 0 0 0 in_0_2 in_0_3 0 0 in_1_2 in_1_3 0 0 0 0 0 0 0 0 0 0 2 2 0 0 2 2 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_1_0 in_1_1 1 1 in_2_0 in_2_1 1 1 1 1 1) (Vec 2 2 2 -2 in_0_1 (- in_0_0) (- in_0_1) (- in_0_2) in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) 2 2 2 -2 0 -2 -2 0 2 -2 -2 -2 2 -2 -2 -2 0 -2 -2 0)))) (&lt;&lt; (VecMul (Vec in_0_1 in_0_2 in_0_3 in_0_2 1 1 1 1 1 1 1 1 in_3_1 in_3_2 in_3_3 in_3_2 1 in_0_0 in_0_1 1 in_1_1 1 1 in_1_2 in_2_1 1 1 in_2_2 1 in_3_0 in_3_1 1) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_1_2 in_1_3 1 1 in_2_2 in_2_3 1 1 1 1 1) (Vec 0 0 0 0 0 in_0_2 in_0_3 0 0 in_1_2 in_1_3 0 0 0 0 0 0 0 0 0 0 2 2 0 0 2 2 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_1_0 in_1_1 1 1 in_2_0 in_2_1 1 1 1 1 1) (Vec 2 2 2 -2 in_0_1 (- in_0_0) (- in_0_1) (- in_0_2) in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) 2 2 2 -2 0 -2 -2 0 2 -2 -2 -2 2 -2 -2 -2 0 -2 -2 0)))) 16)))</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>21507</v>
       </c>
       <c r="F17" t="n">
-        <v>7815</v>
+        <v>4947</v>
       </c>
       <c r="G17" t="n">
-        <v>63.66</v>
+        <v>77</v>
       </c>
       <c r="H17" t="n">
         <v>40.57</v>
       </c>
       <c r="I17" t="n">
-        <v>109.73</v>
+        <v>77.55</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>130.27</v>
+        <v>162.45</v>
       </c>
       <c r="L17" t="n">
         <v>8</v>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMul (Vec a_0_0 a_0_0 a_0_0 a_1_0 a_1_0 a_1_0 a_2_0 a_2_0 a_2_0) (Vec b_0_0 b_0_1 b_0_2 b_0_0 b_0_1 b_0_2 b_0_0 b_0_1 b_0_2)) (VecMul (Vec a_0_1 a_0_1 a_0_1 a_1_1 a_1_1 a_1_1 a_2_1 a_2_1 a_2_1) (Vec b_1_0 b_1_1 b_1_2 b_1_0 b_1_1 b_1_2 b_1_0 b_1_1 b_1_2))) (Vec (* a_0_2 b_2_0) (* a_0_2 b_2_1) (* a_0_2 b_2_2) (* a_1_2 b_2_0) (* a_1_2 b_2_1) (* a_1_2 b_2_2) (* a_2_2 b_2_0) (* a_2_2 b_2_1) (* a_2_2 b_2_2)))</t>
+          <t>(VecAdd (VecAdd (VecMul (Vec a_0_0 a_0_0 a_0_0 a_1_0 a_1_0 a_1_0 a_2_0 a_2_0 a_2_0) (Vec b_0_0 b_0_1 b_0_2 b_0_0 b_0_1 b_0_2 b_0_0 b_0_1 b_0_2)) (VecMul (Vec a_0_1 a_0_1 a_0_1 a_1_1 a_1_1 a_1_1 a_2_1 a_2_1 a_2_1) (Vec b_1_0 b_1_1 b_1_2 b_1_0 b_1_1 b_1_2 b_1_0 b_1_1 b_1_2))) (VecMul (Vec a_0_2 a_0_2 a_0_2 a_1_2 a_1_2 a_1_2 a_2_2 a_2_2 a_2_2) (Vec b_2_0 b_2_1 b_2_2 b_2_0 b_2_1 b_2_2 b_2_0 b_2_1 b_2_2)))</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>11256</v>
       </c>
       <c r="F18" t="n">
-        <v>2458</v>
+        <v>308</v>
       </c>
       <c r="G18" t="n">
-        <v>78.16</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="H18" t="n">
         <v>39.37</v>
@@ -1202,7 +1202,7 @@
         <v>200.63</v>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -1219,32 +1219,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>(Vec ( + ( * ( + ( * o3 ( - 1 c23 ) ) ( * c23 o2 ) ) ( - 1 c12 ) ) ( * c12 ( + ( * o3 ( - 1 c13 ) ) ( * c13 o1 ) ) ) ) )</t>
+          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec o3 1 c23 1) (Vec (- 1 c23) c12 o2 0)) (&lt;&lt; (VecMul (Vec o3 1 c23 1) (Vec (- 1 c23) c12 o2 0)) 2)) (VecAdd (VecMul (Vec 1 o3 1 c13) (VecMinus (Vec 1 1 0 o1) (Vec c12 c13 0 0))) (&lt;&lt; (VecMul (Vec 1 o3 1 c13) (VecMinus (Vec 1 1 0 o1) (Vec c12 c13 0 0))) 2))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o3 1 c23 1) (Vec (- 1 c23) c12 o2 0)) (&lt;&lt; (VecMul (Vec o3 1 c23 1) (Vec (- 1 c23) c12 o2 0)) 2)) (VecAdd (VecMul (Vec 1 o3 1 c13) (VecMinus (Vec 1 1 0 o1) (Vec c12 c13 0 0))) (&lt;&lt; (VecMul (Vec 1 o3 1 c13) (VecMinus (Vec 1 1 0 o1) (Vec c12 c13 0 0))) 2))) 1))</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>3009</v>
       </c>
       <c r="F19" t="n">
-        <v>3009</v>
+        <v>724</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>75.94</v>
       </c>
       <c r="H19" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>75.15000000000001</v>
+        <v>77.55</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>164.85</v>
+        <v>162.45</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -1261,32 +1261,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>(Vec ( + ( * ( + ( * ( + ( * o321 ( - 1 c23 ) ) ( * c23 o231 ) ) ( - 1 c13 ) ) ( * c13 o213 ) ) ( - 1 c12 ) ) ( * c12 ( + ( * ( - 1 c23 ) ( + ( * o312 ( - 1 c13 ) ) ( * c13 o132 ) ) ) ( * c23 o123 ) ) ) ) )</t>
+          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 c13 1) (Vec (- 1 c13) c12 o213 0)) (&lt;&lt; (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 c13 1) (Vec (- 1 c13) c12 o213 0)) 2)) (VecAdd (VecMul (Vec 1 (- 1 c23) 1 c23) (Vec (- 1 c12) (+ (* o312 (- 1 c13)) (* c13 o132)) 0 o123)) (&lt;&lt; (VecMul (Vec 1 (- 1 c23) 1 c23) (Vec (- 1 c12) (+ (* o312 (- 1 c13)) (* c13 o132)) 0 o123)) 2))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 c13 1) (Vec (- 1 c13) c12 o213 0)) (&lt;&lt; (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 c13 1) (Vec (- 1 c13) c12 o213 0)) 2)) (VecAdd (VecMul (Vec 1 (- 1 c23) 1 c23) (Vec (- 1 c12) (+ (* o312 (- 1 c13)) (* c13 o132)) 0 o123)) (&lt;&lt; (VecMul (Vec 1 (- 1 c23) 1 c23) (Vec (- 1 c12) (+ (* o312 (- 1 c13)) (* c13 o132)) 0 o123)) 2))) 1))</t>
         </is>
       </c>
       <c r="E20" t="n">
         <v>5012</v>
       </c>
       <c r="F20" t="n">
-        <v>5012</v>
+        <v>3226</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>35.63</v>
       </c>
       <c r="H20" t="n">
         <v>110.93</v>
       </c>
       <c r="I20" t="n">
-        <v>110.93</v>
+        <v>113.33</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>129.07</v>
+        <v>126.67</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21">
@@ -1303,32 +1303,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>(Vec ( * ( + x9602 x9604 ) ( + ( + x9608 x9610 ) ( + ( * x9613 x9615 ) x9617 ) ) ) )</t>
+          <t>(VecMul (VecAdd (VecAdd (Vec x9602 x9608 0 x9610) (&lt;&lt; (Vec x9602 x9608 0 x9610) 2)) (VecAdd (Vec x9604 (* x9613 x9615) 0 x9617) (&lt;&lt; (Vec x9604 (* x9613 x9615) 0 x9617) 2))) (&lt;&lt; (VecAdd (VecAdd (Vec x9602 x9608 0 x9610) (&lt;&lt; (Vec x9602 x9608 0 x9610) 2)) (VecAdd (Vec x9604 (* x9613 x9615) 0 x9617) (&lt;&lt; (Vec x9604 (* x9613 x9615) 0 x9617) 2))) 1))</t>
         </is>
       </c>
       <c r="E21" t="n">
         <v>1508</v>
       </c>
       <c r="F21" t="n">
-        <v>1508</v>
+        <v>522</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>65.38</v>
       </c>
       <c r="H21" t="n">
         <v>73.95</v>
       </c>
       <c r="I21" t="n">
-        <v>73.95</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>166.05</v>
+        <v>163.65</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -1345,17 +1345,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMul (VecAdd (Vec (* x9604 x9605) (+ (* x9634 x9635) (+ x9637 x9638)) 0 0) (VecAdd (Vec x9607 (* x9641 x9642) 0 0) (VecMul (Vec 1 x9644 (* x9619 x9620) 1) (Vec x9608 x9645 (* x9622 x9623) 1)))) (VecAdd (Vec (+ x9611 x9612) (* (+ x9649 x9650) (+ x9652 x9653)) 0 0) (VecAdd (Vec x9614 (* x9656 x9657) 0 0) (VecMul (Vec 1 x9659 (+ x9626 x9627) 1) (Vec x9615 x9660 (* x9629 x9630) 0))))) (&lt;&lt; (VecMul (VecAdd (Vec (* x9604 x9605) (+ (* x9634 x9635) (+ x9637 x9638)) 0 0) (VecAdd (Vec x9607 (* x9641 x9642) 0 0) (VecMul (Vec 1 x9644 (* x9619 x9620) 1) (Vec x9608 x9645 (* x9622 x9623) 1)))) (VecAdd (Vec (+ x9611 x9612) (* (+ x9649 x9650) (+ x9652 x9653)) 0 0) (VecAdd (Vec x9614 (* x9656 x9657) 0 0) (VecMul (Vec 1 x9659 (+ x9626 x9627) 1) (Vec x9615 x9660 (* x9629 x9630) 0))))) 2)) (&lt;&lt; (VecAdd (VecMul (VecAdd (Vec (* x9604 x9605) (+ (* x9634 x9635) (+ x9637 x9638)) 0 0) (VecAdd (Vec x9607 (* x9641 x9642) 0 0) (VecMul (Vec 1 x9644 (* x9619 x9620) 1) (Vec x9608 x9645 (* x9622 x9623) 1)))) (VecAdd (Vec (+ x9611 x9612) (* (+ x9649 x9650) (+ x9652 x9653)) 0 0) (VecAdd (Vec x9614 (* x9656 x9657) 0 0) (VecMul (Vec 1 x9659 (+ x9626 x9627) 1) (Vec x9615 x9660 (* x9629 x9630) 0))))) (&lt;&lt; (VecMul (VecAdd (Vec (* x9604 x9605) (+ (* x9634 x9635) (+ x9637 x9638)) 0 0) (VecAdd (Vec x9607 (* x9641 x9642) 0 0) (VecMul (Vec 1 x9644 (* x9619 x9620) 1) (Vec x9608 x9645 (* x9622 x9623) 1)))) (VecAdd (Vec (+ x9611 x9612) (* (+ x9649 x9650) (+ x9652 x9653)) 0 0) (VecAdd (Vec x9614 (* x9656 x9657) 0 0) (VecMul (Vec 1 x9659 (+ x9626 x9627) 1) (Vec x9615 x9660 (* x9629 x9630) 0))))) 2)) 1))</t>
+          <t>(VecAdd (VecMul (VecAdd (VecAdd (Vec (* x9604 x9605) (+ (* x9634 x9635) (+ x9637 x9638)) 0 0) (Vec x9607 (* x9641 x9642) 0 0)) (VecMul (Vec 1 x9644 (* x9619 x9620) 1) (Vec x9608 x9645 (* x9622 x9623) 1))) (VecAdd (VecAdd (Vec (+ x9611 x9612) (* (+ x9649 x9650) (+ x9652 x9653)) 0 0) (Vec x9614 (* x9656 x9657) 0 0)) (VecMul (Vec 1 x9659 (+ x9626 x9627) 1) (Vec x9615 x9660 (* x9629 x9630) 0)))) (VecAdd (&lt;&lt; (VecMul (VecAdd (VecAdd (Vec (* x9604 x9605) (+ (* x9634 x9635) (+ x9637 x9638)) 0 0) (Vec x9607 (* x9641 x9642) 0 0)) (VecMul (Vec 1 x9644 (* x9619 x9620) 1) (Vec x9608 x9645 (* x9622 x9623) 1))) (VecAdd (VecAdd (Vec (+ x9611 x9612) (* (+ x9649 x9650) (+ x9652 x9653)) 0 0) (Vec x9614 (* x9656 x9657) 0 0)) (VecMul (Vec 1 x9659 (+ x9626 x9627) 1) (Vec x9615 x9660 (* x9629 x9630) 0)))) 2) (&lt;&lt; (&lt;&lt; (VecMul (VecAdd (VecAdd (Vec (* x9604 x9605) (+ (* x9634 x9635) (+ x9637 x9638)) 0 0) (Vec x9607 (* x9641 x9642) 0 0)) (VecMul (Vec 1 x9644 (* x9619 x9620) 1) (Vec x9608 x9645 (* x9622 x9623) 1))) (VecAdd (VecAdd (Vec (+ x9611 x9612) (* (+ x9649 x9650) (+ x9652 x9653)) 0 0) (Vec x9614 (* x9656 x9657) 0 0)) (VecMul (Vec 1 x9659 (+ x9626 x9627) 1) (Vec x9615 x9660 (* x9629 x9630) 0)))) 2) 1)))</t>
         </is>
       </c>
       <c r="E22" t="n">
         <v>7760</v>
       </c>
       <c r="F22" t="n">
-        <v>3925</v>
+        <v>3923</v>
       </c>
       <c r="G22" t="n">
-        <v>49.42</v>
+        <v>49.45</v>
       </c>
       <c r="H22" t="n">
         <v>108.53</v>
@@ -1370,7 +1370,7 @@
         <v>126.67</v>
       </c>
       <c r="L22" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -1387,29 +1387,29 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))) 0)) (&lt;&lt; (VecMul (Vec (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))) 0)) 2)) (VecAdd (VecMul (Vec 1 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c13) (VecMinus (Vec 1 1 0 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (+ (* o5 (- 1 c15)) (* c15 o1))))) (VecMinus (VecMinus (Vec c12 c13 (- 0 0) (- 0 0)) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0))))))))))))))))))) (&lt;&lt; (VecMul (Vec 1 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c13) (VecMinus (Vec 1 1 0 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (+ (* o5 (- 1 c15)) (* c15 o1))))) (VecMinus (VecMinus (Vec c12 c13 (- 0 0) (- 0 0)) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0))))))))))))))))))) 2))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))) 0)) (&lt;&lt; (VecMul (Vec (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))) 0)) 2)) (VecAdd (VecMul (Vec 1 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c13) (VecMinus (Vec 1 1 0 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (+ (* o5 (- 1 c15)) (* c15 o1))))) (VecMinus (VecMinus (Vec c12 c13 (- 0 0) (- 0 0)) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0))))))))))))))))))) (&lt;&lt; (VecMul (Vec 1 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c13) (VecMinus (Vec 1 1 0 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (+ (* o5 (- 1 c15)) (* c15 o1))))) (VecMinus (VecMinus (Vec c12 c13 (- 0 0) (- 0 0)) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0))))))))))))))))))) 2))) 1))</t>
+          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))) 0)) (&lt;&lt; (VecMul (Vec (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))) 0)) 2)) (VecAdd (VecMul (Vec 1 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c13) (VecMinus (Vec 1 1 0 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o5 (- 1 c15)) (* c15 o1)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))) (Vec c12 c13 0 0))) (&lt;&lt; (VecMul (Vec 1 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c13) (VecMinus (Vec 1 1 0 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o5 (- 1 c15)) (* c15 o1)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))) (Vec c12 c13 0 0))) 2))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))) 0)) (&lt;&lt; (VecMul (Vec (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))) 0)) 2)) (VecAdd (VecMul (Vec 1 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c13) (VecMinus (Vec 1 1 0 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o5 (- 1 c15)) (* c15 o1)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))) (Vec c12 c13 0 0))) (&lt;&lt; (VecMul (Vec 1 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c13) (VecMinus (Vec 1 1 0 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o5 (- 1 c15)) (* c15 o1)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))) (Vec c12 c13 0 0))) 2))) 1))</t>
         </is>
       </c>
       <c r="E23" t="n">
         <v>15015</v>
       </c>
       <c r="F23" t="n">
-        <v>13259</v>
+        <v>29615</v>
       </c>
       <c r="G23" t="n">
-        <v>11.69</v>
+        <v>-97.23999999999999</v>
       </c>
       <c r="H23" t="n">
         <v>146.71</v>
       </c>
       <c r="I23" t="n">
-        <v>163.48</v>
+        <v>2467.23</v>
       </c>
       <c r="J23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>76.52</v>
+        <v>-2227.23</v>
       </c>
       <c r="L23" t="n">
         <v>75</v>
@@ -1429,17 +1429,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 in_2_1 in_2_2 in_2_3 in_2_3 0 in_3_2 in_3_3 in_3_3 0 in_3_2 in_3_3 0) (VecAdd (Vec 0 0 0 0 0 in_2_1 in_2_2 0 0 in_3_1 in_3_2 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_2_0 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_3_1 in_3_1 in_3_2 in_3_3))) (VecAdd (Vec 0 in_1_0 in_1_1 0 in_1_1 in_1_2 in_1_3 in_1_3 0 in_2_2 in_2_3 in_2_3 0 in_3_0 in_3_1 0) (Vec in_1_0 in_0_2 in_0_3 in_1_2 in_1_0 in_1_1 in_1_2 in_1_2 in_3_0 in_2_1 in_2_2 in_2_2 in_3_0 in_2_2 in_2_3 in_3_2))) (VecAdd (Vec in_0_1 in_0_1 in_0_2 in_0_3 in_0_1 (+ in_1_0 in_0_2) (+ in_1_1 in_0_3) in_0_3 (+ in_2_1 in_2_0) (+ in_2_0 in_1_2) (+ in_2_1 in_1_3) in_1_3 in_2_1 in_2_1 in_2_2 in_2_3) (Vec in_0_0 in_0_0 in_0_1 in_0_2 in_0_0 (+ in_0_1 in_0_0) (+ in_0_2 in_0_1) in_0_2 (+ in_1_1 in_1_0) (+ in_1_1 in_1_0) (+ in_1_2 in_1_1) in_1_2 in_2_0 in_2_0 in_2_1 in_2_2)))</t>
+          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 in_2_1 in_2_2 in_2_3 in_2_3 0 in_3_2 in_3_3 in_3_3 0 in_3_2 in_3_3 0) (VecAdd (Vec 0 0 0 0 0 in_2_1 in_2_2 0 0 in_3_1 in_3_2 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_2_0 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_3_1 in_3_1 in_3_2 in_3_3))) (VecAdd (Vec 0 in_1_0 in_1_1 0 in_1_1 in_1_2 in_1_3 in_1_3 0 in_2_2 in_2_3 in_2_3 0 in_3_0 in_3_1 0) (Vec in_1_0 in_0_2 in_0_3 in_1_2 in_1_0 in_1_1 in_1_2 in_1_2 in_3_0 in_2_1 in_2_2 in_2_2 in_3_0 in_2_2 in_2_3 in_3_2))) (VecAdd (VecAdd (Vec 0 0 0 0 0 in_1_0 in_1_1 0 in_2_1 in_2_0 in_2_1 0 0 0 0 0) (Vec in_0_1 in_0_1 in_0_2 in_0_3 in_0_1 in_0_2 in_0_3 in_0_3 in_2_0 in_1_2 in_1_3 in_1_3 in_2_1 in_2_1 in_2_2 in_2_3)) (VecAdd (Vec 0 0 0 0 0 in_0_1 in_0_2 0 in_1_1 in_1_1 in_1_2 0 0 0 0 0) (Vec in_0_0 in_0_0 in_0_1 in_0_2 in_0_0 in_0_0 in_0_1 in_0_2 in_1_0 in_1_0 in_1_1 in_1_2 in_2_0 in_2_0 in_2_1 in_2_2))))</t>
         </is>
       </c>
       <c r="E24" t="n">
         <v>21006</v>
       </c>
       <c r="F24" t="n">
-        <v>2512</v>
+        <v>14</v>
       </c>
       <c r="G24" t="n">
-        <v>88.04000000000001</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="H24" t="n">
         <v>7.19</v>
@@ -1454,7 +1454,7 @@
         <v>232.81</v>
       </c>
       <c r="L24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -1471,17 +1471,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>(Vec ( + v2_0 ( + 2 ( * v1_0 5 ) ) ) ( + v2_1 ( + 2 ( * v1_1 5 ) ) ) ( + v2_2 ( + 2 ( * v1_2 5 ) ) ) ( + v2_3 ( + 2 ( * v1_3 5 ) ) ) )</t>
+          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3) (VecAdd (Vec 2 2 2 2) (VecMul (Vec v1_0 v1_1 v1_2 v1_3) (Vec 5 5 5 5))))</t>
         </is>
       </c>
       <c r="E25" t="n">
         <v>3006</v>
       </c>
       <c r="F25" t="n">
-        <v>3006</v>
+        <v>108</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>96.41</v>
       </c>
       <c r="H25" t="n">
         <v>39.37</v>
@@ -1496,7 +1496,7 @@
         <v>200.63</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1513,17 +1513,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3 v2_4 v2_5 v2_6 v2_7 v2_8 v2_9 v2_10 v2_11 v2_12 v2_13 v2_14 v2_15) (VecAdd (Vec 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2) (Vec (* v1_0 5) (* v1_1 5) (* v1_2 5) (* v1_3 5) (* v1_4 5) (* v1_5 5) (* v1_6 5) (* v1_7 5) (* v1_8 5) (* v1_9 5) (* v1_10 5) (* v1_11 5) (* v1_12 5) (* v1_13 5) (* v1_14 5) (* v1_15 5))))</t>
+          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3 v2_4 v2_5 v2_6 v2_7 v2_8 v2_9 v2_10 v2_11 v2_12 v2_13 v2_14 v2_15) (VecAdd (Vec 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2) (VecMul (Vec v1_0 v1_1 v1_2 v1_3 v1_4 v1_5 v1_6 v1_7 v1_8 v1_9 v1_10 v1_11 v1_12 v1_13 v1_14 v1_15) (Vec 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5))))</t>
         </is>
       </c>
       <c r="E26" t="n">
         <v>12006</v>
       </c>
       <c r="F26" t="n">
-        <v>4008</v>
+        <v>108</v>
       </c>
       <c r="G26" t="n">
-        <v>66.62</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H26" t="n">
         <v>39.37</v>
@@ -1538,7 +1538,7 @@
         <v>200.63</v>
       </c>
       <c r="L26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( - ( + v1_0 v2_0 ) ( * ( * v1_0 v2_0 ) 2 ) ) ( - ( + v1_1 v2_1 ) ( * 2 ( * v1_1 v2_1 ) ) ) ) ( - ( + v1_2 v2_2 ) ( * 2 ( * v1_2 v2_2 ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2 v1_1 0 v2_0 v2_2 v2_1 0) (&lt;&lt; (Vec v1_0 v1_2 v1_1 0 v2_0 v2_2 v2_1 0) 4)) (VecMul (Vec (* v1_0 v2_0) 2 2 1) (VecMul (Vec 1 v1_2 v1_1 1) (Vec 2 v2_2 v2_1 0)))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_2 v1_1 0 v2_0 v2_2 v2_1 0) (&lt;&lt; (Vec v1_0 v1_2 v1_1 0 v2_0 v2_2 v2_1 0) 4)) (VecMul (Vec (* v1_0 v2_0) 2 2 1) (VecMul (Vec 1 v1_2 v1_1 1) (Vec 2 v2_2 v2_1 0)))) 2)) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2 v1_1 0 v2_0 v2_2 v2_1 0) (&lt;&lt; (Vec v1_0 v1_2 v1_1 0 v2_0 v2_2 v2_1 0) 4)) (VecMul (Vec (* v1_0 v2_0) 2 2 1) (VecMul (Vec 1 v1_2 v1_1 1) (Vec 2 v2_2 v2_1 0)))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_2 v1_1 0 v2_0 v2_2 v2_1 0) (&lt;&lt; (Vec v1_0 v1_2 v1_1 0 v2_0 v2_2 v2_1 0) 4)) (VecMul (Vec (* v1_0 v2_0) 2 2 1) (VecMul (Vec 1 v1_2 v1_1 1) (Vec 2 v2_2 v2_1 0)))) 2)) 1))</t>
         </is>
       </c>
       <c r="E27" t="n">
         <v>3509</v>
       </c>
       <c r="F27" t="n">
-        <v>3509</v>
+        <v>636</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>81.88</v>
       </c>
       <c r="H27" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>75.15000000000001</v>
+        <v>77.55</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>164.85</v>
+        <v>162.45</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -1597,32 +1597,32 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( - ( + v1_0 v2_0 ) ( * ( * v1_0 v2_0 ) 2 ) ) ( - ( + v1_1 v2_1 ) ( * 2 ( * v1_1 v2_1 ) ) ) ) ( + ( + ( - ( + v1_2 v2_2 ) ( * 2 ( * v1_2 v2_2 ) ) ) ( - ( + v1_3 v2_3 ) ( * 2 ( * v1_3 v2_3 ) ) ) ) ( - ( + v1_4 v2_4 ) ( * 2 ( * v1_4 v2_4 ) ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2 0 v1_3) (Vec v2_0 v2_2 0 v2_3)) (VecMul (Vec (* v1_0 v2_0) 2 1 2) (VecMul (Vec 1 v1_2 1 v1_3) (Vec 2 v2_2 0 v2_3)))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_2 0 v1_3) (Vec v2_0 v2_2 0 v2_3)) (VecMul (Vec (* v1_0 v2_0) 2 1 2) (VecMul (Vec 1 v1_2 1 v1_3) (Vec 2 v2_2 0 v2_3)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4) (Vec v2_1 v2_4)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_4) (Vec v2_1 v2_4))))) (&lt;&lt; (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2 0 v1_3) (Vec v2_0 v2_2 0 v2_3)) (VecMul (Vec (* v1_0 v2_0) 2 1 2) (VecMul (Vec 1 v1_2 1 v1_3) (Vec 2 v2_2 0 v2_3)))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_2 0 v1_3) (Vec v2_0 v2_2 0 v2_3)) (VecMul (Vec (* v1_0 v2_0) 2 1 2) (VecMul (Vec 1 v1_2 1 v1_3) (Vec 2 v2_2 0 v2_3)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4) (Vec v2_1 v2_4)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_4) (Vec v2_1 v2_4))))) 1))</t>
         </is>
       </c>
       <c r="E28" t="n">
         <v>6010</v>
       </c>
       <c r="F28" t="n">
-        <v>6010</v>
+        <v>774</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>87.12</v>
       </c>
       <c r="H28" t="n">
         <v>76.34999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>76.34999999999999</v>
+        <v>78.75</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>163.65</v>
+        <v>161.25</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
@@ -1639,32 +1639,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (Vec (* v1_0 v2_0) 2) (Vec 2 (* v1_8 v2_8)))) (VecMinus (VecAdd (Vec v1_1 v1_9) (Vec v2_1 v2_9)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_9) (Vec v2_1 v2_9))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_10) (Vec v2_2 v2_10)))) (VecMinus (VecAdd (Vec v1_3 v1_11) (Vec v2_3 v2_11)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_11) (Vec v2_3 v2_11)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (Vec 2 2) (VecMul (Vec v1_4 v1_12) (Vec v2_4 v2_12)))) (VecMinus (VecAdd (Vec v1_5 v1_13) (Vec v2_5 v2_13)) (VecMul (Vec 2 2) (VecMul (Vec v1_5 v1_13) (Vec v2_5 v2_13))))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (Vec 2 2) (VecMul (Vec v1_6 v1_14) (Vec v2_6 v2_14)))) (VecMinus (VecAdd (Vec v1_7 v1_15) (Vec v2_7 v2_15)) (VecMul (Vec 2 2) (VecMul (Vec v1_7 v1_15) (Vec v2_7 v2_15))))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (Vec (* v1_0 v2_0) 2) (Vec 2 (* v1_8 v2_8)))) (VecMinus (VecAdd (Vec v1_1 v1_9) (Vec v2_1 v2_9)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_9) (Vec v2_1 v2_9))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_10) (Vec v2_2 v2_10)))) (VecMinus (VecAdd (Vec v1_3 v1_11) (Vec v2_3 v2_11)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_11) (Vec v2_3 v2_11)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (Vec 2 2) (VecMul (Vec v1_4 v1_12) (Vec v2_4 v2_12)))) (VecMinus (VecAdd (Vec v1_5 v1_13) (Vec v2_5 v2_13)) (VecMul (Vec 2 2) (VecMul (Vec v1_5 v1_13) (Vec v2_5 v2_13))))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (Vec 2 2) (VecMul (Vec v1_6 v1_14) (Vec v2_6 v2_14)))) (VecMinus (VecAdd (Vec v1_7 v1_15) (Vec v2_7 v2_15)) (VecMul (Vec 2 2) (VecMul (Vec v1_7 v1_15) (Vec v2_7 v2_15))))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (VecMul (Vec v1_0 2 v2_0 1) (&lt;&lt; (Vec v1_0 2 v2_0 1) 2)) (VecMul (Vec 2 v1_8 1 v2_8) (&lt;&lt; (Vec 2 v1_8 1 v2_8) 2)))) (VecMinus (VecAdd (Vec v1_1 v1_9) (Vec v2_1 v2_9)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_9) (Vec v2_1 v2_9))))) (VecMinus (VecAdd (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_10) (Vec v2_2 v2_10))))) (VecMinus (VecAdd (Vec v1_3 v1_11) (Vec v2_3 v2_11)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_11) (Vec v2_3 v2_11))))) (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (Vec 2 2) (VecMul (Vec v1_4 v1_12) (Vec v2_4 v2_12)))) (VecAdd (VecMinus (VecAdd (Vec v1_5 v1_13) (Vec v2_5 v2_13)) (VecMul (Vec 2 2) (VecMul (Vec v1_5 v1_13) (Vec v2_5 v2_13)))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (Vec 2 2) (VecMul (Vec v1_6 v1_14) (Vec v2_6 v2_14)))) (VecMinus (VecAdd (Vec v1_7 v1_15) (Vec v2_7 v2_15)) (VecMul (Vec 2 2) (VecMul (Vec v1_7 v1_15) (Vec v2_7 v2_15))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (VecMul (Vec v1_0 2 v2_0 1) (&lt;&lt; (Vec v1_0 2 v2_0 1) 2)) (VecMul (Vec 2 v1_8 1 v2_8) (&lt;&lt; (Vec 2 v1_8 1 v2_8) 2)))) (VecMinus (VecAdd (Vec v1_1 v1_9) (Vec v2_1 v2_9)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_9) (Vec v2_1 v2_9))))) (VecMinus (VecAdd (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_10) (Vec v2_2 v2_10))))) (VecAdd (VecMinus (VecAdd (Vec v1_3 v1_11) (Vec v2_3 v2_11)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_11) (Vec v2_3 v2_11)))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (Vec 2 2) (VecMul (Vec v1_4 v1_12) (Vec v2_4 v2_12)))) (VecMinus (VecAdd (Vec v1_5 v1_13) (Vec v2_5 v2_13)) (VecMul (Vec 2 2) (VecMul (Vec v1_5 v1_13) (Vec v2_5 v2_13))))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (Vec 2 2) (VecMul (Vec v1_6 v1_14) (Vec v2_6 v2_14)))) (VecMinus (VecAdd (Vec v1_7 v1_15) (Vec v2_7 v2_15)) (VecMul (Vec 2 2) (VecMul (Vec v1_7 v1_15) (Vec v2_7 v2_15)))))))) 1)))))</t>
         </is>
       </c>
       <c r="E29" t="n">
         <v>19761</v>
       </c>
       <c r="F29" t="n">
-        <v>2087</v>
+        <v>1899</v>
       </c>
       <c r="G29" t="n">
-        <v>89.44</v>
+        <v>90.39</v>
       </c>
       <c r="H29" t="n">
         <v>77.55</v>
       </c>
       <c r="I29" t="n">
-        <v>78.75</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>161.25</v>
+        <v>156.46</v>
       </c>
       <c r="L29" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30">
@@ -1681,17 +1681,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>(VecAdd (Vec c1_0 c1_1 c1_2 c1_3) (VecAdd (Vec c2_0 c2_1 c2_2 c2_3) (Vec (* c0_0 (+ c3_0 (* c0_0 c4_0))) (* c0_1 (+ c3_1 (* c0_1 c4_1))) (* c0_2 (+ c3_2 (* c0_2 c4_2))) (* c0_3 (+ c3_3 (* c0_3 c4_3))))))</t>
+          <t>(VecAdd (Vec c1_0 c1_1 c1_2 c1_3) (VecAdd (Vec c2_0 c2_1 c2_2 c2_3) (VecMul (Vec c0_0 c0_1 c0_2 c0_3) (VecAdd (Vec c3_0 c3_1 c3_2 c3_3) (VecMul (Vec c0_0 c0_1 c0_2 c0_3) (Vec c4_0 c4_1 c4_2 c4_3))))))</t>
         </is>
       </c>
       <c r="E30" t="n">
         <v>5009</v>
       </c>
       <c r="F30" t="n">
-        <v>3011</v>
+        <v>212</v>
       </c>
       <c r="G30" t="n">
-        <v>39.89</v>
+        <v>95.77</v>
       </c>
       <c r="H30" t="n">
         <v>75.15000000000001</v>
@@ -1706,7 +1706,7 @@
         <v>164.85</v>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -1765,32 +1765,32 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2 c2_1 1) (Vec c1_0 c1_2 c1_1 0)) (VecMinus (Vec c2_0 c2_2 c2_1 0) (Vec c1_0 c1_2 c1_1 0))) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_2 c2_1 1) (Vec c1_0 c1_2 c1_1 0)) (VecMinus (Vec c2_0 c2_2 c2_1 0) (Vec c1_0 c1_2 c1_1 0))) 2)) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2 c2_1 1) (Vec c1_0 c1_2 c1_1 0)) (VecMinus (Vec c2_0 c2_2 c2_1 0) (Vec c1_0 c1_2 c1_1 0))) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_2 c2_1 1) (Vec c1_0 c1_2 c1_1 0)) (VecMinus (Vec c2_0 c2_2 c2_1 0) (Vec c1_0 c1_2 c1_1 0))) 2)) 1))</t>
         </is>
       </c>
       <c r="E32" t="n">
         <v>2757</v>
       </c>
       <c r="F32" t="n">
-        <v>2757</v>
+        <v>218</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>92.09</v>
       </c>
       <c r="H32" t="n">
         <v>40.57</v>
       </c>
       <c r="I32" t="n">
-        <v>40.57</v>
+        <v>42.97</v>
       </c>
       <c r="J32" t="b">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>199.43</v>
+        <v>197.03</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -1807,32 +1807,32 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( + ( + ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ( * ( - c2_3 c1_3 ) ( - c2_3 c1_3 ) ) ) ( * ( - c2_4 c1_4 ) ( - c2_4 c1_4 ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2 1 c2_3) (Vec c1_0 c1_2 0 c1_3)) (VecMinus (Vec c2_0 c2_2 0 c2_3) (Vec c1_0 c1_2 0 c1_3))) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_2 1 c2_3) (Vec c1_0 c1_2 0 c1_3)) (VecMinus (Vec c2_0 c2_2 0 c2_3) (Vec c1_0 c1_2 0 c1_3))) 2)) (VecMul (VecMinus (Vec c2_1 c2_4) (Vec c1_1 c1_4)) (VecMinus (Vec c2_1 c2_4) (Vec c1_1 c1_4)))) (&lt;&lt; (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2 1 c2_3) (Vec c1_0 c1_2 0 c1_3)) (VecMinus (Vec c2_0 c2_2 0 c2_3) (Vec c1_0 c1_2 0 c1_3))) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_2 1 c2_3) (Vec c1_0 c1_2 0 c1_3)) (VecMinus (Vec c2_0 c2_2 0 c2_3) (Vec c1_0 c1_2 0 c1_3))) 2)) (VecMul (VecMinus (Vec c2_1 c2_4) (Vec c1_1 c1_4)) (VecMinus (Vec c2_1 c2_4) (Vec c1_1 c1_4)))) 1))</t>
         </is>
       </c>
       <c r="E33" t="n">
         <v>4758</v>
       </c>
       <c r="F33" t="n">
-        <v>4758</v>
+        <v>322</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>93.23</v>
       </c>
       <c r="H33" t="n">
         <v>41.77</v>
       </c>
       <c r="I33" t="n">
-        <v>41.77</v>
+        <v>44.16</v>
       </c>
       <c r="J33" t="b">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>198.23</v>
+        <v>195.84</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
@@ -1849,32 +1849,32 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8) (Vec c1_0 c1_8)) (VecMinus (Vec c2_0 c2_8) (Vec c1_0 c1_8))) (VecMul (VecMinus (Vec c2_1 c2_9) (Vec c1_1 c1_9)) (VecMinus (Vec c2_1 c2_9) (Vec c1_1 c1_9)))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_10) (Vec c1_2 c1_10)) (VecMinus (Vec c2_2 c2_10) (Vec c1_2 c1_10))) (VecMul (VecMinus (Vec c2_3 c2_11) (Vec c1_3 c1_11)) (VecMinus (Vec c2_3 c2_11) (Vec c1_3 c1_11))))) (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_12) (Vec c1_4 c1_12)) (VecMinus (Vec c2_4 c2_12) (Vec c1_4 c1_12))) (VecMul (VecMinus (Vec c2_5 c2_13) (Vec c1_5 c1_13)) (VecMinus (Vec c2_5 c2_13) (Vec c1_5 c1_13)))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14) (Vec c1_6 c1_14)) (VecMinus (Vec c2_6 c2_14) (Vec c1_6 c1_14))) (VecMul (VecMinus (Vec c2_7 c2_15) (Vec c1_7 c1_15)) (VecMinus (Vec c2_7 c2_15) (Vec c1_7 c1_15))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8) (Vec c1_0 c1_8)) (VecMinus (Vec c2_0 c2_8) (Vec c1_0 c1_8))) (VecMul (VecMinus (Vec c2_1 c2_9) (Vec c1_1 c1_9)) (VecMinus (Vec c2_1 c2_9) (Vec c1_1 c1_9)))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_10) (Vec c1_2 c1_10)) (VecMinus (Vec c2_2 c2_10) (Vec c1_2 c1_10))) (VecMul (VecMinus (Vec c2_3 c2_11) (Vec c1_3 c1_11)) (VecMinus (Vec c2_3 c2_11) (Vec c1_3 c1_11))))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_12) (Vec c1_4 c1_12)) (VecMinus (Vec c2_4 c2_12) (Vec c1_4 c1_12))) (VecMul (VecMinus (Vec c2_5 c2_13) (Vec c1_5 c1_13)) (VecMinus (Vec c2_5 c2_13) (Vec c1_5 c1_13)))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14) (Vec c1_6 c1_14)) (VecMinus (Vec c2_6 c2_14) (Vec c1_6 c1_14))) (VecMul (VecMinus (Vec c2_7 c2_15) (Vec c1_7 c1_15)) (VecMinus (Vec c2_7 c2_15) (Vec c1_7 c1_15)))))) 1)))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8) (Vec c1_0 c1_8)) (VecMinus (Vec c2_0 c2_8) (Vec c1_0 c1_8))) (VecMul (VecMinus (Vec c2_1 c2_9) (Vec c1_1 c1_9)) (VecMinus (Vec c2_1 c2_9) (Vec c1_1 c1_9)))) (VecMul (VecMinus (Vec c2_2 c2_10) (Vec c1_2 c1_10)) (VecMinus (Vec c2_2 c2_10) (Vec c1_2 c1_10)))) (VecMul (VecMinus (Vec c2_3 c2_11) (Vec c1_3 c1_11)) (VecMinus (Vec c2_3 c2_11) (Vec c1_3 c1_11)))) (VecAdd (VecMul (VecMinus (Vec c2_4 c2_12) (Vec c1_4 c1_12)) (VecMinus (Vec c2_4 c2_12) (Vec c1_4 c1_12))) (VecAdd (VecMul (VecMinus (Vec c2_5 c2_13) (Vec c1_5 c1_13)) (VecMinus (Vec c2_5 c2_13) (Vec c1_5 c1_13))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14) (Vec c1_6 c1_14)) (VecMinus (Vec c2_6 c2_14) (Vec c1_6 c1_14))) (VecMul (VecMinus (Vec c2_7 c2_15) (Vec c1_7 c1_15)) (VecMinus (Vec c2_7 c2_15) (Vec c1_7 c1_15)))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8) (Vec c1_0 c1_8)) (VecMinus (Vec c2_0 c2_8) (Vec c1_0 c1_8))) (VecMul (VecMinus (Vec c2_1 c2_9) (Vec c1_1 c1_9)) (VecMinus (Vec c2_1 c2_9) (Vec c1_1 c1_9)))) (VecMul (VecMinus (Vec c2_2 c2_10) (Vec c1_2 c1_10)) (VecMinus (Vec c2_2 c2_10) (Vec c1_2 c1_10)))) (VecAdd (VecMul (VecMinus (Vec c2_3 c2_11) (Vec c1_3 c1_11)) (VecMinus (Vec c2_3 c2_11) (Vec c1_3 c1_11))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_12) (Vec c1_4 c1_12)) (VecMinus (Vec c2_4 c2_12) (Vec c1_4 c1_12))) (VecMul (VecMinus (Vec c2_5 c2_13) (Vec c1_5 c1_13)) (VecMinus (Vec c2_5 c2_13) (Vec c1_5 c1_13)))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14) (Vec c1_6 c1_14)) (VecMinus (Vec c2_6 c2_14) (Vec c1_6 c1_14))) (VecMul (VecMinus (Vec c2_7 c2_15) (Vec c1_7 c1_15)) (VecMinus (Vec c2_7 c2_15) (Vec c1_7 c1_15))))))) 1)))))</t>
         </is>
       </c>
       <c r="E34" t="n">
         <v>15759</v>
       </c>
       <c r="F34" t="n">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="G34" t="n">
-        <v>94.38</v>
+        <v>94.36</v>
       </c>
       <c r="H34" t="n">
         <v>42.97</v>
       </c>
       <c r="I34" t="n">
-        <v>45.36</v>
+        <v>48.96</v>
       </c>
       <c r="J34" t="b">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>194.64</v>
+        <v>191.04</v>
       </c>
       <c r="L34" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35">
@@ -1891,32 +1891,32 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( * v1_2 v2_2 ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMul (Vec v1_0 v1_2 v1_1 1) (Vec v2_0 v2_2 v2_1 0)) (&lt;&lt; (VecMul (Vec v1_0 v1_2 v1_1 1) (Vec v2_0 v2_2 v2_1 0)) 2)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_2 v1_1 1) (Vec v2_0 v2_2 v2_1 0)) (&lt;&lt; (VecMul (Vec v1_0 v1_2 v1_1 1) (Vec v2_0 v2_2 v2_1 0)) 2)) 1))</t>
         </is>
       </c>
       <c r="E35" t="n">
         <v>1256</v>
       </c>
       <c r="F35" t="n">
-        <v>1256</v>
+        <v>215</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>82.88</v>
       </c>
       <c r="H35" t="n">
         <v>39.37</v>
       </c>
       <c r="I35" t="n">
-        <v>39.37</v>
+        <v>41.77</v>
       </c>
       <c r="J35" t="b">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>200.63</v>
+        <v>198.23</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( + ( + ( * v1_2 v2_2 ) ( * v1_3 v2_3 ) ) ( * v1_4 v2_4 ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_2 1 v1_3) (Vec v2_0 v2_2 0 v2_3)) (&lt;&lt; (VecMul (Vec v1_0 v1_2 1 v1_3) (Vec v2_0 v2_2 0 v2_3)) 2)) (VecMul (Vec v1_1 v1_4) (Vec v2_1 v2_4))) (&lt;&lt; (VecAdd (VecAdd (VecMul (Vec v1_0 v1_2 1 v1_3) (Vec v2_0 v2_2 0 v2_3)) (&lt;&lt; (VecMul (Vec v1_0 v1_2 1 v1_3) (Vec v2_0 v2_2 0 v2_3)) 2)) (VecMul (Vec v1_1 v1_4) (Vec v2_1 v2_4))) 1))</t>
         </is>
       </c>
       <c r="E36" t="n">
         <v>2257</v>
       </c>
       <c r="F36" t="n">
-        <v>2257</v>
+        <v>317</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>85.95</v>
       </c>
       <c r="H36" t="n">
         <v>40.57</v>
       </c>
       <c r="I36" t="n">
-        <v>40.57</v>
+        <v>42.97</v>
       </c>
       <c r="J36" t="b">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>199.43</v>
+        <v>197.03</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -1975,32 +1975,32 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMul (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (Vec v1_1 v1_9) (Vec v2_1 v2_9))) (VecAdd (VecAdd (VecMul (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (Vec v1_3 v1_11) (Vec v2_3 v2_11))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (Vec v1_5 v1_13) (Vec v2_5 v2_13))) (VecAdd (VecAdd (VecMul (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (Vec v1_7 v1_15) (Vec v2_7 v2_15))) (&lt;&lt; (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (Vec v1_1 v1_9) (Vec v2_1 v2_9))) (VecAdd (VecAdd (VecMul (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (Vec v1_3 v1_11) (Vec v2_3 v2_11))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (Vec v1_5 v1_13) (Vec v2_5 v2_13))) (VecAdd (VecMul (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (Vec v1_7 v1_15) (Vec v2_7 v2_15)))))) 1)))))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (Vec v1_1 v1_9) (Vec v2_1 v2_9))) (VecAdd (VecMul (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (Vec v1_3 v1_11) (Vec v2_3 v2_11)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (Vec v1_5 v1_13) (Vec v2_5 v2_13))) (VecAdd (VecMul (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (Vec v1_7 v1_15) (Vec v2_7 v2_15))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (Vec v1_1 v1_9) (Vec v2_1 v2_9))) (VecAdd (VecMul (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (Vec v1_3 v1_11) (Vec v2_3 v2_11)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (Vec v1_5 v1_13) (Vec v2_5 v2_13))) (VecAdd (VecMul (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (Vec v1_7 v1_15) (Vec v2_7 v2_15))))) 1))</t>
         </is>
       </c>
       <c r="E37" t="n">
         <v>7758</v>
       </c>
       <c r="F37" t="n">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="G37" t="n">
-        <v>88.76000000000001</v>
+        <v>88.81</v>
       </c>
       <c r="H37" t="n">
         <v>41.77</v>
       </c>
       <c r="I37" t="n">
-        <v>47.76</v>
+        <v>42.97</v>
       </c>
       <c r="J37" t="b">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>192.24</v>
+        <v>197.03</v>
       </c>
       <c r="L37" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38">
@@ -2017,32 +2017,32 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>(VecAdd (Vec in_1_1 (+ in_1_2 (- in_1_0)) (- in_1_1) in_2_1 (+ in_2_2 (- in_2_0)) (- in_2_1) in_1_1 (+ in_1_2 (- in_1_0)) (- in_1_1)) (VecMul (Vec in_0_1 1 in_0_1 1 1 1 in_2_1 1 in_2_1) (Vec 2 (+ (* in_0_2 2) (* in_0_0 -2)) -2 (+ in_0_1 (* in_1_1 2)) (+ (+ in_0_2 (- in_0_0)) (+ (* in_1_2 2) (* in_1_0 -2))) (+ (- in_0_1) (* in_1_1 -2)) 2 (+ (* in_2_2 2) (* in_2_0 -2)) -2)))</t>
+          <t>(VecAdd (VecAdd (VecNeg (Vec in_1_1 in_1_2 in_1_1 in_2_1 in_2_2 in_2_1 in_1_1 in_1_2 in_1_1 0 in_1_0 0 0 in_2_0 0 0 in_1_0 0)) (&lt;&lt; (VecNeg (Vec in_1_1 in_1_2 in_1_1 in_2_1 in_2_2 in_2_1 in_1_1 in_1_2 in_1_1 0 in_1_0 0 0 in_2_0 0 0 in_1_0 0)) 9)) (VecMul (Vec in_0_1 1 in_0_1 1 1 1 in_2_1 1 in_2_1) (VecAdd (VecMul (Vec 1 in_0_2 1 1 1 1 1 in_2_2 1) (Vec 0 2 0 in_0_1 (+ in_0_2 (- in_0_0)) (- in_0_1) 0 2 0)) (VecMul (Vec 1 in_0_0 1 in_1_1 1 in_1_1 1 in_2_0 1) (Vec 2 -2 -2 2 (+ (* in_1_2 2) (* in_1_0 -2)) -2 2 -2 -2)))))</t>
         </is>
       </c>
       <c r="E38" t="n">
         <v>9757</v>
       </c>
       <c r="F38" t="n">
-        <v>6610</v>
+        <v>1874</v>
       </c>
       <c r="G38" t="n">
-        <v>32.25</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="H38" t="n">
         <v>40.57</v>
       </c>
       <c r="I38" t="n">
-        <v>75.15000000000001</v>
+        <v>111.79</v>
       </c>
       <c r="J38" t="b">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>164.85</v>
+        <v>128.21</v>
       </c>
       <c r="L38" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 in_3_2 in_3_3 in_3_4 0 0 in_4_2 in_4_3 in_4_4 0 0 in_3_2 in_3_3 in_3_4 0) (Vec in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) (- in_1_3) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) (- in_2_3) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) (- in_3_3) in_4_1 (- in_4_0) (- in_4_1) (- in_4_2) (- in_4_3) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) (- in_3_3))) (VecMul (Vec in_0_1 1 1 1 in_0_3 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_4_1 1 1 1 in_4_3) (VecAdd (VecMul (Vec 1 in_0_2 in_0_3 in_0_4 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_4_2 in_4_3 in_4_4 1) (VecAdd (Vec 0 0 0 0 0 0 in_0_2 in_0_3 in_0_4 0 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 0 0 0 0) (Vec 0 2 2 2 0 in_0_1 (- in_0_0) (- in_0_1) (- in_0_2) (- in_0_3) in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) (- in_1_3) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) (- in_2_3) 0 2 2 2 0))) (VecMul (Vec 1 in_0_0 in_0_1 in_0_2 1 in_1_1 1 1 1 in_1_3 in_2_1 1 1 1 in_2_3 in_3_1 1 1 1 in_3_3 1 in_4_0 in_4_1 in_4_2 1) (VecAdd (VecMul (Vec 1 1 1 1 1 1 in_1_2 in_1_3 in_1_4 1 1 in_2_2 in_2_3 in_2_4 1 1 in_3_2 in_3_3 in_3_4 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 2 2 2 0 0 2 2 2 0 0 2 2 2 0 0 0 0 0 0)) (Vec 2 -2 -2 -2 -2 2 (* in_1_0 -2) (* in_1_1 -2) (* in_1_2 -2) -2 2 (* in_2_0 -2) (* in_2_1 -2) (* in_2_2 -2) -2 2 (* in_3_0 -2) (* in_3_1 -2) (* in_3_2 -2) -2 2 -2 -2 -2 -2))))))</t>
+          <t>(VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 in_3_2 in_3_3 in_3_4 0 0 in_4_2 in_4_3 in_4_4 0 0 in_3_2 in_3_3 in_3_4 0) (Vec in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) (- in_1_3) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) (- in_2_3) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) (- in_3_3) in_4_1 (- in_4_0) (- in_4_1) (- in_4_2) (- in_4_3) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) (- in_3_3))) (VecMul (Vec in_0_1 1 1 1 in_0_3 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_4_1 1 1 1 in_4_3) (VecAdd (VecMul (Vec 1 in_0_2 in_0_3 in_0_4 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_4_2 in_4_3 in_4_4 1) (VecAdd (Vec 0 0 0 0 0 0 in_0_2 in_0_3 in_0_4 0 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 0 0 0 0) (Vec 0 2 2 2 0 in_0_1 (- in_0_0) (- in_0_1) (- in_0_2) (- in_0_3) in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) (- in_1_3) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) (- in_2_3) 0 2 2 2 0))) (VecMul (Vec 1 in_0_0 in_0_1 in_0_2 1 in_1_1 1 1 1 in_1_3 in_2_1 1 1 1 in_2_3 in_3_1 1 1 1 in_3_3 1 in_4_0 in_4_1 in_4_2 1) (VecAdd (VecMul (Vec 1 1 1 1 1 1 in_1_2 in_1_3 in_1_4 1 1 in_2_2 in_2_3 in_2_4 1 1 in_3_2 in_3_3 in_3_4 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 2 2 2 0 0 2 2 2 0 0 2 2 2 0 0 0 0 0 0)) (VecMul (Vec 1 1 1 1 1 1 in_1_0 in_1_1 in_1_2 1 1 in_2_0 in_2_1 in_2_2 1 1 in_3_0 in_3_1 in_3_2 1 1 1 1 1 1) (Vec 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2)))))))</t>
         </is>
       </c>
       <c r="E39" t="n">
         <v>37757</v>
       </c>
       <c r="F39" t="n">
-        <v>10666</v>
+        <v>8516</v>
       </c>
       <c r="G39" t="n">
-        <v>71.75</v>
+        <v>77.45</v>
       </c>
       <c r="H39" t="n">
         <v>40.57</v>
@@ -2084,7 +2084,7 @@
         <v>130.27</v>
       </c>
       <c r="L39" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40">
@@ -2143,32 +2143,32 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>(Vec ( + ( * ( + ( * ( + ( * o4 ( - 1 c34 ) ) ( * c34 o3 ) ) ( - 1 c23 ) ) ( * c23 ( + ( * o4 ( - 1 c24 ) ) ( * c24 o2 ) ) ) ) ( - 1 c12 ) ) ( * c12 ( + ( * ( + ( * o4 ( - 1 c34 ) ) ( * c34 o3 ) ) ( - 1 c13 ) ) ( * c13 ( + ( * o4 ( - 1 c14 ) ) ( * c14 o1 ) ) ) ) ) ) )</t>
+          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c23 1) (Vec (- 1 c23) c12 (* 1 (+ (* o4 (- 1 c24)) (* c24 o2))) 0)) (&lt;&lt; (VecMul (Vec (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c23 1) (Vec (- 1 c23) c12 (* 1 (+ (* o4 (- 1 c24)) (* c24 o2))) 0)) 2)) (VecAdd (VecMul (Vec 1 (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c13) (VecMinus (Vec 1 1 0 (+ (* o4 (- 1 c14)) (* c14 o1))) (Vec c12 c13 0 0))) (&lt;&lt; (VecMul (Vec 1 (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c13) (VecMinus (Vec 1 1 0 (+ (* o4 (- 1 c14)) (* c14 o1))) (Vec c12 c13 0 0))) 2))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c23 1) (Vec (- 1 c23) c12 (* 1 (+ (* o4 (- 1 c24)) (* c24 o2))) 0)) (&lt;&lt; (VecMul (Vec (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c23 1) (Vec (- 1 c23) c12 (* 1 (+ (* o4 (- 1 c24)) (* c24 o2))) 0)) 2)) (VecAdd (VecMul (Vec 1 (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c13) (VecMinus (Vec 1 1 0 (+ (* o4 (- 1 c14)) (* c14 o1))) (Vec c12 c13 0 0))) (&lt;&lt; (VecMul (Vec 1 (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c13) (VecMinus (Vec 1 1 0 (+ (* o4 (- 1 c14)) (* c14 o1))) (Vec c12 c13 0 0))) 2))) 1))</t>
         </is>
       </c>
       <c r="E41" t="n">
         <v>7012</v>
       </c>
       <c r="F41" t="n">
-        <v>7012</v>
+        <v>4979</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>28.99</v>
       </c>
       <c r="H41" t="n">
         <v>110.93</v>
       </c>
       <c r="I41" t="n">
-        <v>110.93</v>
+        <v>147.91</v>
       </c>
       <c r="J41" t="b">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>129.07</v>
+        <v>92.09</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42">
@@ -2185,29 +2185,29 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) (- 1 c13)) (* c13 (+ (* o2134 (- 1 c24)) (* c24 (+ (* (- 1 c14) (+ (* o4213 (- 1 c24)) (* c24 o2413))) (* c14 (+ (* o2143 (- 1 c34)) (* c34 o2134)))))))) 0)) (&lt;&lt; (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) (- 1 c13)) (* c13 (+ (* o2134 (- 1 c24)) (* c24 (+ (* (- 1 c14) (+ (* o4213 (- 1 c24)) (* c24 o2413))) (* c14 (+ (* o2143 (- 1 c34)) (* c34 o2134)))))))) 0)) 2)) (VecAdd (VecMul (Vec 1 (- 1 c13) 1 c13) (VecAdd (VecMul (Vec 1 o3124 1 (- 1 c23)) (VecMinus (Vec 0 1 (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))) (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324))))))) (VecMinus (VecMinus (VecMinus (Vec 0 c34 0 0) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)))))))))))))) (VecMul (Vec 1 c34 1 c23) (VecAdd (VecMul (Vec 1 (- 1 c14) 1 o1234) (VecMinus (Vec 0 (+ (* o4312 (- 1 c34)) (* c34 o3412)) 0 1) (Vec 0 0 0 c14))) (VecMul (Vec 1 c14 1 c14) (VecAdd (VecMul (Vec 1 o3142 1 (- 1 c24)) (Vec 0 (- 1 c24) 0 (+ (* o4123 (- 1 c14)) (* c14 o1423)))) (VecMul (Vec 1 c24 1 c24) (Vec (- 1 c12) o3124 0 (+ (* o1243 (- 1 c34)) (* c34 o1234)))))))))) (&lt;&lt; (VecMul (Vec 1 (- 1 c13) 1 c13) (VecAdd (VecMul (Vec 1 o3124 1 (- 1 c23)) (VecMinus (Vec 0 1 (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))) (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324))))))) (VecMinus (VecMinus (VecMinus (Vec 0 c34 0 0) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)))))))))))))) (VecMul (Vec 1 c34 1 c23) (VecAdd (VecMul (Vec 1 (- 1 c14) 1 o1234) (VecMinus (Vec 0 (+ (* o4312 (- 1 c34)) (* c34 o3412)) 0 1) (Vec 0 0 0 c14))) (VecMul (Vec 1 c14 1 c14) (VecAdd (VecMul (Vec 1 o3142 1 (- 1 c24)) (Vec 0 (- 1 c24) 0 (+ (* o4123 (- 1 c14)) (* c14 o1423)))) (VecMul (Vec 1 c24 1 c24) (Vec (- 1 c12) o3124 0 (+ (* o1243 (- 1 c34)) (* c34 o1234)))))))))) 2))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) (- 1 c13)) (* c13 (+ (* o2134 (- 1 c24)) (* c24 (+ (* (- 1 c14) (+ (* o4213 (- 1 c24)) (* c24 o2413))) (* c14 (+ (* o2143 (- 1 c34)) (* c34 o2134)))))))) 0)) (&lt;&lt; (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) (- 1 c13)) (* c13 (+ (* o2134 (- 1 c24)) (* c24 (+ (* (- 1 c14) (+ (* o4213 (- 1 c24)) (* c24 o2413))) (* c14 (+ (* o2143 (- 1 c34)) (* c34 o2134)))))))) 0)) 2)) (VecAdd (VecMul (Vec 1 (- 1 c13) 1 c13) (VecAdd (VecMul (Vec 1 o3124 1 (- 1 c23)) (VecMinus (Vec 0 1 (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))) (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324))))))) (VecMinus (VecMinus (VecMinus (Vec 0 c34 0 0) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)))))))))))))) (VecMul (Vec 1 c34 1 c23) (VecAdd (VecMul (Vec 1 (- 1 c14) 1 o1234) (VecMinus (Vec 0 (+ (* o4312 (- 1 c34)) (* c34 o3412)) 0 1) (Vec 0 0 0 c14))) (VecMul (Vec 1 c14 1 c14) (VecAdd (VecMul (Vec 1 o3142 1 (- 1 c24)) (Vec 0 (- 1 c24) 0 (+ (* o4123 (- 1 c14)) (* c14 o1423)))) (VecMul (Vec 1 c24 1 c24) (Vec (- 1 c12) o3124 0 (+ (* o1243 (- 1 c34)) (* c34 o1234)))))))))) (&lt;&lt; (VecMul (Vec 1 (- 1 c13) 1 c13) (VecAdd (VecMul (Vec 1 o3124 1 (- 1 c23)) (VecMinus (Vec 0 1 (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))) (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324))))))) (VecMinus (VecMinus (VecMinus (Vec 0 c34 0 0) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)))))))))))))) (VecMul (Vec 1 c34 1 c23) (VecAdd (VecMul (Vec 1 (- 1 c14) 1 o1234) (VecMinus (Vec 0 (+ (* o4312 (- 1 c34)) (* c34 o3412)) 0 1) (Vec 0 0 0 c14))) (VecMul (Vec 1 c14 1 c14) (VecAdd (VecMul (Vec 1 o3142 1 (- 1 c24)) (Vec 0 (- 1 c24) 0 (+ (* o4123 (- 1 c14)) (* c14 o1423)))) (VecMul (Vec 1 c24 1 c24) (Vec (- 1 c12) o3124 0 (+ (* o1243 (- 1 c34)) (* c34 o1234)))))))))) 2))) 1))</t>
+          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4231 (- 1 c24)) (* c24 o2431)))))))))) (* c34 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o2341 (- 1 c14)) (* c14 o2314))))))))))))) (- 1 c13)) (* c13 (+ (* o2134 (- 1 c24)) (* c24 (+ (* (- 1 c14) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4213 (- 1 c24)) (* c24 o2413)))))))))) (* c14 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o2143 (- 1 c34)) (* c34 o2134)))))))))))))) 0)) (&lt;&lt; (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4231 (- 1 c24)) (* c24 o2431)))))))))) (* c34 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o2341 (- 1 c14)) (* c14 o2314))))))))))))) (- 1 c13)) (* c13 (+ (* o2134 (- 1 c24)) (* c24 (+ (* (- 1 c14) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4213 (- 1 c24)) (* c24 o2413)))))))))) (* c14 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o2143 (- 1 c34)) (* c34 o2134)))))))))))))) 0)) 2)) (VecAdd (VecMul (Vec 1 (- 1 c13) 1 c13) (VecAdd (VecMul (Vec 1 o3124 1 (- 1 c23)) (Vec 0 (- 1 c34) 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4132 (- 1 c14)) (* c14 o1432))))))))) (* c34 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))))))))) (VecMul (Vec 1 c34 1 c23) (VecAdd (VecMul (Vec 1 (- 1 c14) 1 o1234) (Vec 0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4312 (- 1 c34)) (* c34 o3412)))))))))) 0 (- 1 c14))) (VecMul (Vec 1 c14 1 c14) (VecAdd (VecMul (Vec 1 o3142 1 (- 1 c24)) (Vec 0 (- 1 c24) 0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4123 (- 1 c14)) (* c14 o1423)))))))))) (VecMul (Vec 1 c24 1 c24) (Vec (- 1 c12) o3124 0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o1243 (- 1 c34)) (* c34 o1234)))))))))))))))) (&lt;&lt; (VecMul (Vec 1 (- 1 c13) 1 c13) (VecAdd (VecMul (Vec 1 o3124 1 (- 1 c23)) (Vec 0 (- 1 c34) 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4132 (- 1 c14)) (* c14 o1432))))))))) (* c34 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))))))))) (VecMul (Vec 1 c34 1 c23) (VecAdd (VecMul (Vec 1 (- 1 c14) 1 o1234) (Vec 0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4312 (- 1 c34)) (* c34 o3412)))))))))) 0 (- 1 c14))) (VecMul (Vec 1 c14 1 c14) (VecAdd (VecMul (Vec 1 o3142 1 (- 1 c24)) (Vec 0 (- 1 c24) 0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4123 (- 1 c14)) (* c14 o1423)))))))))) (VecMul (Vec 1 c24 1 c24) (Vec (- 1 c12) o3124 0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o1243 (- 1 c34)) (* c34 o1234)))))))))))))))) 2))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4231 (- 1 c24)) (* c24 o2431)))))))))) (* c34 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o2341 (- 1 c14)) (* c14 o2314))))))))))))) (- 1 c13)) (* c13 (+ (* o2134 (- 1 c24)) (* c24 (+ (* (- 1 c14) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4213 (- 1 c24)) (* c24 o2413)))))))))) (* c14 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o2143 (- 1 c34)) (* c34 o2134)))))))))))))) 0)) (&lt;&lt; (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4231 (- 1 c24)) (* c24 o2431)))))))))) (* c34 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o2341 (- 1 c14)) (* c14 o2314))))))))))))) (- 1 c13)) (* c13 (+ (* o2134 (- 1 c24)) (* c24 (+ (* (- 1 c14) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4213 (- 1 c24)) (* c24 o2413)))))))))) (* c14 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o2143 (- 1 c34)) (* c34 o2134)))))))))))))) 0)) 2)) (VecAdd (VecMul (Vec 1 (- 1 c13) 1 c13) (VecAdd (VecMul (Vec 1 o3124 1 (- 1 c23)) (Vec 0 (- 1 c34) 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4132 (- 1 c14)) (* c14 o1432))))))))) (* c34 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))))))))) (VecMul (Vec 1 c34 1 c23) (VecAdd (VecMul (Vec 1 (- 1 c14) 1 o1234) (Vec 0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4312 (- 1 c34)) (* c34 o3412)))))))))) 0 (- 1 c14))) (VecMul (Vec 1 c14 1 c14) (VecAdd (VecMul (Vec 1 o3142 1 (- 1 c24)) (Vec 0 (- 1 c24) 0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4123 (- 1 c14)) (* c14 o1423)))))))))) (VecMul (Vec 1 c24 1 c24) (Vec (- 1 c12) o3124 0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o1243 (- 1 c34)) (* c34 o1234)))))))))))))))) (&lt;&lt; (VecMul (Vec 1 (- 1 c13) 1 c13) (VecAdd (VecMul (Vec 1 o3124 1 (- 1 c23)) (Vec 0 (- 1 c34) 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4132 (- 1 c14)) (* c14 o1432))))))))) (* c34 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))))))))) (VecMul (Vec 1 c34 1 c23) (VecAdd (VecMul (Vec 1 (- 1 c14) 1 o1234) (Vec 0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4312 (- 1 c34)) (* c34 o3412)))))))))) 0 (- 1 c14))) (VecMul (Vec 1 c14 1 c14) (VecAdd (VecMul (Vec 1 o3142 1 (- 1 c24)) (Vec 0 (- 1 c24) 0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4123 (- 1 c14)) (* c14 o1423)))))))))) (VecMul (Vec 1 c24 1 c24) (Vec (- 1 c12) o3124 0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o1243 (- 1 c34)) (* c34 o1234)))))))))))))))) 2))) 1))</t>
         </is>
       </c>
       <c r="E42" t="n">
         <v>29021</v>
       </c>
       <c r="F42" t="n">
-        <v>24608</v>
+        <v>38102</v>
       </c>
       <c r="G42" t="n">
-        <v>15.21</v>
+        <v>-31.29</v>
       </c>
       <c r="H42" t="n">
         <v>218.27</v>
       </c>
       <c r="I42" t="n">
-        <v>226.65</v>
+        <v>462.73</v>
       </c>
       <c r="J42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>13.35</v>
+        <v>-222.73</v>
       </c>
       <c r="L42" t="n">
         <v>75</v>
@@ -2227,29 +2227,29 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>(VecMul (VecAdd (VecAdd (Vec 0 x10121 0 x10181) (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) x10125 1 1) (Vec (* x10117 x10119) (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))) (- (- (- (- 0 (- (- (- (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))) (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0)))) (- (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))) (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))))) (- (- (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))) (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0)))) (- (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))) (- (- (- 0 0) (- 0 0)) (- (- 0 0) 0)))))) 0) (- 0 0)) (- (- 0 0) (- 0 0))) x10183))) (&lt;&lt; (VecAdd (Vec 0 x10121 0 x10181) (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) x10125 1 1) (Vec (* x10117 x10119) (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))) (- (- (- (- 0 (- (- (- (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))) (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0)))) (- (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))) (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))))) (- (- (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))) (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0)))) (- (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))) (- (- (- 0 0) (- 0 0)) (- (- 0 0) 0)))))) 0) (- 0 0)) (- (- 0 0) (- 0 0))) x10183))) 2)) (&lt;&lt; (VecAdd (VecAdd (Vec 0 x10121 0 x10181) (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) x10125 1 1) (Vec (* x10117 x10119) (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))) (- (- (- (- 0 (- (- (- (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))) (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0)))) (- (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))) (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))))) (- (- (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))) (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0)))) (- (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))) (- (- (- 0 0) (- 0 0)) (- (- 0 0) 0)))))) 0) (- 0 0)) (- (- 0 0) (- 0 0))) x10183))) (&lt;&lt; (VecAdd (Vec 0 x10121 0 x10181) (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) x10125 1 1) (Vec (* x10117 x10119) (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))) (- (- (- (- 0 (- (- (- (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))) (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0)))) (- (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))) (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))))) (- (- (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))) (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0)))) (- (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))) (- (- (- 0 0) (- 0 0)) (- (- 0 0) 0)))))) 0) (- 0 0)) (- (- 0 0) (- 0 0))) x10183))) 2)) 1))</t>
+          <t>(VecMul (VecAdd (VecAdd (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) 1 1 1 1 x10125 1 1) (Vec (* x10117 x10119) x10121 0 (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- x10181 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ 0 0)) (+ (+ 0 0) (+ 0 0))) (+ (+ (+ 0 0) (+ 0 0)) (+ 0 0))) 0) 0) 0) 0) 0) 0) 0) 0) 0 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))) 0 x10183)) (&lt;&lt; (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) 1 1 1 1 x10125 1 1) (Vec (* x10117 x10119) x10121 0 (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- x10181 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ 0 0)) (+ (+ 0 0) (+ 0 0))) (+ (+ (+ 0 0) (+ 0 0)) (+ 0 0))) 0) 0) 0) 0) 0) 0) 0) 0) 0 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))) 0 x10183)) 4)) (&lt;&lt; (VecAdd (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) 1 1 1 1 x10125 1 1) (Vec (* x10117 x10119) x10121 0 (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- x10181 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ 0 0)) (+ (+ 0 0) (+ 0 0))) (+ (+ (+ 0 0) (+ 0 0)) (+ 0 0))) 0) 0) 0) 0) 0) 0) 0) 0) 0 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))) 0 x10183)) (&lt;&lt; (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) 1 1 1 1 x10125 1 1) (Vec (* x10117 x10119) x10121 0 (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- x10181 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ 0 0)) (+ (+ 0 0) (+ 0 0))) (+ (+ (+ 0 0) (+ 0 0)) (+ 0 0))) 0) 0) 0) 0) 0) 0) 0) 0) 0 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))) 0 x10183)) 4)) 2)) (&lt;&lt; (VecAdd (VecAdd (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) 1 1 1 1 x10125 1 1) (Vec (* x10117 x10119) x10121 0 (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- x10181 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ 0 0)) (+ (+ 0 0) (+ 0 0))) (+ (+ (+ 0 0) (+ 0 0)) (+ 0 0))) 0) 0) 0) 0) 0) 0) 0) 0) 0 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))) 0 x10183)) (&lt;&lt; (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) 1 1 1 1 x10125 1 1) (Vec (* x10117 x10119) x10121 0 (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- x10181 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ 0 0)) (+ (+ 0 0) (+ 0 0))) (+ (+ (+ 0 0) (+ 0 0)) (+ 0 0))) 0) 0) 0) 0) 0) 0) 0) 0) 0 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))) 0 x10183)) 4)) (&lt;&lt; (VecAdd (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) 1 1 1 1 x10125 1 1) (Vec (* x10117 x10119) x10121 0 (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- x10181 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ 0 0)) (+ (+ 0 0) (+ 0 0))) (+ (+ (+ 0 0) (+ 0 0)) (+ 0 0))) 0) 0) 0) 0) 0) 0) 0) 0) 0 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))) 0 x10183)) (&lt;&lt; (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) 1 1 1 1 x10125 1 1) (Vec (* x10117 x10119) x10121 0 (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- x10181 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) (+ 0 0)) (+ (+ 0 0) (+ 0 0))) (+ (+ (+ 0 0) (+ 0 0)) (+ 0 0))) 0) 0) 0) 0) 0) 0) 0) 0) 0 (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))) 0 x10183)) 4)) 2)) 1))</t>
         </is>
       </c>
       <c r="E43" t="n">
         <v>8018</v>
       </c>
       <c r="F43" t="n">
-        <v>24330</v>
+        <v>24448</v>
       </c>
       <c r="G43" t="n">
-        <v>-203.44</v>
+        <v>-204.91</v>
       </c>
       <c r="H43" t="n">
         <v>182.49</v>
       </c>
       <c r="I43" t="n">
-        <v>188.48</v>
+        <v>250.77</v>
       </c>
       <c r="J43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>51.52</v>
+        <v>-10.77</v>
       </c>
       <c r="L43" t="n">
         <v>75</v>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>(VecMul (VecAdd (VecMul (VecMul (VecMul (Vec x9604 x9634) (Vec x9605 x9635)) (Vec x9607 x9637)) (VecMul (Vec x9608 x9638) (VecMul (VecMul (Vec x9611 x9641) (Vec x9612 x9642)) (VecMul (Vec x9614 x9644) (Vec x9615 x9645))))) (VecMul (VecMul (VecMul (Vec x9619 x9649) (Vec x9620 x9650)) (Vec x9622 x9652)) (VecMul (Vec x9623 x9653) (VecMul (VecMul (Vec x9626 x9656) (Vec x9627 x9657)) (VecMul (Vec x9629 x9659) (Vec x9630 x9660)))))) (&lt;&lt; (VecAdd (VecMul (VecMul (VecMul (Vec x9604 x9634) (Vec x9605 x9635)) (Vec x9607 x9637)) (VecMul (Vec x9608 x9638) (VecMul (VecMul (Vec x9611 x9641) (Vec x9612 x9642)) (VecMul (Vec x9614 x9644) (Vec x9615 x9645))))) (VecMul (VecMul (VecMul (Vec x9619 x9649) (Vec x9620 x9650)) (Vec x9622 x9652)) (VecMul (Vec x9623 x9653) (VecMul (VecMul (Vec x9626 x9656) (Vec x9627 x9657)) (VecMul (Vec x9629 x9659) (Vec x9630 x9660)))))) 1))</t>
+          <t>(VecMul (VecAdd (VecMul (VecMul (VecMul (VecMul (Vec x9604 x9634) (Vec x9605 x9635)) (VecMul (Vec x9607 x9637) (Vec x9608 x9638))) (Vec x9611 x9641)) (VecMul (Vec x9612 x9642) (VecMul (Vec x9614 x9644) (Vec x9615 x9645)))) (VecMul (VecMul (VecMul (VecMul (Vec x9619 x9649) (Vec x9620 x9650)) (VecMul (Vec x9622 x9652) (Vec x9623 x9653))) (Vec x9626 x9656)) (VecMul (Vec x9627 x9657) (VecMul (Vec x9629 x9659) (Vec x9630 x9660))))) (&lt;&lt; (VecAdd (VecMul (VecMul (VecMul (VecMul (Vec x9604 x9634) (Vec x9605 x9635)) (VecMul (Vec x9607 x9637) (Vec x9608 x9638))) (Vec x9611 x9641)) (VecMul (Vec x9612 x9642) (VecMul (Vec x9614 x9644) (Vec x9615 x9645)))) (VecMul (VecMul (VecMul (VecMul (Vec x9619 x9649) (Vec x9620 x9650)) (VecMul (Vec x9622 x9652) (Vec x9623 x9653))) (Vec x9626 x9656)) (VecMul (Vec x9627 x9657) (VecMul (Vec x9629 x9659) (Vec x9630 x9660))))) 1))</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -2311,17 +2311,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (Vec in_1_1 (+ in_1_2 in_1_1) in_1_2 (+ in_2_1 in_2_0) (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_2_2 in_2_1) in_2_1 (+ in_2_2 in_2_1) in_2_2) (Vec in_1_0 (+ in_1_0 in_0_2) in_1_1 (+ in_1_1 in_1_0) (+ in_1_2 in_1_1) (+ in_1_2 in_1_1) in_2_0 (+ in_2_0 in_1_2) in_2_1)) (VecAdd (Vec in_0_1 in_0_1 in_0_2 in_0_1 (+ in_1_0 in_0_2) in_0_2 in_1_1 in_1_1 in_1_2) (Vec in_0_0 in_0_0 in_0_1 in_0_0 (+ in_0_1 in_0_0) in_0_1 in_1_0 in_1_0 in_1_1)))</t>
+          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 0 in_2_1 in_2_2 in_2_2 0 in_2_2 0) (Vec in_1_1 in_1_1 in_1_2 in_2_0 (+ in_2_1 in_2_0) in_2_1 in_2_1 in_2_1 in_2_2)) (VecAdd (Vec 0 in_1_0 0 in_1_1 in_1_2 in_1_2 0 in_2_0 0) (Vec in_1_0 in_0_2 in_1_1 in_1_0 in_1_1 in_1_1 in_2_0 in_1_2 in_2_1))) (VecAdd (Vec in_0_1 in_0_1 in_0_2 in_0_1 (+ in_1_0 in_0_2) in_0_2 in_1_1 in_1_1 in_1_2) (Vec in_0_0 in_0_0 in_0_1 in_0_0 (+ in_0_1 in_0_0) in_0_1 in_1_0 in_1_0 in_1_1)))</t>
         </is>
       </c>
       <c r="E45" t="n">
         <v>10006</v>
       </c>
       <c r="F45" t="n">
-        <v>3259</v>
+        <v>761</v>
       </c>
       <c r="G45" t="n">
-        <v>67.43000000000001</v>
+        <v>92.39</v>
       </c>
       <c r="H45" t="n">
         <v>7.19</v>
@@ -2336,7 +2336,7 @@
         <v>292.81</v>
       </c>
       <c r="L45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
@@ -2353,17 +2353,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_2 in_3_3 in_3_4 in_3_4 in_4_1 in_4_2 in_4_3 in_4_4 in_4_4 0 in_4_2 in_4_3 in_4_4 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_1_4 in_2_0 (+ in_2_1 in_2_0) (+ in_2_2 in_2_1) (+ in_2_3 in_2_2) in_2_3 in_3_0 (+ in_3_1 in_3_0) (+ in_3_2 in_3_1) (+ in_3_3 in_3_2) in_3_3 in_4_0 (+ in_4_1 in_4_0) (+ in_4_2 in_4_1) (+ in_4_3 in_4_2) in_4_3 in_4_1 in_4_1 in_4_2 in_4_3 in_4_4)) (Vec in_1_0 (+ in_1_0 in_0_2) (+ in_1_1 in_0_3) (+ in_1_2 in_0_4) in_1_3 (+ in_1_1 in_1_0) (+ in_1_2 in_1_1) (+ in_1_3 in_1_2) (+ in_1_4 in_1_3) (+ in_1_4 in_1_3) (+ in_2_1 in_2_0) (+ in_2_2 in_2_1) (+ in_2_3 in_2_2) (+ in_2_4 in_2_3) (+ in_2_4 in_2_3) (+ in_3_1 in_3_0) (+ in_3_2 in_3_1) (+ in_3_3 in_3_2) (+ in_3_4 in_3_3) (+ in_3_4 in_3_3) in_4_0 (+ in_4_0 in_3_2) (+ in_4_1 in_3_3) (+ in_4_2 in_3_4) in_4_3)) (VecAdd (Vec in_0_1 in_0_1 in_0_2 in_0_3 in_0_4 in_0_1 (+ in_1_0 in_0_2) (+ in_1_1 in_0_3) (+ in_1_2 in_0_4) in_0_4 in_1_1 (+ in_2_0 in_1_2) (+ in_2_1 in_1_3) (+ in_2_2 in_1_4) in_1_4 in_2_1 (+ in_3_0 in_2_2) (+ in_3_1 in_2_3) (+ in_3_2 in_2_4) in_2_4 in_3_1 in_3_1 in_3_2 in_3_3 in_3_4) (VecAdd (Vec 0 0 0 0 0 0 in_0_1 in_0_2 in_0_3 0 0 in_1_1 in_1_2 in_1_3 0 0 in_2_1 in_2_2 in_2_3 0 0 0 0 0 0) (Vec in_0_0 in_0_0 in_0_1 in_0_2 in_0_3 in_0_0 in_0_0 in_0_1 in_0_2 in_0_3 in_1_0 in_1_0 in_1_1 in_1_2 in_1_3 in_2_0 in_2_0 in_2_1 in_2_2 in_2_3 in_3_0 in_3_0 in_3_1 in_3_2 in_3_3))))</t>
+          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_2 in_3_3 in_3_4 in_3_4 in_4_1 in_4_2 in_4_3 in_4_4 in_4_4 0 in_4_2 in_4_3 in_4_4 0) (VecAdd (Vec 0 0 0 0 0 0 in_2_1 in_2_2 in_2_3 0 0 in_3_1 in_3_2 in_3_3 0 0 in_4_1 in_4_2 in_4_3 0 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_1_4 in_2_0 in_2_0 in_2_1 in_2_2 in_2_3 in_3_0 in_3_0 in_3_1 in_3_2 in_3_3 in_4_0 in_4_0 in_4_1 in_4_2 in_4_3 in_4_1 in_4_1 in_4_2 in_4_3 in_4_4))) (VecAdd (Vec 0 in_1_0 in_1_1 in_1_2 0 in_1_1 in_1_2 in_1_3 in_1_4 in_1_4 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_2 in_3_3 in_3_4 in_3_4 0 in_4_0 in_4_1 in_4_2 0) (Vec in_1_0 in_0_2 in_0_3 in_0_4 in_1_3 in_1_0 in_1_1 in_1_2 in_1_3 in_1_3 in_2_0 in_2_1 in_2_2 in_2_3 in_2_3 in_3_0 in_3_1 in_3_2 in_3_3 in_3_3 in_4_0 in_3_2 in_3_3 in_3_4 in_4_3))) (VecAdd (VecAdd (Vec 0 0 0 0 0 0 in_1_0 in_1_1 in_1_2 0 0 in_2_0 in_2_1 in_2_2 0 0 in_3_0 in_3_1 in_3_2 0 0 0 0 0 0) (Vec in_0_1 in_0_1 in_0_2 in_0_3 in_0_4 in_0_1 in_0_2 in_0_3 in_0_4 in_0_4 in_1_1 in_1_2 in_1_3 in_1_4 in_1_4 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_1 in_3_2 in_3_3 in_3_4)) (VecAdd (Vec 0 0 0 0 0 0 in_0_1 in_0_2 in_0_3 0 0 in_1_1 in_1_2 in_1_3 0 0 in_2_1 in_2_2 in_2_3 0 0 0 0 0 0) (Vec in_0_0 in_0_0 in_0_1 in_0_2 in_0_3 in_0_0 in_0_0 in_0_1 in_0_2 in_0_3 in_1_0 in_1_0 in_1_1 in_1_2 in_1_3 in_2_0 in_2_0 in_2_1 in_2_2 in_2_3 in_3_0 in_3_0 in_3_1 in_3_2 in_3_3))))</t>
         </is>
       </c>
       <c r="E46" t="n">
         <v>36006</v>
       </c>
       <c r="F46" t="n">
-        <v>9761</v>
+        <v>14</v>
       </c>
       <c r="G46" t="n">
-        <v>72.89</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="H46" t="n">
         <v>7.19</v>
@@ -2378,7 +2378,7 @@
         <v>292.81</v>
       </c>
       <c r="L46" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
@@ -2395,17 +2395,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3 v2_4 v2_5 v2_6 v2_7) (VecAdd (Vec 2 2 2 2 2 2 2 2) (Vec (* v1_0 5) (* v1_1 5) (* v1_2 5) (* v1_3 5) (* v1_4 5) (* v1_5 5) (* v1_6 5) (* v1_7 5))))</t>
+          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3 v2_4 v2_5 v2_6 v2_7) (VecAdd (Vec 2 2 2 2 2 2 2 2) (VecMul (Vec v1_0 v1_1 v1_2 v1_3 v1_4 v1_5 v1_6 v1_7) (Vec 5 5 5 5 5 5 5 5))))</t>
         </is>
       </c>
       <c r="E47" t="n">
         <v>6006</v>
       </c>
       <c r="F47" t="n">
-        <v>2008</v>
+        <v>108</v>
       </c>
       <c r="G47" t="n">
-        <v>66.56999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="H47" t="n">
         <v>39.37</v>
@@ -2420,7 +2420,7 @@
         <v>260.63</v>
       </c>
       <c r="L47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -2479,32 +2479,32 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( - ( + v1_0 v2_0 ) ( * ( * v1_0 v2_0 ) 2 ) ) ( - ( + v1_1 v2_1 ) ( * 2 ( * v1_1 v2_1 ) ) ) ) ( + ( - ( + v1_2 v2_2 ) ( * 2 ( * v1_2 v2_2 ) ) ) ( - ( + v1_3 v2_3 ) ( * 2 ( * v1_3 v2_3 ) ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2) (Vec v2_0 v2_2)) (VecMul (VecMul (Vec v1_0 2 v2_0 1) (&lt;&lt; (Vec v1_0 2 v2_0 1) 2)) (VecMul (Vec 2 v1_2 1 v2_2) (&lt;&lt; (Vec 2 v1_2 1 v2_2) 2)))) (VecMinus (VecAdd (Vec v1_1 v1_3) (Vec v2_1 v2_3)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_3) (Vec v2_1 v2_3))))) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2) (Vec v2_0 v2_2)) (VecMul (VecMul (Vec v1_0 2 v2_0 1) (&lt;&lt; (Vec v1_0 2 v2_0 1) 2)) (VecMul (Vec 2 v1_2 1 v2_2) (&lt;&lt; (Vec 2 v1_2 1 v2_2) 2)))) (VecMinus (VecAdd (Vec v1_1 v1_3) (Vec v2_1 v2_3)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_3) (Vec v2_1 v2_3))))) 1))</t>
         </is>
       </c>
       <c r="E49" t="n">
         <v>4759</v>
       </c>
       <c r="F49" t="n">
-        <v>4759</v>
+        <v>676</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>85.8</v>
       </c>
       <c r="H49" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>75.15000000000001</v>
+        <v>77.55</v>
       </c>
       <c r="J49" t="b">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>224.85</v>
+        <v>222.45</v>
       </c>
       <c r="L49" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50">
@@ -2521,17 +2521,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (Vec (* v1_0 v2_0) 2) (Vec 2 (* v1_4 v2_4)))) (VecMinus (VecAdd (Vec v1_1 v1_5) (Vec v2_1 v2_5)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_5) (Vec v2_1 v2_5))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_6) (Vec v2_2 v2_6)))) (VecMinus (VecAdd (Vec v1_3 v1_7) (Vec v2_3 v2_7)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_7) (Vec v2_3 v2_7))))) (&lt;&lt; (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (Vec (* v1_0 v2_0) 2) (Vec 2 (* v1_4 v2_4)))) (VecMinus (VecAdd (Vec v1_1 v1_5) (Vec v2_1 v2_5)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_5) (Vec v2_1 v2_5))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_6) (Vec v2_2 v2_6)))) (VecMinus (VecAdd (Vec v1_3 v1_7) (Vec v2_3 v2_7)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_7) (Vec v2_3 v2_7)))))) 1)))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (VecMul (Vec v1_0 2 v2_0 1) (&lt;&lt; (Vec v1_0 2 v2_0 1) 2)) (VecMul (Vec 2 v1_4 1 v2_4) (&lt;&lt; (Vec 2 v1_4 1 v2_4) 2)))) (VecMinus (VecAdd (Vec v1_1 v1_5) (Vec v2_1 v2_5)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_5) (Vec v2_1 v2_5))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_6) (Vec v2_2 v2_6)))) (VecMinus (VecAdd (Vec v1_3 v1_7) (Vec v2_3 v2_7)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_7) (Vec v2_3 v2_7)))))) (&lt;&lt; (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (VecMul (Vec v1_0 2 v2_0 1) (&lt;&lt; (Vec v1_0 2 v2_0 1) 2)) (VecMul (Vec 2 v1_4 1 v2_4) (&lt;&lt; (Vec 2 v1_4 1 v2_4) 2)))) (VecMinus (VecAdd (Vec v1_1 v1_5) (Vec v2_1 v2_5)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_5) (Vec v2_1 v2_5))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_6) (Vec v2_2 v2_6)))) (VecMinus (VecAdd (Vec v1_3 v1_7) (Vec v2_3 v2_7)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_7) (Vec v2_3 v2_7)))))) 1))</t>
         </is>
       </c>
       <c r="E50" t="n">
         <v>9760</v>
       </c>
       <c r="F50" t="n">
-        <v>1275</v>
+        <v>1083</v>
       </c>
       <c r="G50" t="n">
-        <v>86.94</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H50" t="n">
         <v>76.34999999999999</v>
@@ -2546,7 +2546,7 @@
         <v>221.25</v>
       </c>
       <c r="L50" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51">
@@ -2563,17 +2563,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec (* v1_0 v2_0) 2) (Vec 2 (* v1_16 v2_16)))) (VecMinus (VecAdd (Vec v1_1 v1_17) (Vec v2_1 v2_17)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_17) (Vec v2_1 v2_17))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_18) (Vec v2_2 v2_18)))) (VecMinus (VecAdd (Vec v1_3 v1_19) (Vec v2_3 v2_19)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_19) (Vec v2_3 v2_19)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (Vec 2 2) (VecMul (Vec v1_4 v1_20) (Vec v2_4 v2_20)))) (VecMinus (VecAdd (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecMul (Vec 2 2) (VecMul (Vec v1_5 v1_21) (Vec v2_5 v2_21))))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (Vec 2 2) (VecMul (Vec v1_6 v1_22) (Vec v2_6 v2_22)))) (VecMinus (VecAdd (Vec v1_7 v1_23) (Vec v2_7 v2_23)) (VecMul (Vec 2 2) (VecMul (Vec v1_7 v1_23) (Vec v2_7 v2_23))))))) (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (Vec 2 2) (VecMul (Vec v1_8 v1_24) (Vec v2_8 v2_24)))) (VecMinus (VecAdd (Vec v1_9 v1_25) (Vec v2_9 v2_25)) (VecMul (Vec 2 2) (VecMul (Vec v1_9 v1_25) (Vec v2_9 v2_25))))) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (Vec 2 2) (VecMul (Vec v1_10 v1_26) (Vec v2_10 v2_26)))) (VecMinus (VecAdd (Vec v1_11 v1_27) (Vec v2_11 v2_27)) (VecMul (Vec 2 2) (VecMul (Vec v1_11 v1_27) (Vec v2_11 v2_27)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec 2 2) (VecMul (Vec v1_12 v1_28) (Vec v2_12 v2_28)))) (VecMinus (VecAdd (Vec v1_13 v1_29) (Vec v2_13 v2_29)) (VecMul (Vec 2 2) (Vec (* v1_13 v2_13) (* v1_29 v2_29))))) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (Vec (* 2 (* v1_14 v2_14)) (* 2 (* v1_30 v2_30)))) (VecMinus (VecAdd (Vec v1_15 v1_31) (Vec v2_15 v2_31)) (Vec (* 2 (* v1_15 v2_15)) (* 2 (* v1_31 v2_31)))))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec (* v1_0 v2_0) 2) (Vec 2 (* v1_16 v2_16)))) (VecMinus (VecAdd (Vec v1_1 v1_17) (Vec v2_1 v2_17)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_17) (Vec v2_1 v2_17))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_18) (Vec v2_2 v2_18)))) (VecMinus (VecAdd (Vec v1_3 v1_19) (Vec v2_3 v2_19)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_19) (Vec v2_3 v2_19)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (Vec 2 2) (VecMul (Vec v1_4 v1_20) (Vec v2_4 v2_20)))) (VecMinus (VecAdd (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecMul (Vec 2 2) (VecMul (Vec v1_5 v1_21) (Vec v2_5 v2_21))))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (Vec 2 2) (VecMul (Vec v1_6 v1_22) (Vec v2_6 v2_22)))) (VecMinus (VecAdd (Vec v1_7 v1_23) (Vec v2_7 v2_23)) (VecMul (Vec 2 2) (VecMul (Vec v1_7 v1_23) (Vec v2_7 v2_23))))))) (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (Vec 2 2) (VecMul (Vec v1_8 v1_24) (Vec v2_8 v2_24)))) (VecMinus (VecAdd (Vec v1_9 v1_25) (Vec v2_9 v2_25)) (VecMul (Vec 2 2) (VecMul (Vec v1_9 v1_25) (Vec v2_9 v2_25))))) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (Vec 2 2) (VecMul (Vec v1_10 v1_26) (Vec v2_10 v2_26)))) (VecMinus (VecAdd (Vec v1_11 v1_27) (Vec v2_11 v2_27)) (VecMul (Vec 2 2) (VecMul (Vec v1_11 v1_27) (Vec v2_11 v2_27)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec 2 2) (VecMul (Vec v1_12 v1_28) (Vec v2_12 v2_28)))) (VecMinus (VecAdd (Vec v1_13 v1_29) (Vec v2_13 v2_29)) (VecMul (Vec 2 2) (Vec (* v1_13 v2_13) (* v1_29 v2_29))))) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (Vec (* 2 (* v1_14 v2_14)) (* 2 (* v1_30 v2_30)))) (VecMinus (VecAdd (Vec v1_15 v1_31) (Vec v2_15 v2_31)) (Vec (* 2 (* v1_15 v2_15)) (* 2 (* v1_31 v2_31)))))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec (* v1_0 v2_0) 2) (Vec 2 (* v1_16 v2_16)))) (VecMinus (VecAdd (Vec v1_1 v1_17) (Vec v2_1 v2_17)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_17) (Vec v2_1 v2_17))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_18) (Vec v2_2 v2_18)))) (VecMinus (VecAdd (Vec v1_3 v1_19) (Vec v2_3 v2_19)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_19) (Vec v2_3 v2_19)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (Vec 2 2) (VecMul (Vec v1_4 v1_20) (Vec v2_4 v2_20)))) (VecMinus (VecAdd (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecMul (Vec 2 2) (VecMul (Vec v1_5 v1_21) (Vec v2_5 v2_21))))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (Vec 2 2) (VecMul (Vec v1_6 v1_22) (Vec v2_6 v2_22)))) (VecMinus (VecAdd (Vec v1_7 v1_23) (Vec v2_7 v2_23)) (VecMul (Vec 2 2) (VecMul (Vec v1_7 v1_23) (Vec v2_7 v2_23))))))) (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (Vec 2 2) (VecMul (Vec v1_8 v1_24) (Vec v2_8 v2_24)))) (VecMinus (VecAdd (Vec v1_9 v1_25) (Vec v2_9 v2_25)) (VecMul (Vec 2 2) (VecMul (Vec v1_9 v1_25) (Vec v2_9 v2_25))))) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (Vec 2 2) (VecMul (Vec v1_10 v1_26) (Vec v2_10 v2_26)))) (VecMinus (VecAdd (Vec v1_11 v1_27) (Vec v2_11 v2_27)) (VecMul (Vec 2 2) (VecMul (Vec v1_11 v1_27) (Vec v2_11 v2_27)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec 2 2) (VecMul (Vec v1_12 v1_28) (Vec v2_12 v2_28)))) (VecMinus (VecAdd (Vec v1_13 v1_29) (Vec v2_13 v2_29)) (VecMul (Vec 2 2) (VecMul (Vec v1_13 v1_29) (Vec v2_13 v2_29))))) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (VecMul (Vec 2 2) (Vec (* v1_14 v2_14) (* v1_30 v2_30)))) (Vec (- (+ v1_15 v2_15) (* 2 (* v1_15 v2_15))) (- (+ v1_31 v2_31) (* 2 (* v1_31 v2_31)))))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec (* v1_0 v2_0) 2) (Vec 2 (* v1_16 v2_16)))) (VecMinus (VecAdd (Vec v1_1 v1_17) (Vec v2_1 v2_17)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_17) (Vec v2_1 v2_17))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_18) (Vec v2_2 v2_18)))) (VecMinus (VecAdd (Vec v1_3 v1_19) (Vec v2_3 v2_19)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_19) (Vec v2_3 v2_19)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (Vec 2 2) (VecMul (Vec v1_4 v1_20) (Vec v2_4 v2_20)))) (VecMinus (VecAdd (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecMul (Vec 2 2) (VecMul (Vec v1_5 v1_21) (Vec v2_5 v2_21))))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (Vec 2 2) (VecMul (Vec v1_6 v1_22) (Vec v2_6 v2_22)))) (VecMinus (VecAdd (Vec v1_7 v1_23) (Vec v2_7 v2_23)) (VecMul (Vec 2 2) (VecMul (Vec v1_7 v1_23) (Vec v2_7 v2_23))))))) (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (Vec 2 2) (VecMul (Vec v1_8 v1_24) (Vec v2_8 v2_24)))) (VecMinus (VecAdd (Vec v1_9 v1_25) (Vec v2_9 v2_25)) (VecMul (Vec 2 2) (VecMul (Vec v1_9 v1_25) (Vec v2_9 v2_25))))) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (Vec 2 2) (VecMul (Vec v1_10 v1_26) (Vec v2_10 v2_26)))) (VecMinus (VecAdd (Vec v1_11 v1_27) (Vec v2_11 v2_27)) (VecMul (Vec 2 2) (VecMul (Vec v1_11 v1_27) (Vec v2_11 v2_27)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec 2 2) (VecMul (Vec v1_12 v1_28) (Vec v2_12 v2_28)))) (VecMinus (VecAdd (Vec v1_13 v1_29) (Vec v2_13 v2_29)) (VecMul (Vec 2 2) (VecMul (Vec v1_13 v1_29) (Vec v2_13 v2_29))))) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (VecMul (Vec 2 2) (Vec (* v1_14 v2_14) (* v1_30 v2_30)))) (Vec (- (+ v1_15 v2_15) (* 2 (* v1_15 v2_15))) (- (+ v1_31 v2_31) (* 2 (* v1_31 v2_31)))))))) 1))</t>
         </is>
       </c>
       <c r="E51" t="n">
         <v>39762</v>
       </c>
       <c r="F51" t="n">
-        <v>5712</v>
+        <v>5910</v>
       </c>
       <c r="G51" t="n">
-        <v>85.63</v>
+        <v>85.14</v>
       </c>
       <c r="H51" t="n">
         <v>78.75</v>
@@ -2605,17 +2605,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>(VecAdd (Vec c1_0 c1_1 c1_2 c1_3 c1_4 c1_5 c1_6 c1_7) (VecAdd (Vec c2_0 c2_1 c2_2 c2_3 c2_4 c2_5 c2_6 c2_7) (VecMul (Vec c0_0 c0_1 c0_2 c0_3 c0_4 c0_5 c0_6 c0_7) (VecAdd (Vec c3_0 c3_1 c3_2 c3_3 c3_4 c3_5 c3_6 c3_7) (Vec (* c0_0 c4_0) (* c0_1 c4_1) (* c0_2 c4_2) (* c0_3 c4_3) (* c0_4 c4_4) (* c0_5 c4_5) (* c0_6 c4_6) (* c0_7 c4_7))))))</t>
+          <t>(VecAdd (Vec c1_0 c1_1 c1_2 c1_3 c1_4 c1_5 c1_6 c1_7) (VecAdd (Vec c2_0 c2_1 c2_2 c2_3 c2_4 c2_5 c2_6 c2_7) (VecMul (Vec c0_0 c0_1 c0_2 c0_3 c0_4 c0_5 c0_6 c0_7) (VecAdd (Vec c3_0 c3_1 c3_2 c3_3 c3_4 c3_5 c3_6 c3_7) (VecMul (Vec c0_0 c0_1 c0_2 c0_3 c0_4 c0_5 c0_6 c0_7) (Vec c4_0 c4_1 c4_2 c4_3 c4_4 c4_5 c4_6 c4_7))))))</t>
         </is>
       </c>
       <c r="E52" t="n">
         <v>10009</v>
       </c>
       <c r="F52" t="n">
-        <v>2112</v>
+        <v>212</v>
       </c>
       <c r="G52" t="n">
-        <v>78.90000000000001</v>
+        <v>97.88</v>
       </c>
       <c r="H52" t="n">
         <v>75.15000000000001</v>
@@ -2630,7 +2630,7 @@
         <v>224.85</v>
       </c>
       <c r="L52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( + ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ( * ( - c2_3 c1_3 ) ( - c2_3 c1_3 ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2) (Vec c1_0 c1_2)) (VecMinus (Vec c2_0 c2_2) (Vec c1_0 c1_2))) (VecMul (VecMinus (Vec c2_1 c2_3) (Vec c1_1 c1_3)) (VecMinus (Vec c2_1 c2_3) (Vec c1_1 c1_3)))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2) (Vec c1_0 c1_2)) (VecMinus (Vec c2_0 c2_2) (Vec c1_0 c1_2))) (VecMul (VecMinus (Vec c2_1 c2_3) (Vec c1_1 c1_3)) (VecMinus (Vec c2_1 c2_3) (Vec c1_1 c1_3)))) 1))</t>
         </is>
       </c>
       <c r="E54" t="n">
         <v>3757</v>
       </c>
       <c r="F54" t="n">
-        <v>3757</v>
+        <v>265</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>92.95</v>
       </c>
       <c r="H54" t="n">
         <v>40.57</v>
       </c>
       <c r="I54" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="J54" t="b">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>259.43</v>
+        <v>258.23</v>
       </c>
       <c r="L54" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55">
@@ -2731,32 +2731,32 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( + ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ( * ( - c2_3 c1_3 ) ( - c2_3 c1_3 ) ) ) ) ( + ( + ( * ( - c2_4 c1_4 ) ( - c2_4 c1_4 ) ) ( * ( - c2_5 c1_5 ) ( - c2_5 c1_5 ) ) ) ( + ( * ( - c2_6 c1_6 ) ( - c2_6 c1_6 ) ) ( * ( - c2_7 c1_7 ) ( - c2_7 c1_7 ) ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4) (Vec c1_0 c1_4)) (VecMinus (Vec c2_0 c2_4) (Vec c1_0 c1_4))) (VecMul (VecMinus (Vec c2_1 c2_5) (Vec c1_1 c1_5)) (VecMinus (Vec c2_1 c2_5) (Vec c1_1 c1_5)))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6) (Vec c1_2 c1_6)) (VecMinus (Vec c2_2 c2_6) (Vec c1_2 c1_6))) (VecMul (VecMinus (Vec c2_3 c2_7) (Vec c1_3 c1_7)) (VecMinus (Vec c2_3 c2_7) (Vec c1_3 c1_7))))) (&lt;&lt; (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4) (Vec c1_0 c1_4)) (VecMinus (Vec c2_0 c2_4) (Vec c1_0 c1_4))) (VecMul (VecMinus (Vec c2_1 c2_5) (Vec c1_1 c1_5)) (VecMinus (Vec c2_1 c2_5) (Vec c1_1 c1_5)))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6) (Vec c1_2 c1_6)) (VecMinus (Vec c2_2 c2_6) (Vec c1_2 c1_6))) (VecMul (VecMinus (Vec c2_3 c2_7) (Vec c1_3 c1_7)) (VecMinus (Vec c2_3 c2_7) (Vec c1_3 c1_7))))) 1))</t>
         </is>
       </c>
       <c r="E55" t="n">
         <v>7758</v>
       </c>
       <c r="F55" t="n">
-        <v>7758</v>
+        <v>472</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>93.92</v>
       </c>
       <c r="H55" t="n">
         <v>41.77</v>
       </c>
       <c r="I55" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="J55" t="b">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>258.23</v>
+        <v>257.03</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16) (Vec c1_0 c1_16)) (VecMinus (Vec c2_0 c2_16) (Vec c1_0 c1_16))) (VecMul (VecMinus (Vec c2_1 c2_17) (Vec c1_1 c1_17)) (VecMinus (Vec c2_1 c2_17) (Vec c1_1 c1_17)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18) (Vec c1_2 c1_18)) (VecMinus (Vec c2_2 c2_18) (Vec c1_2 c1_18))) (VecMul (VecMinus (Vec c2_3 c2_19) (Vec c1_3 c1_19)) (VecMinus (Vec c2_3 c2_19) (Vec c1_3 c1_19)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_20) (Vec c1_4 c1_20)) (VecMinus (Vec c2_4 c2_20) (Vec c1_4 c1_20))) (VecMul (VecMinus (Vec c2_5 c2_21) (Vec c1_5 c1_21)) (VecMinus (Vec c2_5 c2_21) (Vec c1_5 c1_21)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22) (Vec c1_6 c1_22)) (VecMinus (Vec c2_6 c2_22) (Vec c1_6 c1_22))) (VecMul (VecMinus (Vec c2_7 c2_23) (Vec c1_7 c1_23)) (VecMinus (Vec c2_7 c2_23) (Vec c1_7 c1_23)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_8 c2_24) (Vec c1_8 c1_24)) (VecMinus (Vec c2_8 c2_24) (Vec c1_8 c1_24))) (VecMul (VecMinus (Vec c2_9 c2_25) (Vec c1_9 c1_25)) (VecMinus (Vec c2_9 c2_25) (Vec c1_9 c1_25)))) (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26) (Vec c1_10 c1_26)) (VecMinus (Vec c2_10 c2_26) (Vec c1_10 c1_26))) (VecMul (VecMinus (Vec c2_11 c2_27) (Vec c1_11 c1_27)) (VecMinus (Vec c2_11 c2_27) (Vec c1_11 c1_27)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28) (Vec c1_12 c1_28)) (VecMinus (Vec c2_12 c2_28) (Vec c1_12 c1_28))) (VecMul (VecMinus (Vec c2_13 c2_29) (Vec c1_13 c1_29)) (VecMinus (Vec c2_13 c2_29) (Vec c1_13 c1_29)))) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30) (Vec c1_14 c1_30)) (VecMinus (Vec c2_14 c2_30) (Vec c1_14 c1_30))) (VecMul (VecMinus (Vec c2_15 c2_31) (Vec c1_15 c1_31)) (VecMinus (Vec c2_15 c2_31) (Vec c1_15 c1_31)))))) (&lt;&lt; (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16) (Vec c1_0 c1_16)) (VecMinus (Vec c2_0 c2_16) (Vec c1_0 c1_16))) (VecMul (VecMinus (Vec c2_1 c2_17) (Vec c1_1 c1_17)) (VecMinus (Vec c2_1 c2_17) (Vec c1_1 c1_17)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18) (Vec c1_2 c1_18)) (VecMinus (Vec c2_2 c2_18) (Vec c1_2 c1_18))) (VecMul (VecMinus (Vec c2_3 c2_19) (Vec c1_3 c1_19)) (VecMinus (Vec c2_3 c2_19) (Vec c1_3 c1_19)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_20) (Vec c1_4 c1_20)) (VecMinus (Vec c2_4 c2_20) (Vec c1_4 c1_20))) (VecMul (VecMinus (Vec c2_5 c2_21) (Vec c1_5 c1_21)) (VecMinus (Vec c2_5 c2_21) (Vec c1_5 c1_21)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22) (Vec c1_6 c1_22)) (VecMinus (Vec c2_6 c2_22) (Vec c1_6 c1_22))) (VecMul (VecMinus (Vec c2_7 c2_23) (Vec c1_7 c1_23)) (VecMinus (Vec c2_7 c2_23) (Vec c1_7 c1_23)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_8 c2_24) (Vec c1_8 c1_24)) (VecMinus (Vec c2_8 c2_24) (Vec c1_8 c1_24))) (VecMul (VecMinus (Vec c2_9 c2_25) (Vec c1_9 c1_25)) (VecMinus (Vec c2_9 c2_25) (Vec c1_9 c1_25)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26) (Vec c1_10 c1_26)) (VecMinus (Vec c2_10 c2_26) (Vec c1_10 c1_26))) (VecMul (VecMinus (Vec c2_11 c2_27) (Vec c1_11 c1_27)) (VecMinus (Vec c2_11 c2_27) (Vec c1_11 c1_27)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28) (Vec c1_12 c1_28)) (VecMinus (Vec c2_12 c2_28) (Vec c1_12 c1_28))) (VecMul (VecMinus (Vec c2_13 c2_29) (Vec c1_13 c1_29)) (VecMinus (Vec c2_13 c2_29) (Vec c1_13 c1_29)))) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30) (Vec c1_14 c1_30)) (VecMinus (Vec c2_14 c2_30) (Vec c1_14 c1_30))) (VecMul (VecMinus (Vec c2_15 c2_31) (Vec c1_15 c1_31)) (VecMinus (Vec c2_15 c2_31) (Vec c1_15 c1_31))))))))))) 1)))))))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16) (Vec c1_0 c1_16)) (VecMinus (Vec c2_0 c2_16) (Vec c1_0 c1_16))) (VecMul (VecMinus (Vec c2_1 c2_17) (Vec c1_1 c1_17)) (VecMinus (Vec c2_1 c2_17) (Vec c1_1 c1_17)))) (VecMul (VecMinus (Vec c2_2 c2_18) (Vec c1_2 c1_18)) (VecMinus (Vec c2_2 c2_18) (Vec c1_2 c1_18)))) (VecMul (VecMinus (Vec c2_3 c2_19) (Vec c1_3 c1_19)) (VecMinus (Vec c2_3 c2_19) (Vec c1_3 c1_19)))) (VecMul (VecMinus (Vec c2_4 c2_20) (Vec c1_4 c1_20)) (VecMinus (Vec c2_4 c2_20) (Vec c1_4 c1_20)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_5 c2_21) (Vec c1_5 c1_21)) (VecMinus (Vec c2_5 c2_21) (Vec c1_5 c1_21))) (VecMul (VecMinus (Vec c2_6 c2_22) (Vec c1_6 c1_22)) (VecMinus (Vec c2_6 c2_22) (Vec c1_6 c1_22)))) (VecAdd (VecMul (VecMinus (Vec c2_7 c2_23) (Vec c1_7 c1_23)) (VecMinus (Vec c2_7 c2_23) (Vec c1_7 c1_23))) (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_8 c2_24) (Vec c1_8 c1_24)) (VecMinus (Vec c2_8 c2_24) (Vec c1_8 c1_24))) (VecMul (VecMinus (Vec c2_9 c2_25) (Vec c1_9 c1_25)) (VecMinus (Vec c2_9 c2_25) (Vec c1_9 c1_25)))) (VecMul (VecMinus (Vec c2_10 c2_26) (Vec c1_10 c1_26)) (VecMinus (Vec c2_10 c2_26) (Vec c1_10 c1_26)))) (VecMul (VecMinus (Vec c2_11 c2_27) (Vec c1_11 c1_27)) (VecMinus (Vec c2_11 c2_27) (Vec c1_11 c1_27)))) (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28) (Vec c1_12 c1_28)) (VecMinus (Vec c2_12 c2_28) (Vec c1_12 c1_28))) (VecMul (VecMinus (Vec c2_13 c2_29) (Vec c1_13 c1_29)) (VecMinus (Vec c2_13 c2_29) (Vec c1_13 c1_29)))) (VecMul (VecMinus (Vec c2_14 c2_30) (Vec c1_14 c1_30)) (VecMinus (Vec c2_14 c2_30) (Vec c1_14 c1_30)))) (VecAdd (VecMul (VecMinus (Vec c2_15 c2_31) (Vec c1_15 c1_31)) (VecMinus (Vec c2_15 c2_31) (Vec c1_15 c1_31))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16) (Vec c1_0 c1_16)) (VecMinus (Vec c2_0 c2_16) (Vec c1_0 c1_16))) (VecMul (VecMinus (Vec c2_1 c2_17) (Vec c1_1 c1_17)) (VecMinus (Vec c2_1 c2_17) (Vec c1_1 c1_17)))) (VecMul (VecMinus (Vec c2_2 c2_18) (Vec c1_2 c1_18)) (VecMinus (Vec c2_2 c2_18) (Vec c1_2 c1_18)))) (VecMul (VecMinus (Vec c2_3 c2_19) (Vec c1_3 c1_19)) (VecMinus (Vec c2_3 c2_19) (Vec c1_3 c1_19)))) (VecAdd (VecMul (VecMinus (Vec c2_4 c2_20) (Vec c1_4 c1_20)) (VecMinus (Vec c2_4 c2_20) (Vec c1_4 c1_20))) (VecAdd (VecMul (VecMinus (Vec c2_5 c2_21) (Vec c1_5 c1_21)) (VecMinus (Vec c2_5 c2_21) (Vec c1_5 c1_21))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22) (Vec c1_6 c1_22)) (VecMinus (Vec c2_6 c2_22) (Vec c1_6 c1_22))) (VecMul (VecMinus (Vec c2_7 c2_23) (Vec c1_7 c1_23)) (VecMinus (Vec c2_7 c2_23) (Vec c1_7 c1_23)))) (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_8 c2_24) (Vec c1_8 c1_24)) (VecMinus (Vec c2_8 c2_24) (Vec c1_8 c1_24))) (VecMul (VecMinus (Vec c2_9 c2_25) (Vec c1_9 c1_25)) (VecMinus (Vec c2_9 c2_25) (Vec c1_9 c1_25)))) (VecMul (VecMinus (Vec c2_10 c2_26) (Vec c1_10 c1_26)) (VecMinus (Vec c2_10 c2_26) (Vec c1_10 c1_26)))) (VecAdd (VecMul (VecMinus (Vec c2_11 c2_27) (Vec c1_11 c1_27)) (VecMinus (Vec c2_11 c2_27) (Vec c1_11 c1_27))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28) (Vec c1_12 c1_28)) (VecMinus (Vec c2_12 c2_28) (Vec c1_12 c1_28))) (VecMul (VecMinus (Vec c2_13 c2_29) (Vec c1_13 c1_29)) (VecMinus (Vec c2_13 c2_29) (Vec c1_13 c1_29)))) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30) (Vec c1_14 c1_30)) (VecMinus (Vec c2_14 c2_30) (Vec c1_14 c1_30))) (VecMul (VecMinus (Vec c2_15 c2_31) (Vec c1_15 c1_31)) (VecMinus (Vec c2_15 c2_31) (Vec c1_15 c1_31))))))))))) 1)))))))</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -2815,32 +2815,32 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( + ( * v1_2 v2_2 ) ( * v1_3 v2_3 ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMul (Vec v1_0 v1_2) (Vec v2_0 v2_2)) (VecMul (Vec v1_1 v1_3) (Vec v2_1 v2_3))) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_2) (Vec v2_0 v2_2)) (VecMul (Vec v1_1 v1_3) (Vec v2_1 v2_3))) 1))</t>
         </is>
       </c>
       <c r="E57" t="n">
         <v>1756</v>
       </c>
       <c r="F57" t="n">
-        <v>1756</v>
+        <v>260</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>85.19</v>
       </c>
       <c r="H57" t="n">
         <v>39.37</v>
       </c>
       <c r="I57" t="n">
-        <v>39.37</v>
+        <v>40.57</v>
       </c>
       <c r="J57" t="b">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>260.63</v>
+        <v>259.43</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( + ( * v1_2 v2_2 ) ( * v1_3 v2_3 ) ) ) ( + ( + ( * v1_4 v2_4 ) ( * v1_5 v2_5 ) ) ( + ( * v1_6 v2_6 ) ( * v1_7 v2_7 ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (Vec v1_1 v1_5) (Vec v2_1 v2_5))) (VecAdd (VecMul (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (Vec v1_3 v1_7) (Vec v2_3 v2_7)))) (&lt;&lt; (VecAdd (VecAdd (VecMul (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (Vec v1_1 v1_5) (Vec v2_1 v2_5))) (VecAdd (VecMul (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (Vec v1_3 v1_7) (Vec v2_3 v2_7)))) 1))</t>
         </is>
       </c>
       <c r="E58" t="n">
         <v>3757</v>
       </c>
       <c r="F58" t="n">
-        <v>3757</v>
+        <v>463</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="H58" t="n">
         <v>40.57</v>
       </c>
       <c r="I58" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="J58" t="b">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>259.43</v>
+        <v>258.23</v>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
@@ -2899,32 +2899,32 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMul (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec v1_1 v1_17) (Vec v2_1 v2_17))) (VecAdd (VecAdd (VecMul (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (Vec v1_3 v1_19) (Vec v2_3 v2_19))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (Vec v1_5 v1_21) (Vec v2_5 v2_21))) (VecAdd (VecAdd (VecMul (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (Vec v1_7 v1_23) (Vec v2_7 v2_23))) (VecAdd (VecAdd (VecMul (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (Vec v1_9 v1_25) (Vec v2_9 v2_25))) (VecAdd (VecAdd (VecMul (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (Vec v1_11 v1_27) (Vec v2_11 v2_27))) (VecAdd (VecAdd (VecMul (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec v1_13 v1_29) (Vec v2_13 v2_29))) (VecAdd (VecAdd (VecMul (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (VecMul (Vec v1_15 v1_31) (Vec v2_15 v2_31))) (&lt;&lt; (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec v1_1 v1_17) (Vec v2_1 v2_17))) (VecAdd (VecAdd (VecMul (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (Vec v1_3 v1_19) (Vec v2_3 v2_19))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (Vec v1_5 v1_21) (Vec v2_5 v2_21))) (VecAdd (VecAdd (VecMul (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (Vec v1_7 v1_23) (Vec v2_7 v2_23))) (VecAdd (VecAdd (VecMul (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (Vec v1_9 v1_25) (Vec v2_9 v2_25))) (VecAdd (VecAdd (VecMul (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (Vec v1_11 v1_27) (Vec v2_11 v2_27))) (VecAdd (VecAdd (VecMul (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec v1_13 v1_29) (Vec v2_13 v2_29))) (VecAdd (VecMul (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (VecMul (Vec v1_15 v1_31) (Vec v2_15 v2_31)))))))))) 1)))))))))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec v1_1 v1_17) (Vec v2_1 v2_17))) (VecMul (Vec v1_2 v1_18) (Vec v2_2 v2_18))) (VecMul (Vec v1_3 v1_19) (Vec v2_3 v2_19))) (VecMul (Vec v1_4 v1_20) (Vec v2_4 v2_20))) (VecAdd (VecAdd (VecMul (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecMul (Vec v1_6 v1_22) (Vec v2_6 v2_22))) (VecAdd (VecMul (Vec v1_7 v1_23) (Vec v2_7 v2_23)) (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (Vec v1_9 v1_25) (Vec v2_9 v2_25))) (VecMul (Vec v1_10 v1_26) (Vec v2_10 v2_26))) (VecMul (Vec v1_11 v1_27) (Vec v2_11 v2_27))) (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec v1_13 v1_29) (Vec v2_13 v2_29))) (VecMul (Vec v1_14 v1_30) (Vec v2_14 v2_30))) (VecAdd (VecMul (Vec v1_15 v1_31) (Vec v2_15 v2_31)) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec v1_1 v1_17) (Vec v2_1 v2_17))) (VecMul (Vec v1_2 v1_18) (Vec v2_2 v2_18))) (VecMul (Vec v1_3 v1_19) (Vec v2_3 v2_19))) (VecAdd (VecMul (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecAdd (VecMul (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecAdd (VecAdd (VecMul (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (Vec v1_7 v1_23) (Vec v2_7 v2_23))) (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (Vec v1_9 v1_25) (Vec v2_9 v2_25))) (VecMul (Vec v1_10 v1_26) (Vec v2_10 v2_26))) (VecAdd (VecMul (Vec v1_11 v1_27) (Vec v2_11 v2_27)) (VecAdd (VecAdd (VecMul (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec v1_13 v1_29) (Vec v2_13 v2_29))) (VecAdd (VecMul (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (VecMul (Vec v1_15 v1_31) (Vec v2_15 v2_31)))))))))) 1)))))))</t>
         </is>
       </c>
       <c r="E59" t="n">
         <v>15759</v>
       </c>
       <c r="F59" t="n">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="G59" t="n">
-        <v>89.29000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="H59" t="n">
         <v>42.97</v>
       </c>
       <c r="I59" t="n">
-        <v>57.34</v>
+        <v>54.95</v>
       </c>
       <c r="J59" t="b">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>242.66</v>
+        <v>245.05</v>
       </c>
       <c r="L59" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60">
@@ -2941,32 +2941,32 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 0 in_2_2 in_2_3 0 0 in_3_2 in_3_3 0 0 in_2_2 in_2_3 0) (Vec in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2))) (VecAdd (VecAdd (Vec 0 0 0 0 0 in_0_2 in_0_3 0 0 in_1_2 in_1_3 0 0 0 0 0) (Vec 0 (* in_0_2 2) (* in_0_3 2) 0 in_0_1 (- in_0_0) (- in_0_1) (- in_0_2) in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) 0 (* in_3_2 2) (* in_3_3 2) 0)) (VecAdd (Vec 0 0 0 0 0 (* in_1_2 2) (* in_1_3 2) 0 0 (* in_2_2 2) (* in_2_3 2) 0 0 0 0 0) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2) (Vec 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2)))))</t>
+          <t>(VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 0 in_2_2 in_2_3 0 0 in_3_2 in_3_3 0 0 in_2_2 in_2_3 0) (VecMinus (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_2_1 in_2_0 in_2_1 in_2_2 0 in_1_0 in_1_1 in_1_2 0 in_2_0 in_2_1 in_2_2 0 in_3_0 in_3_1 in_3_2 0 in_2_0 in_2_1 in_2_2) (&lt;&lt; (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_2_1 in_2_0 in_2_1 in_2_2 0 in_1_0 in_1_1 in_1_2 0 in_2_0 in_2_1 in_2_2 0 in_3_0 in_3_1 in_3_2 0 in_2_0 in_2_1 in_2_2) 16))) (VecAdd (VecAdd (Vec 0 0 0 0 0 in_0_2 in_0_3 0 0 in_1_2 in_1_3 0 0 0 0 0) (VecMul (Vec 1 in_0_2 in_0_3 1 1 1 1 1 1 1 1 1 1 in_3_2 in_3_3 1) (VecMinus (Vec 0 2 2 0 in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 0 2 2 0 0 0 0 0 0 in_0_0 in_0_1 in_0_2 0 in_1_0 in_1_1 in_1_2 0 0 0 0) (&lt;&lt; (Vec 0 2 2 0 in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 0 2 2 0 0 0 0 0 0 in_0_0 in_0_1 in_0_2 0 in_1_0 in_1_1 in_1_2 0 0 0 0) 16)))) (VecAdd (VecMul (Vec 1 1 1 1 1 in_1_2 in_1_3 1 1 in_2_2 in_2_3 1 1 1 1 1) (Vec 0 0 0 0 0 2 2 0 0 2 2 0 0 0 0 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2) (Vec 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2)))))</t>
         </is>
       </c>
       <c r="E60" t="n">
         <v>21507</v>
       </c>
       <c r="F60" t="n">
-        <v>6612</v>
+        <v>448</v>
       </c>
       <c r="G60" t="n">
-        <v>69.26000000000001</v>
+        <v>97.92</v>
       </c>
       <c r="H60" t="n">
         <v>40.57</v>
       </c>
       <c r="I60" t="n">
-        <v>40.57</v>
+        <v>42.97</v>
       </c>
       <c r="J60" t="b">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>259.43</v>
+        <v>257.03</v>
       </c>
       <c r="L60" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61">
@@ -2983,17 +2983,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMul (Vec a_0_0 a_0_0 a_0_0 a_1_0 a_1_0 a_1_0 a_2_0 a_2_0 a_2_0) (Vec b_0_0 b_0_1 b_0_2 b_0_0 b_0_1 b_0_2 b_0_0 b_0_1 b_0_2)) (VecMul (Vec a_0_1 a_0_1 a_0_1 a_1_1 a_1_1 a_1_1 a_2_1 a_2_1 a_2_1) (Vec b_1_0 b_1_1 b_1_2 b_1_0 b_1_1 b_1_2 b_1_0 b_1_1 b_1_2))) (Vec (* a_0_2 b_2_0) (* a_0_2 b_2_1) (* a_0_2 b_2_2) (* a_1_2 b_2_0) (* a_1_2 b_2_1) (* a_1_2 b_2_2) (* a_2_2 b_2_0) (* a_2_2 b_2_1) (* a_2_2 b_2_2)))</t>
+          <t>(VecAdd (VecAdd (VecMul (Vec a_0_0 a_0_0 a_0_0 a_1_0 a_1_0 a_1_0 a_2_0 a_2_0 a_2_0) (Vec b_0_0 b_0_1 b_0_2 b_0_0 b_0_1 b_0_2 b_0_0 b_0_1 b_0_2)) (VecMul (Vec a_0_1 a_0_1 a_0_1 a_1_1 a_1_1 a_1_1 a_2_1 a_2_1 a_2_1) (Vec b_1_0 b_1_1 b_1_2 b_1_0 b_1_1 b_1_2 b_1_0 b_1_1 b_1_2))) (VecMul (Vec a_0_2 a_0_2 a_0_2 a_1_2 a_1_2 a_1_2 a_2_2 a_2_2 a_2_2) (Vec b_2_0 b_2_1 b_2_2 b_2_0 b_2_1 b_2_2 b_2_0 b_2_1 b_2_2)))</t>
         </is>
       </c>
       <c r="E61" t="n">
         <v>11256</v>
       </c>
       <c r="F61" t="n">
-        <v>2458</v>
+        <v>308</v>
       </c>
       <c r="G61" t="n">
-        <v>78.16</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="H61" t="n">
         <v>39.37</v>
@@ -3008,7 +3008,7 @@
         <v>260.63</v>
       </c>
       <c r="L61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
@@ -3025,32 +3025,32 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>(Vec ( + ( * ( + ( * o3 ( - 1 c23 ) ) ( * c23 o2 ) ) ( - 1 c12 ) ) ( * c12 ( + ( * o3 ( - 1 c13 ) ) ( * c13 o1 ) ) ) ) )</t>
+          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec o3 1 c23 1) (Vec (- 1 c23) c12 o2 0)) (&lt;&lt; (VecMul (Vec o3 1 c23 1) (Vec (- 1 c23) c12 o2 0)) 2)) (VecAdd (VecMul (Vec 1 o3 1 c13) (VecMinus (Vec 1 1 0 o1) (Vec c12 c13 0 0))) (&lt;&lt; (VecMul (Vec 1 o3 1 c13) (VecMinus (Vec 1 1 0 o1) (Vec c12 c13 0 0))) 2))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o3 1 c23 1) (Vec (- 1 c23) c12 o2 0)) (&lt;&lt; (VecMul (Vec o3 1 c23 1) (Vec (- 1 c23) c12 o2 0)) 2)) (VecAdd (VecMul (Vec 1 o3 1 c13) (VecMinus (Vec 1 1 0 o1) (Vec c12 c13 0 0))) (&lt;&lt; (VecMul (Vec 1 o3 1 c13) (VecMinus (Vec 1 1 0 o1) (Vec c12 c13 0 0))) 2))) 1))</t>
         </is>
       </c>
       <c r="E62" t="n">
         <v>3009</v>
       </c>
       <c r="F62" t="n">
-        <v>3009</v>
+        <v>724</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>75.94</v>
       </c>
       <c r="H62" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>75.15000000000001</v>
+        <v>77.55</v>
       </c>
       <c r="J62" t="b">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>224.85</v>
+        <v>222.45</v>
       </c>
       <c r="L62" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>(Vec ( + ( * ( + ( * ( + ( * o321 ( - 1 c23 ) ) ( * c23 o231 ) ) ( - 1 c13 ) ) ( * c13 o213 ) ) ( - 1 c12 ) ) ( * c12 ( + ( * ( - 1 c23 ) ( + ( * o312 ( - 1 c13 ) ) ( * c13 o132 ) ) ) ( * c23 o123 ) ) ) ) )</t>
+          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 c13 1) (Vec (- 1 c13) c12 o213 0)) (&lt;&lt; (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 c13 1) (Vec (- 1 c13) c12 o213 0)) 2)) (VecAdd (VecMul (Vec 1 (- 1 c23) 1 c23) (Vec (- 1 c12) (+ (* o312 (- 1 c13)) (* c13 o132)) 0 o123)) (&lt;&lt; (VecMul (Vec 1 (- 1 c23) 1 c23) (Vec (- 1 c12) (+ (* o312 (- 1 c13)) (* c13 o132)) 0 o123)) 2))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 c13 1) (Vec (- 1 c13) c12 o213 0)) (&lt;&lt; (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 c13 1) (Vec (- 1 c13) c12 o213 0)) 2)) (VecAdd (VecMul (Vec 1 (- 1 c23) 1 c23) (Vec (- 1 c12) (+ (* o312 (- 1 c13)) (* c13 o132)) 0 o123)) (&lt;&lt; (VecMul (Vec 1 (- 1 c23) 1 c23) (Vec (- 1 c12) (+ (* o312 (- 1 c13)) (* c13 o132)) 0 o123)) 2))) 1))</t>
         </is>
       </c>
       <c r="E63" t="n">
         <v>5012</v>
       </c>
       <c r="F63" t="n">
-        <v>5012</v>
+        <v>3226</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>35.63</v>
       </c>
       <c r="H63" t="n">
         <v>110.93</v>
       </c>
       <c r="I63" t="n">
-        <v>110.93</v>
+        <v>113.33</v>
       </c>
       <c r="J63" t="b">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>189.07</v>
+        <v>186.67</v>
       </c>
       <c r="L63" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
     </row>
     <row r="64">
@@ -3109,32 +3109,32 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>(Vec ( * ( + x9602 x9604 ) ( + ( + x9608 x9610 ) ( + ( * x9613 x9615 ) x9617 ) ) ) )</t>
+          <t>(VecMul (VecAdd (VecAdd (Vec x9602 x9608 0 x9610) (&lt;&lt; (Vec x9602 x9608 0 x9610) 2)) (VecAdd (Vec x9604 (* x9613 x9615) 0 x9617) (&lt;&lt; (Vec x9604 (* x9613 x9615) 0 x9617) 2))) (&lt;&lt; (VecAdd (VecAdd (Vec x9602 x9608 0 x9610) (&lt;&lt; (Vec x9602 x9608 0 x9610) 2)) (VecAdd (Vec x9604 (* x9613 x9615) 0 x9617) (&lt;&lt; (Vec x9604 (* x9613 x9615) 0 x9617) 2))) 1))</t>
         </is>
       </c>
       <c r="E64" t="n">
         <v>1508</v>
       </c>
       <c r="F64" t="n">
-        <v>1508</v>
+        <v>522</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>65.38</v>
       </c>
       <c r="H64" t="n">
         <v>73.95</v>
       </c>
       <c r="I64" t="n">
-        <v>73.95</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="J64" t="b">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>226.05</v>
+        <v>223.65</v>
       </c>
       <c r="L64" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -3151,32 +3151,32 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * ( + ( * x9604 x9605 ) ( + x9607 x9608 ) ) ( + ( + x9611 x9612 ) ( + x9614 x9615 ) ) ) ( * ( * ( * x9619 x9620 ) ( * x9622 x9623 ) ) ( * ( + x9626 x9627 ) ( * x9629 x9630 ) ) ) ) ( * ( + ( + ( * x9634 x9635 ) ( + x9637 x9638 ) ) ( + ( * x9641 x9642 ) ( * x9644 x9645 ) ) ) ( + ( * ( + x9649 x9650 ) ( + x9652 x9653 ) ) ( + ( * x9656 x9657 ) ( * x9659 x9660 ) ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMul (VecAdd (VecAdd (VecMul (Vec 1 x9634 1 1 1 x9641 1 1) (Vec 0 x9635 0 0 x9607 x9642 0 0)) (VecMul (Vec x9604 1 (* x9619 x9620) 1 1 x9644 1 1) (Vec x9605 (+ x9637 x9638) (* x9622 x9623) 1 x9608 x9645 0 0))) (&lt;&lt; (VecAdd (VecMul (Vec 1 x9634 1 1 1 x9641 1 1) (Vec 0 x9635 0 0 x9607 x9642 0 0)) (VecMul (Vec x9604 1 (* x9619 x9620) 1 1 x9644 1 1) (Vec x9605 (+ x9637 x9638) (* x9622 x9623) 1 x9608 x9645 0 0))) 4)) (VecAdd (Vec (+ x9611 x9612) (* (+ x9649 x9650) (+ x9652 x9653)) 0 0) (VecAdd (Vec x9614 (* x9656 x9657) 0 0) (VecMul (Vec 1 x9659 (+ x9626 x9627) 1) (Vec x9615 x9660 (* x9629 x9630) 0))))) (&lt;&lt; (VecMul (VecAdd (VecAdd (VecMul (Vec 1 x9634 1 1 1 x9641 1 1) (Vec 0 x9635 0 0 x9607 x9642 0 0)) (VecMul (Vec x9604 1 (* x9619 x9620) 1 1 x9644 1 1) (Vec x9605 (+ x9637 x9638) (* x9622 x9623) 1 x9608 x9645 0 0))) (&lt;&lt; (VecAdd (VecMul (Vec 1 x9634 1 1 1 x9641 1 1) (Vec 0 x9635 0 0 x9607 x9642 0 0)) (VecMul (Vec x9604 1 (* x9619 x9620) 1 1 x9644 1 1) (Vec x9605 (+ x9637 x9638) (* x9622 x9623) 1 x9608 x9645 0 0))) 4)) (VecAdd (Vec (+ x9611 x9612) (* (+ x9649 x9650) (+ x9652 x9653)) 0 0) (VecAdd (Vec x9614 (* x9656 x9657) 0 0) (VecMul (Vec 1 x9659 (+ x9626 x9627) 1) (Vec x9615 x9660 (* x9629 x9630) 0))))) 2)) (&lt;&lt; (VecAdd (VecMul (VecAdd (VecAdd (VecMul (Vec 1 x9634 1 1 1 x9641 1 1) (Vec 0 x9635 0 0 x9607 x9642 0 0)) (VecMul (Vec x9604 1 (* x9619 x9620) 1 1 x9644 1 1) (Vec x9605 (+ x9637 x9638) (* x9622 x9623) 1 x9608 x9645 0 0))) (&lt;&lt; (VecAdd (VecMul (Vec 1 x9634 1 1 1 x9641 1 1) (Vec 0 x9635 0 0 x9607 x9642 0 0)) (VecMul (Vec x9604 1 (* x9619 x9620) 1 1 x9644 1 1) (Vec x9605 (+ x9637 x9638) (* x9622 x9623) 1 x9608 x9645 0 0))) 4)) (VecAdd (Vec (+ x9611 x9612) (* (+ x9649 x9650) (+ x9652 x9653)) 0 0) (VecAdd (Vec x9614 (* x9656 x9657) 0 0) (VecMul (Vec 1 x9659 (+ x9626 x9627) 1) (Vec x9615 x9660 (* x9629 x9630) 0))))) (&lt;&lt; (VecMul (VecAdd (VecAdd (VecMul (Vec 1 x9634 1 1 1 x9641 1 1) (Vec 0 x9635 0 0 x9607 x9642 0 0)) (VecMul (Vec x9604 1 (* x9619 x9620) 1 1 x9644 1 1) (Vec x9605 (+ x9637 x9638) (* x9622 x9623) 1 x9608 x9645 0 0))) (&lt;&lt; (VecAdd (VecMul (Vec 1 x9634 1 1 1 x9641 1 1) (Vec 0 x9635 0 0 x9607 x9642 0 0)) (VecMul (Vec x9604 1 (* x9619 x9620) 1 1 x9644 1 1) (Vec x9605 (+ x9637 x9638) (* x9622 x9623) 1 x9608 x9645 0 0))) 4)) (VecAdd (Vec (+ x9611 x9612) (* (+ x9649 x9650) (+ x9652 x9653)) 0 0) (VecAdd (Vec x9614 (* x9656 x9657) 0 0) (VecMul (Vec 1 x9659 (+ x9626 x9627) 1) (Vec x9615 x9660 (* x9629 x9630) 0))))) 2)) 1))</t>
         </is>
       </c>
       <c r="E65" t="n">
         <v>7760</v>
       </c>
       <c r="F65" t="n">
-        <v>7760</v>
+        <v>3092</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>60.15</v>
       </c>
       <c r="H65" t="n">
         <v>108.53</v>
       </c>
       <c r="I65" t="n">
-        <v>108.53</v>
+        <v>114.52</v>
       </c>
       <c r="J65" t="b">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>191.47</v>
+        <v>185.48</v>
       </c>
       <c r="L65" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66">
@@ -3193,29 +3193,29 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))) 0)) (&lt;&lt; (VecMul (Vec (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))) 0)) 2)) (VecAdd (VecMul (Vec 1 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c13) (VecMinus (Vec 1 1 0 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (+ (* o5 (- 1 c15)) (* c15 o1))))) (VecMinus (VecMinus (Vec c12 c13 (- 0 0) (- 0 0)) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0))))))))))))))))))) (&lt;&lt; (VecMul (Vec 1 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c13) (VecMinus (Vec 1 1 0 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (+ (* o5 (- 1 c15)) (* c15 o1))))) (VecMinus (VecMinus (Vec c12 c13 (- 0 0) (- 0 0)) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0))))))))))))))))))) 2))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))) 0)) (&lt;&lt; (VecMul (Vec (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))) 0)) 2)) (VecAdd (VecMul (Vec 1 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c13) (VecMinus (Vec 1 1 0 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (+ (* o5 (- 1 c15)) (* c15 o1))))) (VecMinus (VecMinus (Vec c12 c13 (- 0 0) (- 0 0)) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0))))))))))))))))))) (&lt;&lt; (VecMul (Vec 1 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c13) (VecMinus (Vec 1 1 0 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (+ (* o5 (- 1 c15)) (* c15 o1))))) (VecMinus (VecMinus (Vec c12 c13 (- 0 0) (- 0 0)) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0))))))))))))))))))) 2))) 1))</t>
+          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))) 0)) (&lt;&lt; (VecMul (Vec (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))) 0)) 2)) (VecAdd (VecMul (Vec 1 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c13) (VecMinus (Vec 1 1 0 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o5 (- 1 c15)) (* c15 o1)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))) (Vec c12 c13 0 0))) (&lt;&lt; (VecMul (Vec 1 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c13) (VecMinus (Vec 1 1 0 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o5 (- 1 c15)) (* c15 o1)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))) (Vec c12 c13 0 0))) 2))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))) 0)) (&lt;&lt; (VecMul (Vec (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))) 0)) 2)) (VecAdd (VecMul (Vec 1 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c13) (VecMinus (Vec 1 1 0 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o5 (- 1 c15)) (* c15 o1)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))) (Vec c12 c13 0 0))) (&lt;&lt; (VecMul (Vec 1 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c13) (VecMinus (Vec 1 1 0 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o5 (- 1 c15)) (* c15 o1)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))) (Vec c12 c13 0 0))) 2))) 1))</t>
         </is>
       </c>
       <c r="E66" t="n">
         <v>15015</v>
       </c>
       <c r="F66" t="n">
-        <v>13259</v>
+        <v>29615</v>
       </c>
       <c r="G66" t="n">
-        <v>11.69</v>
+        <v>-97.23999999999999</v>
       </c>
       <c r="H66" t="n">
         <v>146.71</v>
       </c>
       <c r="I66" t="n">
-        <v>163.48</v>
+        <v>2467.23</v>
       </c>
       <c r="J66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" t="n">
-        <v>136.52</v>
+        <v>-2167.23</v>
       </c>
       <c r="L66" t="n">
         <v>75</v>
@@ -3235,17 +3235,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 in_2_1 in_2_2 in_2_3 in_2_3 0 in_3_2 in_3_3 in_3_3 0 in_3_2 in_3_3 0) (VecAdd (Vec 0 0 0 0 0 in_2_1 in_2_2 0 0 in_3_1 in_3_2 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_2_0 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_3_1 in_3_1 in_3_2 in_3_3))) (Vec in_1_0 (+ in_1_0 in_0_2) (+ in_1_1 in_0_3) in_1_2 (+ in_1_1 in_1_0) (+ in_1_2 in_1_1) (+ in_1_3 in_1_2) (+ in_1_3 in_1_2) in_3_0 (+ in_2_2 in_2_1) (+ in_2_3 in_2_2) (+ in_2_3 in_2_2) in_3_0 (+ in_3_0 in_2_2) (+ in_3_1 in_2_3) in_3_2)) (VecAdd (Vec in_0_1 in_0_1 in_0_2 in_0_3 in_0_1 (+ in_1_0 in_0_2) (+ in_1_1 in_0_3) in_0_3 (+ in_2_1 in_2_0) (+ in_2_0 in_1_2) (+ in_2_1 in_1_3) in_1_3 in_2_1 in_2_1 in_2_2 in_2_3) (Vec in_0_0 in_0_0 in_0_1 in_0_2 in_0_0 (+ in_0_1 in_0_0) (+ in_0_2 in_0_1) in_0_2 (+ in_1_1 in_1_0) (+ in_1_1 in_1_0) (+ in_1_2 in_1_1) in_1_2 in_2_0 in_2_0 in_2_1 in_2_2)))</t>
+          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 in_2_1 in_2_2 in_2_3 in_2_3 0 in_3_2 in_3_3 in_3_3 0 in_3_2 in_3_3 0) (VecAdd (Vec 0 0 0 0 0 in_2_1 in_2_2 0 0 in_3_1 in_3_2 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_2_0 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_3_1 in_3_1 in_3_2 in_3_3))) (VecAdd (Vec 0 in_1_0 in_1_1 0 in_1_1 in_1_2 in_1_3 in_1_3 0 in_2_2 in_2_3 in_2_3 0 in_3_0 in_3_1 0) (Vec in_1_0 in_0_2 in_0_3 in_1_2 in_1_0 in_1_1 in_1_2 in_1_2 in_3_0 in_2_1 in_2_2 in_2_2 in_3_0 in_2_2 in_2_3 in_3_2))) (VecAdd (VecAdd (Vec 0 0 0 0 0 in_1_0 in_1_1 0 in_2_1 in_2_0 in_2_1 0 0 0 0 0) (Vec in_0_1 in_0_1 in_0_2 in_0_3 in_0_1 in_0_2 in_0_3 in_0_3 in_2_0 in_1_2 in_1_3 in_1_3 in_2_1 in_2_1 in_2_2 in_2_3)) (VecAdd (Vec 0 0 0 0 0 in_0_1 in_0_2 0 in_1_1 in_1_1 in_1_2 0 0 0 0 0) (Vec in_0_0 in_0_0 in_0_1 in_0_2 in_0_0 in_0_0 in_0_1 in_0_2 in_1_0 in_1_0 in_1_1 in_1_2 in_2_0 in_2_0 in_2_1 in_2_2))))</t>
         </is>
       </c>
       <c r="E67" t="n">
         <v>21006</v>
       </c>
       <c r="F67" t="n">
-        <v>5261</v>
+        <v>14</v>
       </c>
       <c r="G67" t="n">
-        <v>74.95</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="H67" t="n">
         <v>7.19</v>
@@ -3260,7 +3260,7 @@
         <v>292.81</v>
       </c>
       <c r="L67" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68">
@@ -3277,17 +3277,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3) (VecAdd (Vec 2 2 2 2) (Vec (* v1_0 5) (* v1_1 5) (* v1_2 5) (* v1_3 5))))</t>
+          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3) (VecAdd (Vec 2 2 2 2) (VecMul (Vec v1_0 v1_1 v1_2 v1_3) (Vec 5 5 5 5))))</t>
         </is>
       </c>
       <c r="E68" t="n">
         <v>3006</v>
       </c>
       <c r="F68" t="n">
-        <v>1008</v>
+        <v>108</v>
       </c>
       <c r="G68" t="n">
-        <v>66.47</v>
+        <v>96.41</v>
       </c>
       <c r="H68" t="n">
         <v>39.37</v>
@@ -3302,7 +3302,7 @@
         <v>260.63</v>
       </c>
       <c r="L68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
@@ -3319,17 +3319,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3 v2_4 v2_5 v2_6 v2_7 v2_8 v2_9 v2_10 v2_11 v2_12 v2_13 v2_14 v2_15) (VecAdd (Vec 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2) (Vec (* v1_0 5) (* v1_1 5) (* v1_2 5) (* v1_3 5) (* v1_4 5) (* v1_5 5) (* v1_6 5) (* v1_7 5) (* v1_8 5) (* v1_9 5) (* v1_10 5) (* v1_11 5) (* v1_12 5) (* v1_13 5) (* v1_14 5) (* v1_15 5))))</t>
+          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3 v2_4 v2_5 v2_6 v2_7 v2_8 v2_9 v2_10 v2_11 v2_12 v2_13 v2_14 v2_15) (VecAdd (Vec 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2 2) (VecMul (Vec v1_0 v1_1 v1_2 v1_3 v1_4 v1_5 v1_6 v1_7 v1_8 v1_9 v1_10 v1_11 v1_12 v1_13 v1_14 v1_15) (Vec 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5 5))))</t>
         </is>
       </c>
       <c r="E69" t="n">
         <v>12006</v>
       </c>
       <c r="F69" t="n">
-        <v>4008</v>
+        <v>108</v>
       </c>
       <c r="G69" t="n">
-        <v>66.62</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H69" t="n">
         <v>39.37</v>
@@ -3344,7 +3344,7 @@
         <v>260.63</v>
       </c>
       <c r="L69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -3361,32 +3361,32 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( - ( + v1_0 v2_0 ) ( * ( * v1_0 v2_0 ) 2 ) ) ( - ( + v1_1 v2_1 ) ( * 2 ( * v1_1 v2_1 ) ) ) ) ( - ( + v1_2 v2_2 ) ( * 2 ( * v1_2 v2_2 ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2 v1_1 0 v2_0 v2_2 v2_1 0) (&lt;&lt; (Vec v1_0 v1_2 v1_1 0 v2_0 v2_2 v2_1 0) 4)) (VecMul (Vec (* v1_0 v2_0) 2 2 1) (VecMul (Vec 1 v1_2 v1_1 1) (Vec 2 v2_2 v2_1 0)))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_2 v1_1 0 v2_0 v2_2 v2_1 0) (&lt;&lt; (Vec v1_0 v1_2 v1_1 0 v2_0 v2_2 v2_1 0) 4)) (VecMul (Vec (* v1_0 v2_0) 2 2 1) (VecMul (Vec 1 v1_2 v1_1 1) (Vec 2 v2_2 v2_1 0)))) 2)) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2 v1_1 0 v2_0 v2_2 v2_1 0) (&lt;&lt; (Vec v1_0 v1_2 v1_1 0 v2_0 v2_2 v2_1 0) 4)) (VecMul (Vec (* v1_0 v2_0) 2 2 1) (VecMul (Vec 1 v1_2 v1_1 1) (Vec 2 v2_2 v2_1 0)))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_2 v1_1 0 v2_0 v2_2 v2_1 0) (&lt;&lt; (Vec v1_0 v1_2 v1_1 0 v2_0 v2_2 v2_1 0) 4)) (VecMul (Vec (* v1_0 v2_0) 2 2 1) (VecMul (Vec 1 v1_2 v1_1 1) (Vec 2 v2_2 v2_1 0)))) 2)) 1))</t>
         </is>
       </c>
       <c r="E70" t="n">
         <v>3509</v>
       </c>
       <c r="F70" t="n">
-        <v>3509</v>
+        <v>636</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>81.88</v>
       </c>
       <c r="H70" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>75.15000000000001</v>
+        <v>77.55</v>
       </c>
       <c r="J70" t="b">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>224.85</v>
+        <v>222.45</v>
       </c>
       <c r="L70" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
@@ -3403,32 +3403,32 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( - ( + v1_0 v2_0 ) ( * ( * v1_0 v2_0 ) 2 ) ) ( - ( + v1_1 v2_1 ) ( * 2 ( * v1_1 v2_1 ) ) ) ) ( + ( + ( - ( + v1_2 v2_2 ) ( * 2 ( * v1_2 v2_2 ) ) ) ( - ( + v1_3 v2_3 ) ( * 2 ( * v1_3 v2_3 ) ) ) ) ( - ( + v1_4 v2_4 ) ( * 2 ( * v1_4 v2_4 ) ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2 0 v1_3) (Vec v2_0 v2_2 0 v2_3)) (VecMul (Vec (* v1_0 v2_0) 2 1 2) (VecMul (Vec 1 v1_2 1 v1_3) (Vec 2 v2_2 0 v2_3)))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_2 0 v1_3) (Vec v2_0 v2_2 0 v2_3)) (VecMul (Vec (* v1_0 v2_0) 2 1 2) (VecMul (Vec 1 v1_2 1 v1_3) (Vec 2 v2_2 0 v2_3)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4) (Vec v2_1 v2_4)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_4) (Vec v2_1 v2_4))))) (&lt;&lt; (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2 0 v1_3) (Vec v2_0 v2_2 0 v2_3)) (VecMul (Vec (* v1_0 v2_0) 2 1 2) (VecMul (Vec 1 v1_2 1 v1_3) (Vec 2 v2_2 0 v2_3)))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_2 0 v1_3) (Vec v2_0 v2_2 0 v2_3)) (VecMul (Vec (* v1_0 v2_0) 2 1 2) (VecMul (Vec 1 v1_2 1 v1_3) (Vec 2 v2_2 0 v2_3)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4) (Vec v2_1 v2_4)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_4) (Vec v2_1 v2_4))))) 1))</t>
         </is>
       </c>
       <c r="E71" t="n">
         <v>6010</v>
       </c>
       <c r="F71" t="n">
-        <v>6010</v>
+        <v>774</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>87.12</v>
       </c>
       <c r="H71" t="n">
         <v>76.34999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>76.34999999999999</v>
+        <v>78.75</v>
       </c>
       <c r="J71" t="b">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>223.65</v>
+        <v>221.25</v>
       </c>
       <c r="L71" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72">
@@ -3445,17 +3445,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (Vec (* v1_0 v2_0) 2) (VecMul (Vec 2 v1_8 1 v2_8) (&lt;&lt; (Vec 2 v1_8 1 v2_8) 2)))) (VecMinus (VecAdd (Vec v1_1 v1_9) (Vec v2_1 v2_9)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_9) (Vec v2_1 v2_9))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_10) (Vec v2_2 v2_10)))) (VecMinus (VecAdd (Vec v1_3 v1_11) (Vec v2_3 v2_11)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_11) (Vec v2_3 v2_11))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (Vec 2 2) (VecMul (Vec v1_4 v1_12) (Vec v2_4 v2_12)))) (VecMinus (VecAdd (Vec v1_5 v1_13) (Vec v2_5 v2_13)) (VecMul (Vec 2 2) (VecMul (Vec v1_5 v1_13) (Vec v2_5 v2_13))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (Vec 2 2) (VecMul (Vec v1_6 v1_14) (Vec v2_6 v2_14)))) (VecMinus (VecAdd (Vec v1_7 v1_15) (Vec v2_7 v2_15)) (VecMul (Vec 2 2) (VecMul (Vec v1_7 v1_15) (Vec v2_7 v2_15))))) (&lt;&lt; (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (Vec (* v1_0 v2_0) 2) (Vec 2 (* v1_8 v2_8)))) (VecMinus (VecAdd (Vec v1_1 v1_9) (Vec v2_1 v2_9)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_9) (Vec v2_1 v2_9))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_10) (Vec v2_2 v2_10)))) (VecMinus (VecAdd (Vec v1_3 v1_11) (Vec v2_3 v2_11)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_11) (Vec v2_3 v2_11))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (Vec 2 2) (VecMul (Vec v1_4 v1_12) (Vec v2_4 v2_12)))) (VecMinus (VecAdd (Vec v1_5 v1_13) (Vec v2_5 v2_13)) (VecMul (Vec 2 2) (VecMul (Vec v1_5 v1_13) (Vec v2_5 v2_13))))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (Vec 2 2) (VecMul (Vec v1_6 v1_14) (Vec v2_6 v2_14)))) (VecMinus (VecAdd (Vec v1_7 v1_15) (Vec v2_7 v2_15)) (VecMul (Vec 2 2) (VecMul (Vec v1_7 v1_15) (Vec v2_7 v2_15)))))))) 1)))))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (VecMul (Vec v1_0 2 v2_0 1) (&lt;&lt; (Vec v1_0 2 v2_0 1) 2)) (VecMul (Vec 2 v1_8 1 v2_8) (&lt;&lt; (Vec 2 v1_8 1 v2_8) 2)))) (VecMinus (VecAdd (Vec v1_1 v1_9) (Vec v2_1 v2_9)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_9) (Vec v2_1 v2_9))))) (VecMinus (VecAdd (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_10) (Vec v2_2 v2_10))))) (VecMinus (VecAdd (Vec v1_3 v1_11) (Vec v2_3 v2_11)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_11) (Vec v2_3 v2_11))))) (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (Vec 2 2) (VecMul (Vec v1_4 v1_12) (Vec v2_4 v2_12)))) (VecAdd (VecMinus (VecAdd (Vec v1_5 v1_13) (Vec v2_5 v2_13)) (VecMul (Vec 2 2) (VecMul (Vec v1_5 v1_13) (Vec v2_5 v2_13)))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (Vec 2 2) (VecMul (Vec v1_6 v1_14) (Vec v2_6 v2_14)))) (VecMinus (VecAdd (Vec v1_7 v1_15) (Vec v2_7 v2_15)) (VecMul (Vec 2 2) (VecMul (Vec v1_7 v1_15) (Vec v2_7 v2_15))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (VecMul (Vec v1_0 2 v2_0 1) (&lt;&lt; (Vec v1_0 2 v2_0 1) 2)) (VecMul (Vec 2 v1_8 1 v2_8) (&lt;&lt; (Vec 2 v1_8 1 v2_8) 2)))) (VecMinus (VecAdd (Vec v1_1 v1_9) (Vec v2_1 v2_9)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_9) (Vec v2_1 v2_9))))) (VecMinus (VecAdd (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_10) (Vec v2_2 v2_10))))) (VecAdd (VecMinus (VecAdd (Vec v1_3 v1_11) (Vec v2_3 v2_11)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_11) (Vec v2_3 v2_11)))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (Vec 2 2) (VecMul (Vec v1_4 v1_12) (Vec v2_4 v2_12)))) (VecMinus (VecAdd (Vec v1_5 v1_13) (Vec v2_5 v2_13)) (VecMul (Vec 2 2) (VecMul (Vec v1_5 v1_13) (Vec v2_5 v2_13))))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (Vec 2 2) (VecMul (Vec v1_6 v1_14) (Vec v2_6 v2_14)))) (VecMinus (VecAdd (Vec v1_7 v1_15) (Vec v2_7 v2_15)) (VecMul (Vec 2 2) (VecMul (Vec v1_7 v1_15) (Vec v2_7 v2_15)))))))) 1)))))</t>
         </is>
       </c>
       <c r="E72" t="n">
         <v>19761</v>
       </c>
       <c r="F72" t="n">
-        <v>1993</v>
+        <v>1899</v>
       </c>
       <c r="G72" t="n">
-        <v>89.91</v>
+        <v>90.39</v>
       </c>
       <c r="H72" t="n">
         <v>77.55</v>
@@ -3470,7 +3470,7 @@
         <v>216.46</v>
       </c>
       <c r="L72" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="73">
@@ -3487,17 +3487,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>(VecAdd (Vec c1_0 c1_1 c1_2 c1_3) (VecAdd (Vec c2_0 c2_1 c2_2 c2_3) (Vec (* c0_0 (+ c3_0 (* c0_0 c4_0))) (* c0_1 (+ c3_1 (* c0_1 c4_1))) (* c0_2 (+ c3_2 (* c0_2 c4_2))) (* c0_3 (+ c3_3 (* c0_3 c4_3))))))</t>
+          <t>(VecAdd (Vec c1_0 c1_1 c1_2 c1_3) (VecAdd (Vec c2_0 c2_1 c2_2 c2_3) (VecMul (Vec c0_0 c0_1 c0_2 c0_3) (VecAdd (Vec c3_0 c3_1 c3_2 c3_3) (VecMul (Vec c0_0 c0_1 c0_2 c0_3) (Vec c4_0 c4_1 c4_2 c4_3))))))</t>
         </is>
       </c>
       <c r="E73" t="n">
         <v>5009</v>
       </c>
       <c r="F73" t="n">
-        <v>3011</v>
+        <v>212</v>
       </c>
       <c r="G73" t="n">
-        <v>39.89</v>
+        <v>95.77</v>
       </c>
       <c r="H73" t="n">
         <v>75.15000000000001</v>
@@ -3512,7 +3512,7 @@
         <v>224.85</v>
       </c>
       <c r="L73" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
@@ -3571,32 +3571,32 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2 c2_1 1) (Vec c1_0 c1_2 c1_1 0)) (VecMinus (Vec c2_0 c2_2 c2_1 0) (Vec c1_0 c1_2 c1_1 0))) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_2 c2_1 1) (Vec c1_0 c1_2 c1_1 0)) (VecMinus (Vec c2_0 c2_2 c2_1 0) (Vec c1_0 c1_2 c1_1 0))) 2)) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2 c2_1 1) (Vec c1_0 c1_2 c1_1 0)) (VecMinus (Vec c2_0 c2_2 c2_1 0) (Vec c1_0 c1_2 c1_1 0))) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_2 c2_1 1) (Vec c1_0 c1_2 c1_1 0)) (VecMinus (Vec c2_0 c2_2 c2_1 0) (Vec c1_0 c1_2 c1_1 0))) 2)) 1))</t>
         </is>
       </c>
       <c r="E75" t="n">
         <v>2757</v>
       </c>
       <c r="F75" t="n">
-        <v>2757</v>
+        <v>218</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>92.09</v>
       </c>
       <c r="H75" t="n">
         <v>40.57</v>
       </c>
       <c r="I75" t="n">
-        <v>40.57</v>
+        <v>42.97</v>
       </c>
       <c r="J75" t="b">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>259.43</v>
+        <v>257.03</v>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
@@ -3613,32 +3613,32 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( + ( + ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ( * ( - c2_3 c1_3 ) ( - c2_3 c1_3 ) ) ) ( * ( - c2_4 c1_4 ) ( - c2_4 c1_4 ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2 1 c2_3) (Vec c1_0 c1_2 0 c1_3)) (VecMinus (Vec c2_0 c2_2 0 c2_3) (Vec c1_0 c1_2 0 c1_3))) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_2 1 c2_3) (Vec c1_0 c1_2 0 c1_3)) (VecMinus (Vec c2_0 c2_2 0 c2_3) (Vec c1_0 c1_2 0 c1_3))) 2)) (VecMul (VecMinus (Vec c2_1 c2_4) (Vec c1_1 c1_4)) (VecMinus (Vec c2_1 c2_4) (Vec c1_1 c1_4)))) (&lt;&lt; (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2 1 c2_3) (Vec c1_0 c1_2 0 c1_3)) (VecMinus (Vec c2_0 c2_2 0 c2_3) (Vec c1_0 c1_2 0 c1_3))) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_2 1 c2_3) (Vec c1_0 c1_2 0 c1_3)) (VecMinus (Vec c2_0 c2_2 0 c2_3) (Vec c1_0 c1_2 0 c1_3))) 2)) (VecMul (VecMinus (Vec c2_1 c2_4) (Vec c1_1 c1_4)) (VecMinus (Vec c2_1 c2_4) (Vec c1_1 c1_4)))) 1))</t>
         </is>
       </c>
       <c r="E76" t="n">
         <v>4758</v>
       </c>
       <c r="F76" t="n">
-        <v>4758</v>
+        <v>322</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>93.23</v>
       </c>
       <c r="H76" t="n">
         <v>41.77</v>
       </c>
       <c r="I76" t="n">
-        <v>41.77</v>
+        <v>44.16</v>
       </c>
       <c r="J76" t="b">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>258.23</v>
+        <v>255.84</v>
       </c>
       <c r="L76" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77">
@@ -3655,32 +3655,32 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8) (Vec c1_0 c1_8)) (VecMinus (Vec c2_0 c2_8) (Vec c1_0 c1_8))) (VecMul (VecMinus (Vec c2_1 c2_9) (Vec c1_1 c1_9)) (VecMinus (Vec c2_1 c2_9) (Vec c1_1 c1_9)))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_10) (Vec c1_2 c1_10)) (VecMinus (Vec c2_2 c2_10) (Vec c1_2 c1_10))) (VecMul (VecMinus (Vec c2_3 c2_11) (Vec c1_3 c1_11)) (VecMinus (Vec c2_3 c2_11) (Vec c1_3 c1_11))))) (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_12) (Vec c1_4 c1_12)) (VecMinus (Vec c2_4 c2_12) (Vec c1_4 c1_12))) (VecMul (VecMinus (Vec c2_5 c2_13) (Vec c1_5 c1_13)) (VecMinus (Vec c2_5 c2_13) (Vec c1_5 c1_13)))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14) (Vec c1_6 c1_14)) (VecMinus (Vec c2_6 c2_14) (Vec c1_6 c1_14))) (VecMul (VecMinus (Vec c2_7 c2_15) (Vec c1_7 c1_15)) (VecMinus (Vec c2_7 c2_15) (Vec c1_7 c1_15))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8) (Vec c1_0 c1_8)) (VecMinus (Vec c2_0 c2_8) (Vec c1_0 c1_8))) (VecMul (VecMinus (Vec c2_1 c2_9) (Vec c1_1 c1_9)) (VecMinus (Vec c2_1 c2_9) (Vec c1_1 c1_9)))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_10) (Vec c1_2 c1_10)) (VecMinus (Vec c2_2 c2_10) (Vec c1_2 c1_10))) (VecMul (VecMinus (Vec c2_3 c2_11) (Vec c1_3 c1_11)) (VecMinus (Vec c2_3 c2_11) (Vec c1_3 c1_11))))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_12) (Vec c1_4 c1_12)) (VecMinus (Vec c2_4 c2_12) (Vec c1_4 c1_12))) (VecMul (VecMinus (Vec c2_5 c2_13) (Vec c1_5 c1_13)) (VecMinus (Vec c2_5 c2_13) (Vec c1_5 c1_13)))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14) (Vec c1_6 c1_14)) (VecMinus (Vec c2_6 c2_14) (Vec c1_6 c1_14))) (VecMul (VecMinus (Vec c2_7 c2_15) (Vec c1_7 c1_15)) (VecMinus (Vec c2_7 c2_15) (Vec c1_7 c1_15)))))) 1)))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8) (Vec c1_0 c1_8)) (VecMinus (Vec c2_0 c2_8) (Vec c1_0 c1_8))) (VecMul (VecMinus (Vec c2_1 c2_9) (Vec c1_1 c1_9)) (VecMinus (Vec c2_1 c2_9) (Vec c1_1 c1_9)))) (VecMul (VecMinus (Vec c2_2 c2_10) (Vec c1_2 c1_10)) (VecMinus (Vec c2_2 c2_10) (Vec c1_2 c1_10)))) (VecMul (VecMinus (Vec c2_3 c2_11) (Vec c1_3 c1_11)) (VecMinus (Vec c2_3 c2_11) (Vec c1_3 c1_11)))) (VecAdd (VecMul (VecMinus (Vec c2_4 c2_12) (Vec c1_4 c1_12)) (VecMinus (Vec c2_4 c2_12) (Vec c1_4 c1_12))) (VecAdd (VecMul (VecMinus (Vec c2_5 c2_13) (Vec c1_5 c1_13)) (VecMinus (Vec c2_5 c2_13) (Vec c1_5 c1_13))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14) (Vec c1_6 c1_14)) (VecMinus (Vec c2_6 c2_14) (Vec c1_6 c1_14))) (VecMul (VecMinus (Vec c2_7 c2_15) (Vec c1_7 c1_15)) (VecMinus (Vec c2_7 c2_15) (Vec c1_7 c1_15)))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8) (Vec c1_0 c1_8)) (VecMinus (Vec c2_0 c2_8) (Vec c1_0 c1_8))) (VecMul (VecMinus (Vec c2_1 c2_9) (Vec c1_1 c1_9)) (VecMinus (Vec c2_1 c2_9) (Vec c1_1 c1_9)))) (VecMul (VecMinus (Vec c2_2 c2_10) (Vec c1_2 c1_10)) (VecMinus (Vec c2_2 c2_10) (Vec c1_2 c1_10)))) (VecAdd (VecMul (VecMinus (Vec c2_3 c2_11) (Vec c1_3 c1_11)) (VecMinus (Vec c2_3 c2_11) (Vec c1_3 c1_11))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_12) (Vec c1_4 c1_12)) (VecMinus (Vec c2_4 c2_12) (Vec c1_4 c1_12))) (VecMul (VecMinus (Vec c2_5 c2_13) (Vec c1_5 c1_13)) (VecMinus (Vec c2_5 c2_13) (Vec c1_5 c1_13)))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14) (Vec c1_6 c1_14)) (VecMinus (Vec c2_6 c2_14) (Vec c1_6 c1_14))) (VecMul (VecMinus (Vec c2_7 c2_15) (Vec c1_7 c1_15)) (VecMinus (Vec c2_7 c2_15) (Vec c1_7 c1_15))))))) 1)))))</t>
         </is>
       </c>
       <c r="E77" t="n">
         <v>15759</v>
       </c>
       <c r="F77" t="n">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="G77" t="n">
-        <v>94.38</v>
+        <v>94.36</v>
       </c>
       <c r="H77" t="n">
         <v>42.97</v>
       </c>
       <c r="I77" t="n">
-        <v>45.36</v>
+        <v>48.96</v>
       </c>
       <c r="J77" t="b">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>254.64</v>
+        <v>251.04</v>
       </c>
       <c r="L77" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="78">
@@ -3697,32 +3697,32 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( * v1_2 v2_2 ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMul (Vec v1_0 v1_2 v1_1 1) (Vec v2_0 v2_2 v2_1 0)) (&lt;&lt; (VecMul (Vec v1_0 v1_2 v1_1 1) (Vec v2_0 v2_2 v2_1 0)) 2)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_2 v1_1 1) (Vec v2_0 v2_2 v2_1 0)) (&lt;&lt; (VecMul (Vec v1_0 v1_2 v1_1 1) (Vec v2_0 v2_2 v2_1 0)) 2)) 1))</t>
         </is>
       </c>
       <c r="E78" t="n">
         <v>1256</v>
       </c>
       <c r="F78" t="n">
-        <v>1256</v>
+        <v>215</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>82.88</v>
       </c>
       <c r="H78" t="n">
         <v>39.37</v>
       </c>
       <c r="I78" t="n">
-        <v>39.37</v>
+        <v>41.77</v>
       </c>
       <c r="J78" t="b">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>260.63</v>
+        <v>258.23</v>
       </c>
       <c r="L78" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
@@ -3739,32 +3739,32 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( + ( + ( * v1_2 v2_2 ) ( * v1_3 v2_3 ) ) ( * v1_4 v2_4 ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_2 1 v1_3) (Vec v2_0 v2_2 0 v2_3)) (&lt;&lt; (VecMul (Vec v1_0 v1_2 1 v1_3) (Vec v2_0 v2_2 0 v2_3)) 2)) (VecMul (Vec v1_1 v1_4) (Vec v2_1 v2_4))) (&lt;&lt; (VecAdd (VecAdd (VecMul (Vec v1_0 v1_2 1 v1_3) (Vec v2_0 v2_2 0 v2_3)) (&lt;&lt; (VecMul (Vec v1_0 v1_2 1 v1_3) (Vec v2_0 v2_2 0 v2_3)) 2)) (VecMul (Vec v1_1 v1_4) (Vec v2_1 v2_4))) 1))</t>
         </is>
       </c>
       <c r="E79" t="n">
         <v>2257</v>
       </c>
       <c r="F79" t="n">
-        <v>2257</v>
+        <v>317</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>85.95</v>
       </c>
       <c r="H79" t="n">
         <v>40.57</v>
       </c>
       <c r="I79" t="n">
-        <v>40.57</v>
+        <v>42.97</v>
       </c>
       <c r="J79" t="b">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>259.43</v>
+        <v>257.03</v>
       </c>
       <c r="L79" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
@@ -3781,32 +3781,32 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMul (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (Vec v1_1 v1_9) (Vec v2_1 v2_9))) (VecAdd (VecAdd (VecMul (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (Vec v1_3 v1_11) (Vec v2_3 v2_11))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (Vec v1_5 v1_13) (Vec v2_5 v2_13))) (VecAdd (VecAdd (VecMul (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (Vec v1_7 v1_15) (Vec v2_7 v2_15))) (&lt;&lt; (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (Vec v1_1 v1_9) (Vec v2_1 v2_9))) (VecAdd (VecAdd (VecMul (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (Vec v1_3 v1_11) (Vec v2_3 v2_11))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (Vec v1_5 v1_13) (Vec v2_5 v2_13))) (VecAdd (VecMul (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (Vec v1_7 v1_15) (Vec v2_7 v2_15)))))) 1)))))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (Vec v1_1 v1_9) (Vec v2_1 v2_9))) (VecAdd (VecMul (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (Vec v1_3 v1_11) (Vec v2_3 v2_11)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (Vec v1_5 v1_13) (Vec v2_5 v2_13))) (VecAdd (VecMul (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (Vec v1_7 v1_15) (Vec v2_7 v2_15))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (Vec v1_1 v1_9) (Vec v2_1 v2_9))) (VecAdd (VecMul (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (Vec v1_3 v1_11) (Vec v2_3 v2_11)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (Vec v1_5 v1_13) (Vec v2_5 v2_13))) (VecAdd (VecMul (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (Vec v1_7 v1_15) (Vec v2_7 v2_15))))) 1))</t>
         </is>
       </c>
       <c r="E80" t="n">
         <v>7758</v>
       </c>
       <c r="F80" t="n">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="G80" t="n">
-        <v>88.76000000000001</v>
+        <v>88.81</v>
       </c>
       <c r="H80" t="n">
         <v>41.77</v>
       </c>
       <c r="I80" t="n">
-        <v>47.76</v>
+        <v>42.97</v>
       </c>
       <c r="J80" t="b">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>252.24</v>
+        <v>257.03</v>
       </c>
       <c r="L80" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="81">
@@ -3823,32 +3823,32 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (Vec 0 in_1_2 0 0 in_2_2 0 0 in_1_2 0) (Vec in_1_1 (- in_1_0) (- in_1_1) in_2_1 (- in_2_0) (- in_2_1) in_1_1 (- in_1_0) (- in_1_1))) (VecAdd (Vec 0 (* in_0_2 2) 0 in_0_1 (+ in_0_2 (- in_0_0)) (- in_0_1) 0 (* in_2_2 2) 0) (Vec (* in_0_1 2) (* in_0_0 -2) (* in_0_1 -2) (* in_1_1 2) (+ (* in_1_2 2) (* in_1_0 -2)) (* in_1_1 -2) (* in_2_1 2) (* in_2_0 -2) (* in_2_1 -2))))</t>
+          <t>(VecAdd (VecAdd (Vec 0 in_1_2 0 0 in_2_2 0 0 in_1_2 0) (VecMinus (Vec in_1_1 in_1_0 in_1_1 in_2_1 in_2_0 in_2_1 in_1_1 in_1_0 in_1_1 0 in_1_0 in_1_1 0 in_2_0 in_2_1 0 in_1_0 in_1_1) (&lt;&lt; (Vec in_1_1 in_1_0 in_1_1 in_2_1 in_2_0 in_2_1 in_1_1 in_1_0 in_1_1 0 in_1_0 in_1_1 0 in_2_0 in_2_1 0 in_1_0 in_1_1) 9))) (VecAdd (VecMul (Vec 1 in_0_2 1 1 1 1 1 in_2_2 1) (Vec 0 2 0 in_0_1 (+ in_0_2 (- in_0_0)) (- in_0_1) 0 2 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_1_1 1 in_1_1 in_2_1 in_2_0 in_2_1) (Vec 2 -2 -2 2 (+ (* in_1_2 2) (* in_1_0 -2)) -2 2 -2 -2))))</t>
         </is>
       </c>
       <c r="E81" t="n">
         <v>9757</v>
       </c>
       <c r="F81" t="n">
-        <v>5510</v>
+        <v>1772</v>
       </c>
       <c r="G81" t="n">
-        <v>43.53</v>
+        <v>81.84</v>
       </c>
       <c r="H81" t="n">
         <v>40.57</v>
       </c>
       <c r="I81" t="n">
-        <v>40.57</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J81" t="b">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>259.43</v>
+        <v>224.85</v>
       </c>
       <c r="L81" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82">
@@ -3865,32 +3865,32 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 in_3_2 in_3_3 in_3_4 0 0 in_4_2 in_4_3 in_4_4 0 0 in_3_2 in_3_3 in_3_4 0) (Vec in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) (- in_1_3) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) (- in_2_3) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) (- in_3_3) in_4_1 (- in_4_0) (- in_4_1) (- in_4_2) (- in_4_3) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) (- in_3_3))) (VecAdd (VecAdd (Vec 0 0 0 0 0 0 in_0_2 in_0_3 in_0_4 0 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 0 0 0 0) (VecMul (Vec 1 in_0_2 in_0_3 in_0_4 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_4_2 in_4_3 in_4_4 1) (Vec 0 2 2 2 0 in_0_1 (- in_0_0) (- in_0_1) (- in_0_2) (- in_0_3) in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) (- in_1_3) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) (- in_2_3) 0 2 2 2 0))) (VecAdd (Vec 0 0 0 0 0 0 (* in_1_2 2) (* in_1_3 2) (* in_1_4 2) 0 0 (* in_2_2 2) (* in_2_3 2) (* in_2_4 2) 0 0 (* in_3_2 2) (* in_3_3 2) (* in_3_4 2) 0 0 0 0 0 0) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_0_3 in_1_1 in_1_0 in_1_1 in_1_2 in_1_3 in_2_1 in_2_0 in_2_1 in_2_2 in_2_3 in_3_1 in_3_0 in_3_1 in_3_2 in_3_3 in_4_1 in_4_0 in_4_1 in_4_2 in_4_3) (Vec 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2)))))</t>
+          <t>(VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 in_3_2 in_3_3 in_3_4 0 0 in_4_2 in_4_3 in_4_4 0 0 in_3_2 in_3_3 in_3_4 0) (VecNeg (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_1_3 in_2_1 in_2_0 in_2_1 in_2_2 in_2_3 in_3_1 in_3_0 in_3_1 in_3_2 in_3_3 in_4_1 in_4_0 in_4_1 in_4_2 in_4_3 in_3_1 in_3_0 in_3_1 in_3_2 in_3_3))) (VecAdd (VecAdd (Vec 0 0 0 0 0 0 in_0_2 in_0_3 in_0_4 0 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 0 0 0 0) (VecMul (Vec 1 in_0_2 in_0_3 in_0_4 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_4_2 in_4_3 in_4_4 1) (Vec 0 2 2 2 0 in_0_1 (- in_0_0) (- in_0_1) (- in_0_2) (- in_0_3) in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) (- in_1_3) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) (- in_2_3) 0 2 2 2 0))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 in_1_2 in_1_3 in_1_4 1 1 in_2_2 in_2_3 in_2_4 1 1 in_3_2 in_3_3 in_3_4 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 2 2 2 0 0 2 2 2 0 0 2 2 2 0 0 0 0 0 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_0_3 in_1_1 in_1_0 in_1_1 in_1_2 in_1_3 in_2_1 in_2_0 in_2_1 in_2_2 in_2_3 in_3_1 in_3_0 in_3_1 in_3_2 in_3_3 in_4_1 in_4_0 in_4_1 in_4_2 in_4_3) (Vec 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2)))))</t>
         </is>
       </c>
       <c r="E82" t="n">
         <v>37757</v>
       </c>
       <c r="F82" t="n">
-        <v>10463</v>
+        <v>3314</v>
       </c>
       <c r="G82" t="n">
-        <v>72.29000000000001</v>
+        <v>91.22</v>
       </c>
       <c r="H82" t="n">
         <v>40.57</v>
       </c>
       <c r="I82" t="n">
-        <v>41.77</v>
+        <v>42.8</v>
       </c>
       <c r="J82" t="b">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>258.23</v>
+        <v>257.2</v>
       </c>
       <c r="L82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
@@ -3949,29 +3949,29 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c23 1) (Vec (- 1 c23) c12 (+ (* o4 (- 1 c24)) (* c24 o2)) 0)) (&lt;&lt; (VecMul (Vec (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c23 1) (Vec (- 1 c23) c12 (+ (* o4 (- 1 c24)) (* c24 o2)) 0)) 2)) (VecAdd (VecMul (Vec 1 (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c13) (VecMinus (VecMinus (Vec 1 1 0 (+ (* o4 (- 1 c14)) (* c14 o1))) (Vec c12 c13 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)))))))))))))) (&lt;&lt; (VecMul (Vec 1 (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c13) (VecMinus (VecMinus (Vec 1 1 0 (+ (* o4 (- 1 c14)) (* c14 o1))) (Vec c12 c13 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)))))))))))))) 2))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c23 1) (Vec (- 1 c23) c12 (+ (* o4 (- 1 c24)) (* c24 o2)) 0)) (&lt;&lt; (VecMul (Vec (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c23 1) (Vec (- 1 c23) c12 (+ (* o4 (- 1 c24)) (* c24 o2)) 0)) 2)) (VecAdd (VecMul (Vec 1 (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c13) (VecMinus (VecMinus (Vec 1 1 0 (+ (* o4 (- 1 c14)) (* c14 o1))) (Vec c12 c13 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)))))))))))))) (&lt;&lt; (VecMul (Vec 1 (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c13) (VecMinus (VecMinus (Vec 1 1 0 (+ (* o4 (- 1 c14)) (* c14 o1))) (Vec c12 c13 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)))))))))))))) 2))) 1))</t>
+          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c23 1) (Vec (- 1 c23) c12 (+ (* o4 (- 1 c24)) (* c24 o2)) 0)) (&lt;&lt; (VecMul (Vec (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c23 1) (Vec (- 1 c23) c12 (+ (* o4 (- 1 c24)) (* c24 o2)) 0)) 2)) (VecAdd (VecMul (Vec 1 (+ (* o4 (- 1 c34)) (* c34 o3)) 1 (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- c13 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)) (VecMinus (Vec 1 1 0 (+ (* o4 (- 1 c14)) (* c14 o1))) (Vec c12 c13 0 0))) (&lt;&lt; (VecMul (Vec 1 (+ (* o4 (- 1 c34)) (* c34 o3)) 1 (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- c13 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)) (VecMinus (Vec 1 1 0 (+ (* o4 (- 1 c14)) (* c14 o1))) (Vec c12 c13 0 0))) 2))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c23 1) (Vec (- 1 c23) c12 (+ (* o4 (- 1 c24)) (* c24 o2)) 0)) (&lt;&lt; (VecMul (Vec (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c23 1) (Vec (- 1 c23) c12 (+ (* o4 (- 1 c24)) (* c24 o2)) 0)) 2)) (VecAdd (VecMul (Vec 1 (+ (* o4 (- 1 c34)) (* c34 o3)) 1 (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- c13 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)) (VecMinus (Vec 1 1 0 (+ (* o4 (- 1 c14)) (* c14 o1))) (Vec c12 c13 0 0))) (&lt;&lt; (VecMul (Vec 1 (+ (* o4 (- 1 c34)) (* c34 o3)) 1 (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- c13 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)) (VecMinus (Vec 1 1 0 (+ (* o4 (- 1 c14)) (* c14 o1))) (Vec c12 c13 0 0))) 2))) 1))</t>
         </is>
       </c>
       <c r="E84" t="n">
         <v>7012</v>
       </c>
       <c r="F84" t="n">
-        <v>4749</v>
+        <v>21541</v>
       </c>
       <c r="G84" t="n">
-        <v>32.27</v>
+        <v>-207.2</v>
       </c>
       <c r="H84" t="n">
         <v>110.93</v>
       </c>
       <c r="I84" t="n">
-        <v>124.11</v>
+        <v>190</v>
       </c>
       <c r="J84" t="b">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>175.89</v>
+        <v>110</v>
       </c>
       <c r="L84" t="n">
         <v>75</v>
@@ -3991,17 +3991,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 c23 1) (VecMinus (VecMinus (Vec 1 c12 (+ (* (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) (- 1 c13)) (* c13 (+ (* o2134 (- 1 c24)) (* c24 (+ (* (- 1 c14) (+ (* o4213 (- 1 c24)) (* c24 o2413))) (* c14 (+ (* o2143 (- 1 c34)) (* c34 o2134)))))))) 0) (Vec c23 0 0 0)) (VecMinus (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)))))))))))))) (&lt;&lt; (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 c23 1) (VecMinus (VecMinus (Vec 1 c12 (+ (* (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) (- 1 c13)) (* c13 (+ (* o2134 (- 1 c24)) (* c24 (+ (* (- 1 c14) (+ (* o4213 (- 1 c24)) (* c24 o2413))) (* c14 (+ (* o2143 (- 1 c34)) (* c34 o2134)))))))) 0) (Vec c23 0 0 0)) (VecMinus (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)))))))))))))) 2)) (Vec (- 1 c12) (+ (* (- 1 c13) (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124))))))) (* c13 (+ (* (- 1 c23) (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324))))))) (* c23 (+ (* o1234 (- 1 c14)) (* c14 (+ (* (- 1 c24) (+ (* o4123 (- 1 c14)) (* c14 o1423))) (* c24 (+ (* o1243 (- 1 c34)) (* c34 o1234)))))))))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 c23 1) (VecMinus (VecMinus (Vec 1 c12 (+ (* (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) (- 1 c13)) (* c13 (+ (* o2134 (- 1 c24)) (* c24 (+ (* (- 1 c14) (+ (* o4213 (- 1 c24)) (* c24 o2413))) (* c14 (+ (* o2143 (- 1 c34)) (* c34 o2134)))))))) 0) (Vec c23 0 0 0)) (VecMinus (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)))))))))))))) (&lt;&lt; (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 c23 1) (VecMinus (VecMinus (Vec 1 c12 (+ (* (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) (- 1 c13)) (* c13 (+ (* o2134 (- 1 c24)) (* c24 (+ (* (- 1 c14) (+ (* o4213 (- 1 c24)) (* c24 o2413))) (* c14 (+ (* o2143 (- 1 c34)) (* c34 o2134)))))))) 0) (Vec c23 0 0 0)) (VecMinus (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)))))))))))))) 2)) (Vec (- 1 c12) (+ (* (- 1 c13) (+ (* o3124 (- 1 c34)) (* c34 (+ (* (- 1 c14) (+ (* o4312 (- 1 c34)) (* c34 o3412))) (* c14 (+ (* o3142 (- 1 c24)) (* c24 o3124))))))) (* c13 (+ (* (- 1 c23) (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324))))))) (* c23 (+ (* o1234 (- 1 c14)) (* c14 (+ (* (- 1 c24) (+ (* o4123 (- 1 c14)) (* c14 o1423))) (* c24 (+ (* o1243 (- 1 c34)) (* c34 o1234)))))))))))) 1))</t>
+          <t>(VecAdd (VecMul (VecAdd (VecMul (VecAdd (VecMul (VecMinus (Vec o3214 0 0 0 0 0 (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 0 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 c34 0 0 0 0 0 c13 0)) (&lt;&lt; (VecMinus (Vec o3214 0 0 0 0 0 (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 0 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 c34 0 0 0 0 0 c13 0)) 8)) (VecMul (VecAdd (VecMul (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) (&lt;&lt; (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) 16)) (VecMul (Vec 1 1 1 1 1 1 1 1 c24 1 1 1 1 1 c24 1) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 o3241 1 1 1 1 1 (- 1 c14) 1) (Vec 0 0 0 0 0 0 0 0 (- 1 c14) 0 0 0 0 0 (+ (* o4213 (- 1 c24)) (* c24 o2413)) 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 c14 1 1 1 1 1 c14 1) (Vec c34 c12 c23 0 (- 1 c23) 1 c13 1 o3214 1 1 1 1 1 (+ (* o2143 (- 1 c34)) (* c34 o2134)) 1))))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) (&lt;&lt; (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) 16)) (VecMul (Vec 1 1 1 1 1 1 1 1 c24 1 1 1 1 1 c24 1) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 o3241 1 1 1 1 1 (- 1 c14) 1) (Vec 0 0 0 0 0 0 0 0 (- 1 c14) 0 0 0 0 0 (+ (* o4213 (- 1 c24)) (* c24 o2413)) 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 c14 1 1 1 1 1 c14 1) (Vec c34 c12 c23 0 (- 1 c23) 1 c13 1 o3214 1 1 1 1 1 (+ (* o2143 (- 1 c34)) (* c34 o2134)) 1))))) 8))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec o3214 0 0 0 0 0 (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 0 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 c34 0 0 0 0 0 c13 0)) (&lt;&lt; (VecMinus (Vec o3214 0 0 0 0 0 (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 0 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 c34 0 0 0 0 0 c13 0)) 8)) (VecMul (VecAdd (VecMul (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) (&lt;&lt; (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) 16)) (VecMul (Vec 1 1 1 1 1 1 1 1 c24 1 1 1 1 1 c24 1) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 o3241 1 1 1 1 1 (- 1 c14) 1) (Vec 0 0 0 0 0 0 0 0 (- 1 c14) 0 0 0 0 0 (+ (* o4213 (- 1 c24)) (* c24 o2413)) 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 c14 1 1 1 1 1 c14 1) (Vec c34 c12 c23 0 (- 1 c23) 1 c13 1 o3214 1 1 1 1 1 (+ (* o2143 (- 1 c34)) (* c34 o2134)) 1))))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) (&lt;&lt; (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) 16)) (VecMul (Vec 1 1 1 1 1 1 1 1 c24 1 1 1 1 1 c24 1) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 o3241 1 1 1 1 1 (- 1 c14) 1) (Vec 0 0 0 0 0 0 0 0 (- 1 c14) 0 0 0 0 0 (+ (* o4213 (- 1 c24)) (* c24 o2413)) 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 c14 1 1 1 1 1 c14 1) (Vec c34 c12 c23 0 (- 1 c23) 1 c13 1 o3214 1 1 1 1 1 (+ (* o2143 (- 1 c34)) (* c34 o2134)) 1))))) 8))) 4)) (&lt;&lt; (VecMul (VecAdd (VecMul (VecMinus (Vec o3214 0 0 0 0 0 (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 0 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 c34 0 0 0 0 0 c13 0)) (&lt;&lt; (VecMinus (Vec o3214 0 0 0 0 0 (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 0 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 c34 0 0 0 0 0 c13 0)) 8)) (VecMul (VecAdd (VecMul (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) (&lt;&lt; (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) 16)) (VecMul (Vec 1 1 1 1 1 1 1 1 c24 1 1 1 1 1 c24 1) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 o3241 1 1 1 1 1 (- 1 c14) 1) (Vec 0 0 0 0 0 0 0 0 (- 1 c14) 0 0 0 0 0 (+ (* o4213 (- 1 c24)) (* c24 o2413)) 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 c14 1 1 1 1 1 c14 1) (Vec c34 c12 c23 0 (- 1 c23) 1 c13 1 o3214 1 1 1 1 1 (+ (* o2143 (- 1 c34)) (* c34 o2134)) 1))))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) (&lt;&lt; (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) 16)) (VecMul (Vec 1 1 1 1 1 1 1 1 c24 1 1 1 1 1 c24 1) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 o3241 1 1 1 1 1 (- 1 c14) 1) (Vec 0 0 0 0 0 0 0 0 (- 1 c14) 0 0 0 0 0 (+ (* o4213 (- 1 c24)) (* c24 o2413)) 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 c14 1 1 1 1 1 c14 1) (Vec c34 c12 c23 0 (- 1 c23) 1 c13 1 o3214 1 1 1 1 1 (+ (* o2143 (- 1 c34)) (* c34 o2134)) 1))))) 8))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec o3214 0 0 0 0 0 (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 0 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 c34 0 0 0 0 0 c13 0)) (&lt;&lt; (VecMinus (Vec o3214 0 0 0 0 0 (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 0 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 c34 0 0 0 0 0 c13 0)) 8)) (VecMul (VecAdd (VecMul (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) (&lt;&lt; (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) 16)) (VecMul (Vec 1 1 1 1 1 1 1 1 c24 1 1 1 1 1 c24 1) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 o3241 1 1 1 1 1 (- 1 c14) 1) (Vec 0 0 0 0 0 0 0 0 (- 1 c14) 0 0 0 0 0 (+ (* o4213 (- 1 c24)) (* c24 o2413)) 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 c14 1 1 1 1 1 c14 1) (Vec c34 c12 c23 0 (- 1 c23) 1 c13 1 o3214 1 1 1 1 1 (+ (* o2143 (- 1 c34)) (* c34 o2134)) 1))))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) (&lt;&lt; (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) 16)) (VecMul (Vec 1 1 1 1 1 1 1 1 c24 1 1 1 1 1 c24 1) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 o3241 1 1 1 1 1 (- 1 c14) 1) (Vec 0 0 0 0 0 0 0 0 (- 1 c14) 0 0 0 0 0 (+ (* o4213 (- 1 c24)) (* c24 o2413)) 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 c14 1 1 1 1 1 c14 1) (Vec c34 c12 c23 0 (- 1 c23) 1 c13 1 o3214 1 1 1 1 1 (+ (* o2143 (- 1 c34)) (* c34 o2134)) 1))))) 8))) 4)) 2)) (VecAdd (VecMul (VecMinus (VecAdd (VecMul (Vec 1 1 1 1 1 o3124 1 (- 1 c23)) (Vec 0 0 0 0 0 (- 1 c34) 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec 1 1 1 1 1 c34 1 c23) (VecAdd (VecMul (Vec 1 1 1 1 1 (- 1 c14) 1 o1234) (Vec 0 0 0 0 0 (+ (* o4312 (- 1 c34)) (* c34 o3412)) 0 (- 1 c14))) (VecMul (Vec 1 1 1 1 1 c14 1 c14) (VecAdd (VecMul (Vec 1 1 1 1 1 o3142 1 (- 1 c24)) (Vec 0 0 0 0 0 (- 1 c24) 0 (+ (* o4123 (- 1 c14)) (* c14 o1423)))) (VecMul (Vec 1 1 1 1 1 c24 1 c24) (Vec 1 1 0 c13 1 o3124 1 (+ (* o1243 (- 1 c34)) (* c34 o1234))))))))) (Vec c12 c13 0 0 0 0 0 0)) (&lt;&lt; (VecMinus (VecAdd (VecMul (Vec 1 1 1 1 1 o3124 1 (- 1 c23)) (Vec 0 0 0 0 0 (- 1 c34) 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec 1 1 1 1 1 c34 1 c23) (VecAdd (VecMul (Vec 1 1 1 1 1 (- 1 c14) 1 o1234) (Vec 0 0 0 0 0 (+ (* o4312 (- 1 c34)) (* c34 o3412)) 0 (- 1 c14))) (VecMul (Vec 1 1 1 1 1 c14 1 c14) (VecAdd (VecMul (Vec 1 1 1 1 1 o3142 1 (- 1 c24)) (Vec 0 0 0 0 0 (- 1 c24) 0 (+ (* o4123 (- 1 c14)) (* c14 o1423)))) (VecMul (Vec 1 1 1 1 1 c24 1 c24) (Vec 1 1 0 c13 1 o3124 1 (+ (* o1243 (- 1 c34)) (* c34 o1234))))))))) (Vec c12 c13 0 0 0 0 0 0)) 4)) (&lt;&lt; (VecMul (VecMinus (VecAdd (VecMul (Vec 1 1 1 1 1 o3124 1 (- 1 c23)) (Vec 0 0 0 0 0 (- 1 c34) 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec 1 1 1 1 1 c34 1 c23) (VecAdd (VecMul (Vec 1 1 1 1 1 (- 1 c14) 1 o1234) (Vec 0 0 0 0 0 (+ (* o4312 (- 1 c34)) (* c34 o3412)) 0 (- 1 c14))) (VecMul (Vec 1 1 1 1 1 c14 1 c14) (VecAdd (VecMul (Vec 1 1 1 1 1 o3142 1 (- 1 c24)) (Vec 0 0 0 0 0 (- 1 c24) 0 (+ (* o4123 (- 1 c14)) (* c14 o1423)))) (VecMul (Vec 1 1 1 1 1 c24 1 c24) (Vec 1 1 0 c13 1 o3124 1 (+ (* o1243 (- 1 c34)) (* c34 o1234))))))))) (Vec c12 c13 0 0 0 0 0 0)) (&lt;&lt; (VecMinus (VecAdd (VecMul (Vec 1 1 1 1 1 o3124 1 (- 1 c23)) (Vec 0 0 0 0 0 (- 1 c34) 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec 1 1 1 1 1 c34 1 c23) (VecAdd (VecMul (Vec 1 1 1 1 1 (- 1 c14) 1 o1234) (Vec 0 0 0 0 0 (+ (* o4312 (- 1 c34)) (* c34 o3412)) 0 (- 1 c14))) (VecMul (Vec 1 1 1 1 1 c14 1 c14) (VecAdd (VecMul (Vec 1 1 1 1 1 o3142 1 (- 1 c24)) (Vec 0 0 0 0 0 (- 1 c24) 0 (+ (* o4123 (- 1 c14)) (* c14 o1423)))) (VecMul (Vec 1 1 1 1 1 c24 1 c24) (Vec 1 1 0 c13 1 o3124 1 (+ (* o1243 (- 1 c34)) (* c34 o1234))))))))) (Vec c12 c13 0 0 0 0 0 0)) 4)) 2))) (&lt;&lt; (VecMul (VecAdd (VecMul (VecAdd (VecMul (VecMinus (Vec o3214 0 0 0 0 0 (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 0 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 c34 0 0 0 0 0 c13 0)) (&lt;&lt; (VecMinus (Vec o3214 0 0 0 0 0 (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 0 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 c34 0 0 0 0 0 c13 0)) 8)) (VecMul (VecAdd (VecMul (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) (&lt;&lt; (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) 16)) (VecMul (Vec 1 1 1 1 1 1 1 1 c24 1 1 1 1 1 c24 1) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 o3241 1 1 1 1 1 (- 1 c14) 1) (Vec 0 0 0 0 0 0 0 0 (- 1 c14) 0 0 0 0 0 (+ (* o4213 (- 1 c24)) (* c24 o2413)) 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 c14 1 1 1 1 1 c14 1) (Vec c34 c12 c23 0 (- 1 c23) 1 c13 1 o3214 1 1 1 1 1 (+ (* o2143 (- 1 c34)) (* c34 o2134)) 1))))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) (&lt;&lt; (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) 16)) (VecMul (Vec 1 1 1 1 1 1 1 1 c24 1 1 1 1 1 c24 1) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 o3241 1 1 1 1 1 (- 1 c14) 1) (Vec 0 0 0 0 0 0 0 0 (- 1 c14) 0 0 0 0 0 (+ (* o4213 (- 1 c24)) (* c24 o2413)) 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 c14 1 1 1 1 1 c14 1) (Vec c34 c12 c23 0 (- 1 c23) 1 c13 1 o3214 1 1 1 1 1 (+ (* o2143 (- 1 c34)) (* c34 o2134)) 1))))) 8))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec o3214 0 0 0 0 0 (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 0 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 c34 0 0 0 0 0 c13 0)) (&lt;&lt; (VecMinus (Vec o3214 0 0 0 0 0 (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 0 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 c34 0 0 0 0 0 c13 0)) 8)) (VecMul (VecAdd (VecMul (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) (&lt;&lt; (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) 16)) (VecMul (Vec 1 1 1 1 1 1 1 1 c24 1 1 1 1 1 c24 1) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 o3241 1 1 1 1 1 (- 1 c14) 1) (Vec 0 0 0 0 0 0 0 0 (- 1 c14) 0 0 0 0 0 (+ (* o4213 (- 1 c24)) (* c24 o2413)) 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 c14 1 1 1 1 1 c14 1) (Vec c34 c12 c23 0 (- 1 c23) 1 c13 1 o3214 1 1 1 1 1 (+ (* o2143 (- 1 c34)) (* c34 o2134)) 1))))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) (&lt;&lt; (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) 16)) (VecMul (Vec 1 1 1 1 1 1 1 1 c24 1 1 1 1 1 c24 1) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 o3241 1 1 1 1 1 (- 1 c14) 1) (Vec 0 0 0 0 0 0 0 0 (- 1 c14) 0 0 0 0 0 (+ (* o4213 (- 1 c24)) (* c24 o2413)) 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 c14 1 1 1 1 1 c14 1) (Vec c34 c12 c23 0 (- 1 c23) 1 c13 1 o3214 1 1 1 1 1 (+ (* o2143 (- 1 c34)) (* c34 o2134)) 1))))) 8))) 4)) (&lt;&lt; (VecMul (VecAdd (VecMul (VecMinus (Vec o3214 0 0 0 0 0 (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 0 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 c34 0 0 0 0 0 c13 0)) (&lt;&lt; (VecMinus (Vec o3214 0 0 0 0 0 (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 0 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 c34 0 0 0 0 0 c13 0)) 8)) (VecMul (VecAdd (VecMul (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) (&lt;&lt; (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) 16)) (VecMul (Vec 1 1 1 1 1 1 1 1 c24 1 1 1 1 1 c24 1) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 o3241 1 1 1 1 1 (- 1 c14) 1) (Vec 0 0 0 0 0 0 0 0 (- 1 c14) 0 0 0 0 0 (+ (* o4213 (- 1 c24)) (* c24 o2413)) 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 c14 1 1 1 1 1 c14 1) (Vec c34 c12 c23 0 (- 1 c23) 1 c13 1 o3214 1 1 1 1 1 (+ (* o2143 (- 1 c34)) (* c34 o2134)) 1))))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) (&lt;&lt; (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) 16)) (VecMul (Vec 1 1 1 1 1 1 1 1 c24 1 1 1 1 1 c24 1) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 o3241 1 1 1 1 1 (- 1 c14) 1) (Vec 0 0 0 0 0 0 0 0 (- 1 c14) 0 0 0 0 0 (+ (* o4213 (- 1 c24)) (* c24 o2413)) 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 c14 1 1 1 1 1 c14 1) (Vec c34 c12 c23 0 (- 1 c23) 1 c13 1 o3214 1 1 1 1 1 (+ (* o2143 (- 1 c34)) (* c34 o2134)) 1))))) 8))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec o3214 0 0 0 0 0 (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 0 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 c34 0 0 0 0 0 c13 0)) (&lt;&lt; (VecMinus (Vec o3214 0 0 0 0 0 (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) 0 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 c34 0 0 0 0 0 c13 0)) 8)) (VecMul (VecAdd (VecMul (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) (&lt;&lt; (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) 16)) (VecMul (Vec 1 1 1 1 1 1 1 1 c24 1 1 1 1 1 c24 1) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 o3241 1 1 1 1 1 (- 1 c14) 1) (Vec 0 0 0 0 0 0 0 0 (- 1 c14) 0 0 0 0 0 (+ (* o4213 (- 1 c24)) (* c24 o2413)) 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 c14 1 1 1 1 1 c14 1) (Vec c34 c12 c23 0 (- 1 c23) 1 c13 1 o3214 1 1 1 1 1 (+ (* o2143 (- 1 c34)) (* c34 o2134)) 1))))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) (&lt;&lt; (VecMinus (Vec 0 0 0 0 0 0 0 0 (+ (* o4321 (- 1 c34)) (* c34 o3421)) 0 0 0 0 0 o2134 0 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 0 c24 0 0 0 0 0 c24 0)) 16)) (VecMul (Vec 1 1 1 1 1 1 1 1 c24 1 1 1 1 1 c24 1) (VecAdd (VecMul (Vec 1 1 1 1 1 1 1 1 o3241 1 1 1 1 1 (- 1 c14) 1) (Vec 0 0 0 0 0 0 0 0 (- 1 c14) 0 0 0 0 0 (+ (* o4213 (- 1 c24)) (* c24 o2413)) 0)) (VecMul (Vec 1 1 1 1 1 1 1 1 c14 1 1 1 1 1 c14 1) (Vec c34 c12 c23 0 (- 1 c23) 1 c13 1 o3214 1 1 1 1 1 (+ (* o2143 (- 1 c34)) (* c34 o2134)) 1))))) 8))) 4)) 2)) (VecAdd (VecMul (VecMinus (VecAdd (VecMul (Vec 1 1 1 1 1 o3124 1 (- 1 c23)) (Vec 0 0 0 0 0 (- 1 c34) 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec 1 1 1 1 1 c34 1 c23) (VecAdd (VecMul (Vec 1 1 1 1 1 (- 1 c14) 1 o1234) (Vec 0 0 0 0 0 (+ (* o4312 (- 1 c34)) (* c34 o3412)) 0 (- 1 c14))) (VecMul (Vec 1 1 1 1 1 c14 1 c14) (VecAdd (VecMul (Vec 1 1 1 1 1 o3142 1 (- 1 c24)) (Vec 0 0 0 0 0 (- 1 c24) 0 (+ (* o4123 (- 1 c14)) (* c14 o1423)))) (VecMul (Vec 1 1 1 1 1 c24 1 c24) (Vec 1 1 0 c13 1 o3124 1 (+ (* o1243 (- 1 c34)) (* c34 o1234))))))))) (Vec c12 c13 0 0 0 0 0 0)) (&lt;&lt; (VecMinus (VecAdd (VecMul (Vec 1 1 1 1 1 o3124 1 (- 1 c23)) (Vec 0 0 0 0 0 (- 1 c34) 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec 1 1 1 1 1 c34 1 c23) (VecAdd (VecMul (Vec 1 1 1 1 1 (- 1 c14) 1 o1234) (Vec 0 0 0 0 0 (+ (* o4312 (- 1 c34)) (* c34 o3412)) 0 (- 1 c14))) (VecMul (Vec 1 1 1 1 1 c14 1 c14) (VecAdd (VecMul (Vec 1 1 1 1 1 o3142 1 (- 1 c24)) (Vec 0 0 0 0 0 (- 1 c24) 0 (+ (* o4123 (- 1 c14)) (* c14 o1423)))) (VecMul (Vec 1 1 1 1 1 c24 1 c24) (Vec 1 1 0 c13 1 o3124 1 (+ (* o1243 (- 1 c34)) (* c34 o1234))))))))) (Vec c12 c13 0 0 0 0 0 0)) 4)) (&lt;&lt; (VecMul (VecMinus (VecAdd (VecMul (Vec 1 1 1 1 1 o3124 1 (- 1 c23)) (Vec 0 0 0 0 0 (- 1 c34) 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec 1 1 1 1 1 c34 1 c23) (VecAdd (VecMul (Vec 1 1 1 1 1 (- 1 c14) 1 o1234) (Vec 0 0 0 0 0 (+ (* o4312 (- 1 c34)) (* c34 o3412)) 0 (- 1 c14))) (VecMul (Vec 1 1 1 1 1 c14 1 c14) (VecAdd (VecMul (Vec 1 1 1 1 1 o3142 1 (- 1 c24)) (Vec 0 0 0 0 0 (- 1 c24) 0 (+ (* o4123 (- 1 c14)) (* c14 o1423)))) (VecMul (Vec 1 1 1 1 1 c24 1 c24) (Vec 1 1 0 c13 1 o3124 1 (+ (* o1243 (- 1 c34)) (* c34 o1234))))))))) (Vec c12 c13 0 0 0 0 0 0)) (&lt;&lt; (VecMinus (VecAdd (VecMul (Vec 1 1 1 1 1 o3124 1 (- 1 c23)) (Vec 0 0 0 0 0 (- 1 c34) 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))) (VecMul (Vec 1 1 1 1 1 c34 1 c23) (VecAdd (VecMul (Vec 1 1 1 1 1 (- 1 c14) 1 o1234) (Vec 0 0 0 0 0 (+ (* o4312 (- 1 c34)) (* c34 o3412)) 0 (- 1 c14))) (VecMul (Vec 1 1 1 1 1 c14 1 c14) (VecAdd (VecMul (Vec 1 1 1 1 1 o3142 1 (- 1 c24)) (Vec 0 0 0 0 0 (- 1 c24) 0 (+ (* o4123 (- 1 c14)) (* c14 o1423)))) (VecMul (Vec 1 1 1 1 1 c24 1 c24) (Vec 1 1 0 c13 1 o3124 1 (+ (* o1243 (- 1 c34)) (* c34 o1234))))))))) (Vec c12 c13 0 0 0 0 0 0)) 4)) 2))) 1))</t>
         </is>
       </c>
       <c r="E85" t="n">
         <v>29021</v>
       </c>
       <c r="F85" t="n">
-        <v>27597</v>
+        <v>18613</v>
       </c>
       <c r="G85" t="n">
-        <v>4.91</v>
+        <v>35.86</v>
       </c>
       <c r="H85" t="n">
         <v>218.27</v>
@@ -4016,7 +4016,7 @@
         <v>75.73999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>75</v>
+        <v>28</v>
       </c>
     </row>
     <row r="86">
@@ -4033,29 +4033,29 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>(VecMul (VecAdd (VecAdd (Vec 0 x10121 0 x10181) (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) x10125 1 1) (Vec (* x10117 x10119) (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))) 0 x10183))) (&lt;&lt; (VecAdd (Vec 0 x10121 0 x10181) (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) x10125 1 1) (Vec (* x10117 x10119) (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))) 0 x10183))) 2)) (&lt;&lt; (VecAdd (VecAdd (Vec 0 x10121 0 x10181) (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) x10125 1 1) (Vec (* x10117 x10119) (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))) 0 x10183))) (&lt;&lt; (VecAdd (Vec 0 x10121 0 x10181) (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) x10125 1 1) (Vec (* x10117 x10119) (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))) 0 x10183))) 2)) 1))</t>
+          <t>(VecMul (VecAdd (VecAdd (Vec 0 x10121 0 x10181) (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) x10125 1 1) (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (Vec 0 0 0 0) (Vec 0 (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (VecAdd (Vec 0 0 0 0) (Vec 0 0 0 (+ 0 0)))) (Vec 0 (* (* x10146 x10147) (* (+ x10149 x10150) x10152)) 0 (+ (+ 0 0) (+ 0 0)))) (VecAdd (Vec 0 (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) 0 0) (Vec (* x10117 x10119) (+ (+ x10170 x10173) (+ x10176 x10178)) 0 x10183))))) (&lt;&lt; (VecAdd (Vec 0 x10121 0 x10181) (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) x10125 1 1) (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (Vec 0 0 0 0) (Vec 0 (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (VecAdd (Vec 0 0 0 0) (Vec 0 0 0 (+ 0 0)))) (Vec 0 (* (* x10146 x10147) (* (+ x10149 x10150) x10152)) 0 (+ (+ 0 0) (+ 0 0)))) (VecAdd (Vec 0 (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) 0 0) (Vec (* x10117 x10119) (+ (+ x10170 x10173) (+ x10176 x10178)) 0 x10183))))) 2)) (&lt;&lt; (VecAdd (VecAdd (Vec 0 x10121 0 x10181) (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) x10125 1 1) (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (Vec 0 0 0 0) (Vec 0 (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (VecAdd (Vec 0 0 0 0) (Vec 0 0 0 (+ 0 0)))) (Vec 0 (* (* x10146 x10147) (* (+ x10149 x10150) x10152)) 0 (+ (+ 0 0) (+ 0 0)))) (VecAdd (Vec 0 (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) 0 0) (Vec (* x10117 x10119) (+ (+ x10170 x10173) (+ x10176 x10178)) 0 x10183))))) (&lt;&lt; (VecAdd (Vec 0 x10121 0 x10181) (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) x10125 1 1) (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (Vec 0 0 0 0) (Vec 0 (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (VecAdd (Vec 0 0 0 0) (Vec 0 0 0 (+ 0 0)))) (Vec 0 (* (* x10146 x10147) (* (+ x10149 x10150) x10152)) 0 (+ (+ 0 0) (+ 0 0)))) (VecAdd (Vec 0 (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) 0 0) (Vec (* x10117 x10119) (+ (+ x10170 x10173) (+ x10176 x10178)) 0 x10183))))) 2)) 1))</t>
         </is>
       </c>
       <c r="E86" t="n">
         <v>8018</v>
       </c>
       <c r="F86" t="n">
-        <v>6827</v>
+        <v>7097</v>
       </c>
       <c r="G86" t="n">
-        <v>14.85</v>
+        <v>11.49</v>
       </c>
       <c r="H86" t="n">
         <v>182.49</v>
       </c>
       <c r="I86" t="n">
-        <v>184.88</v>
+        <v>193.27</v>
       </c>
       <c r="J86" t="b">
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>115.12</v>
+        <v>106.73</v>
       </c>
       <c r="L86" t="n">
         <v>75</v>
@@ -4075,32 +4075,32 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>(VecMul (VecAdd (VecMul (VecMul (VecMul (Vec x9604 x9634) (Vec x9605 x9635)) (VecMul (Vec x9607 x9637) (Vec x9608 x9638))) (VecMul (VecMul (Vec x9611 x9641) (Vec x9612 x9642)) (VecMul (Vec x9614 x9644) (Vec x9615 x9645)))) (VecMul (VecMul (VecMul (Vec x9619 x9649) (Vec x9620 x9650)) (VecMul (Vec x9622 x9652) (Vec x9623 x9653))) (VecMul (VecMul (Vec x9626 x9656) (Vec x9627 x9657)) (VecMul (Vec x9629 x9659) (Vec x9630 x9660))))) (&lt;&lt; (VecAdd (VecMul (VecMul (VecMul (Vec x9604 x9634) (Vec x9605 x9635)) (VecMul (Vec x9607 x9637) (Vec x9608 x9638))) (VecMul (VecMul (Vec x9611 x9641) (Vec x9612 x9642)) (VecMul (Vec x9614 x9644) (Vec x9615 x9645)))) (VecMul (VecMul (VecMul (Vec x9619 x9649) (Vec x9620 x9650)) (VecMul (Vec x9622 x9652) (Vec x9623 x9653))) (VecMul (VecMul (Vec x9626 x9656) (Vec x9627 x9657)) (VecMul (Vec x9629 x9659) (Vec x9630 x9660))))) 1))</t>
+          <t>(VecMul (VecAdd (VecMul (VecMul (VecMul (VecMul (Vec x9604 x9634) (Vec x9605 x9635)) (VecMul (Vec x9607 x9637) (Vec x9608 x9638))) (Vec x9611 x9641)) (VecMul (Vec x9612 x9642) (VecMul (Vec x9614 x9644) (Vec x9615 x9645)))) (VecMul (VecMul (VecMul (VecMul (Vec x9619 x9649) (Vec x9620 x9650)) (VecMul (Vec x9622 x9652) (Vec x9623 x9653))) (Vec x9626 x9656)) (VecMul (Vec x9627 x9657) (VecMul (Vec x9629 x9659) (Vec x9630 x9660))))) (&lt;&lt; (VecAdd (VecMul (VecMul (VecMul (VecMul (Vec x9604 x9634) (Vec x9605 x9635)) (VecMul (Vec x9607 x9637) (Vec x9608 x9638))) (Vec x9611 x9641)) (VecMul (Vec x9612 x9642) (VecMul (Vec x9614 x9644) (Vec x9615 x9645)))) (VecMul (VecMul (VecMul (VecMul (Vec x9619 x9649) (Vec x9620 x9650)) (VecMul (Vec x9622 x9652) (Vec x9623 x9653))) (Vec x9626 x9656)) (VecMul (Vec x9627 x9657) (VecMul (Vec x9629 x9659) (Vec x9630 x9660))))) 1))</t>
         </is>
       </c>
       <c r="E87" t="n">
         <v>7761</v>
       </c>
       <c r="F87" t="n">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="G87" t="n">
-        <v>79.84999999999999</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="H87" t="n">
         <v>141.92</v>
       </c>
       <c r="I87" t="n">
-        <v>143.12</v>
+        <v>177.7</v>
       </c>
       <c r="J87" t="b">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>156.88</v>
+        <v>122.3</v>
       </c>
       <c r="L87" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88">
@@ -4117,17 +4117,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (Vec in_1_1 (+ in_1_2 in_1_1) in_1_2 (+ in_2_1 in_2_0) (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_2_2 in_2_1) in_2_1 (+ in_2_2 in_2_1) in_2_2) (Vec in_1_0 (+ in_1_0 in_0_2) in_1_1 (+ in_1_1 in_1_0) (+ in_1_2 in_1_1) (+ in_1_2 in_1_1) in_2_0 (+ in_2_0 in_1_2) in_2_1)) (VecAdd (Vec in_0_1 in_0_1 in_0_2 in_0_1 (+ in_1_0 in_0_2) in_0_2 in_1_1 in_1_1 in_1_2) (Vec in_0_0 in_0_0 in_0_1 in_0_0 (+ in_0_1 in_0_0) in_0_1 in_1_0 in_1_0 in_1_1)))</t>
+          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 0 in_2_1 in_2_2 in_2_2 0 in_2_2 0) (Vec in_1_1 in_1_1 in_1_2 in_2_0 (+ in_2_1 in_2_0) in_2_1 in_2_1 in_2_1 in_2_2)) (VecAdd (Vec 0 in_1_0 0 in_1_1 in_1_2 in_1_2 0 in_2_0 0) (Vec in_1_0 in_0_2 in_1_1 in_1_0 in_1_1 in_1_1 in_2_0 in_1_2 in_2_1))) (VecAdd (Vec in_0_1 in_0_1 in_0_2 in_0_1 (+ in_1_0 in_0_2) in_0_2 in_1_1 in_1_1 in_1_2) (Vec in_0_0 in_0_0 in_0_1 in_0_0 (+ in_0_1 in_0_0) in_0_1 in_1_0 in_1_0 in_1_1)))</t>
         </is>
       </c>
       <c r="E88" t="n">
         <v>10006</v>
       </c>
       <c r="F88" t="n">
-        <v>3259</v>
+        <v>761</v>
       </c>
       <c r="G88" t="n">
-        <v>67.43000000000001</v>
+        <v>92.39</v>
       </c>
       <c r="H88" t="n">
         <v>7.19</v>
@@ -4142,7 +4142,7 @@
         <v>8999992.810000001</v>
       </c>
       <c r="L88" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89">
@@ -4159,17 +4159,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_2 in_3_3 in_3_4 in_3_4 in_4_1 in_4_2 in_4_3 in_4_4 in_4_4 0 in_4_2 in_4_3 in_4_4 0) (VecAdd (Vec 0 0 0 0 0 0 in_2_1 in_2_2 in_2_3 0 0 in_3_1 in_3_2 in_3_3 0 0 in_4_1 in_4_2 in_4_3 0 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_1_4 in_2_0 in_2_0 in_2_1 in_2_2 in_2_3 in_3_0 in_3_0 in_3_1 in_3_2 in_3_3 in_4_0 in_4_0 in_4_1 in_4_2 in_4_3 in_4_1 in_4_1 in_4_2 in_4_3 in_4_4))) (VecAdd (Vec 0 in_1_0 in_1_1 in_1_2 0 in_1_1 in_1_2 in_1_3 in_1_4 in_1_4 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_2 in_3_3 in_3_4 in_3_4 0 in_4_0 in_4_1 in_4_2 0) (Vec in_1_0 in_0_2 in_0_3 in_0_4 in_1_3 in_1_0 in_1_1 in_1_2 in_1_3 in_1_3 in_2_0 in_2_1 in_2_2 in_2_3 in_2_3 in_3_0 in_3_1 in_3_2 in_3_3 in_3_3 in_4_0 in_3_2 in_3_3 in_3_4 in_4_3))) (VecAdd (Vec in_0_1 in_0_1 in_0_2 in_0_3 in_0_4 in_0_1 (+ in_1_0 in_0_2) (+ in_1_1 in_0_3) (+ in_1_2 in_0_4) in_0_4 in_1_1 (+ in_2_0 in_1_2) (+ in_2_1 in_1_3) (+ in_2_2 in_1_4) in_1_4 in_2_1 (+ in_3_0 in_2_2) (+ in_3_1 in_2_3) (+ in_3_2 in_2_4) in_2_4 in_3_1 in_3_1 in_3_2 in_3_3 in_3_4) (Vec in_0_0 in_0_0 in_0_1 in_0_2 in_0_3 in_0_0 (+ in_0_1 in_0_0) (+ in_0_2 in_0_1) (+ in_0_3 in_0_2) in_0_3 in_1_0 (+ in_1_1 in_1_0) (+ in_1_2 in_1_1) (+ in_1_3 in_1_2) in_1_3 in_2_0 (+ in_2_1 in_2_0) (+ in_2_2 in_2_1) (+ in_2_3 in_2_2) in_2_3 in_3_0 in_3_0 in_3_1 in_3_2 in_3_3)))</t>
+          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_2 in_3_3 in_3_4 in_3_4 in_4_1 in_4_2 in_4_3 in_4_4 in_4_4 0 in_4_2 in_4_3 in_4_4 0) (VecAdd (Vec 0 0 0 0 0 0 in_2_1 in_2_2 in_2_3 0 0 in_3_1 in_3_2 in_3_3 0 0 in_4_1 in_4_2 in_4_3 0 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_1_4 in_2_0 in_2_0 in_2_1 in_2_2 in_2_3 in_3_0 in_3_0 in_3_1 in_3_2 in_3_3 in_4_0 in_4_0 in_4_1 in_4_2 in_4_3 in_4_1 in_4_1 in_4_2 in_4_3 in_4_4))) (VecAdd (Vec 0 in_1_0 in_1_1 in_1_2 0 in_1_1 in_1_2 in_1_3 in_1_4 in_1_4 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_2 in_3_3 in_3_4 in_3_4 0 in_4_0 in_4_1 in_4_2 0) (Vec in_1_0 in_0_2 in_0_3 in_0_4 in_1_3 in_1_0 in_1_1 in_1_2 in_1_3 in_1_3 in_2_0 in_2_1 in_2_2 in_2_3 in_2_3 in_3_0 in_3_1 in_3_2 in_3_3 in_3_3 in_4_0 in_3_2 in_3_3 in_3_4 in_4_3))) (VecAdd (VecAdd (Vec 0 0 0 0 0 0 in_1_0 in_1_1 in_1_2 0 0 in_2_0 in_2_1 in_2_2 0 0 in_3_0 in_3_1 in_3_2 0 0 0 0 0 0) (Vec in_0_1 in_0_1 in_0_2 in_0_3 in_0_4 in_0_1 in_0_2 in_0_3 in_0_4 in_0_4 in_1_1 in_1_2 in_1_3 in_1_4 in_1_4 in_2_1 in_2_2 in_2_3 in_2_4 in_2_4 in_3_1 in_3_1 in_3_2 in_3_3 in_3_4)) (VecAdd (Vec 0 0 0 0 0 0 in_0_1 in_0_2 in_0_3 0 0 in_1_1 in_1_2 in_1_3 0 0 in_2_1 in_2_2 in_2_3 0 0 0 0 0 0) (Vec in_0_0 in_0_0 in_0_1 in_0_2 in_0_3 in_0_0 in_0_0 in_0_1 in_0_2 in_0_3 in_1_0 in_1_0 in_1_1 in_1_2 in_1_3 in_2_0 in_2_0 in_2_1 in_2_2 in_2_3 in_3_0 in_3_0 in_3_1 in_3_2 in_3_3))))</t>
         </is>
       </c>
       <c r="E89" t="n">
         <v>36006</v>
       </c>
       <c r="F89" t="n">
-        <v>4512</v>
+        <v>14</v>
       </c>
       <c r="G89" t="n">
-        <v>87.47</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="H89" t="n">
         <v>7.19</v>
@@ -4184,7 +4184,7 @@
         <v>8999992.810000001</v>
       </c>
       <c r="L89" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90">
@@ -4201,17 +4201,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3 v2_4 v2_5 v2_6 v2_7) (VecAdd (Vec 2 2 2 2 2 2 2 2) (Vec (* v1_0 5) (* v1_1 5) (* v1_2 5) (* v1_3 5) (* v1_4 5) (* v1_5 5) (* v1_6 5) (* v1_7 5))))</t>
+          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3 v2_4 v2_5 v2_6 v2_7) (VecAdd (Vec 2 2 2 2 2 2 2 2) (VecMul (Vec v1_0 v1_1 v1_2 v1_3 v1_4 v1_5 v1_6 v1_7) (Vec 5 5 5 5 5 5 5 5))))</t>
         </is>
       </c>
       <c r="E90" t="n">
         <v>6006</v>
       </c>
       <c r="F90" t="n">
-        <v>2008</v>
+        <v>108</v>
       </c>
       <c r="G90" t="n">
-        <v>66.56999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="H90" t="n">
         <v>39.37</v>
@@ -4226,7 +4226,7 @@
         <v>8999960.630000001</v>
       </c>
       <c r="L90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
@@ -4285,32 +4285,32 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( - ( + v1_0 v2_0 ) ( * ( * v1_0 v2_0 ) 2 ) ) ( - ( + v1_1 v2_1 ) ( * 2 ( * v1_1 v2_1 ) ) ) ) ( + ( - ( + v1_2 v2_2 ) ( * 2 ( * v1_2 v2_2 ) ) ) ( - ( + v1_3 v2_3 ) ( * 2 ( * v1_3 v2_3 ) ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2) (Vec v2_0 v2_2)) (VecMul (VecMul (Vec v1_0 2 v2_0 1) (&lt;&lt; (Vec v1_0 2 v2_0 1) 2)) (VecMul (Vec 2 v1_2 1 v2_2) (&lt;&lt; (Vec 2 v1_2 1 v2_2) 2)))) (VecMinus (VecAdd (Vec v1_1 v1_3) (Vec v2_1 v2_3)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_3) (Vec v2_1 v2_3))))) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2) (Vec v2_0 v2_2)) (VecMul (VecMul (Vec v1_0 2 v2_0 1) (&lt;&lt; (Vec v1_0 2 v2_0 1) 2)) (VecMul (Vec 2 v1_2 1 v2_2) (&lt;&lt; (Vec 2 v1_2 1 v2_2) 2)))) (VecMinus (VecAdd (Vec v1_1 v1_3) (Vec v2_1 v2_3)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_3) (Vec v2_1 v2_3))))) 1))</t>
         </is>
       </c>
       <c r="E92" t="n">
         <v>4759</v>
       </c>
       <c r="F92" t="n">
-        <v>4759</v>
+        <v>676</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>85.8</v>
       </c>
       <c r="H92" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I92" t="n">
-        <v>75.15000000000001</v>
+        <v>77.55</v>
       </c>
       <c r="J92" t="b">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>8999924.85</v>
+        <v>8999922.449999999</v>
       </c>
       <c r="L92" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93">
@@ -4327,32 +4327,32 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (Vec (* v1_0 v2_0) 2) (Vec 2 (* v1_4 v2_4)))) (VecMinus (VecAdd (Vec v1_1 v1_5) (Vec v2_1 v2_5)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_5) (Vec v2_1 v2_5))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_6) (Vec v2_2 v2_6)))) (VecMinus (VecAdd (Vec v1_3 v1_7) (Vec v2_3 v2_7)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_7) (Vec v2_3 v2_7)))))) (&lt;&lt; (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (Vec (* v1_0 v2_0) 2) (Vec 2 (* v1_4 v2_4)))) (VecMinus (VecAdd (Vec v1_1 v1_5) (Vec v2_1 v2_5)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_5) (Vec v2_1 v2_5))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_6) (Vec v2_2 v2_6)))) (VecMinus (VecAdd (Vec v1_3 v1_7) (Vec v2_3 v2_7)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_7) (Vec v2_3 v2_7)))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (VecMul (Vec v1_0 2 v2_0 1) (&lt;&lt; (Vec v1_0 2 v2_0 1) 2)) (VecMul (Vec 2 v1_4 1 v2_4) (&lt;&lt; (Vec 2 v1_4 1 v2_4) 2)))) (VecMinus (VecAdd (Vec v1_1 v1_5) (Vec v2_1 v2_5)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_5) (Vec v2_1 v2_5))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_6) (Vec v2_2 v2_6)))) (VecMinus (VecAdd (Vec v1_3 v1_7) (Vec v2_3 v2_7)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_7) (Vec v2_3 v2_7)))))) (&lt;&lt; (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (VecMul (Vec v1_0 2 v2_0 1) (&lt;&lt; (Vec v1_0 2 v2_0 1) 2)) (VecMul (Vec 2 v1_4 1 v2_4) (&lt;&lt; (Vec 2 v1_4 1 v2_4) 2)))) (VecMinus (VecAdd (Vec v1_1 v1_5) (Vec v2_1 v2_5)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_5) (Vec v2_1 v2_5))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_6) (Vec v2_2 v2_6)))) (VecMinus (VecAdd (Vec v1_3 v1_7) (Vec v2_3 v2_7)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_7) (Vec v2_3 v2_7)))))) 1))</t>
         </is>
       </c>
       <c r="E93" t="n">
         <v>9760</v>
       </c>
       <c r="F93" t="n">
-        <v>1274</v>
+        <v>1083</v>
       </c>
       <c r="G93" t="n">
-        <v>86.95</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H93" t="n">
         <v>76.34999999999999</v>
       </c>
       <c r="I93" t="n">
-        <v>77.55</v>
+        <v>78.75</v>
       </c>
       <c r="J93" t="b">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>8999922.449999999</v>
+        <v>8999921.25</v>
       </c>
       <c r="L93" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="94">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec (* v1_0 v2_0) 2) (Vec 2 (* v1_16 v2_16)))) (VecMinus (VecAdd (Vec v1_1 v1_17) (Vec v2_1 v2_17)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_17) (Vec v2_1 v2_17))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_18) (Vec v2_2 v2_18)))) (VecMinus (VecAdd (Vec v1_3 v1_19) (Vec v2_3 v2_19)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_19) (Vec v2_3 v2_19)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (Vec 2 2) (VecMul (Vec v1_4 v1_20) (Vec v2_4 v2_20)))) (VecMinus (VecAdd (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecMul (Vec 2 2) (VecMul (Vec v1_5 v1_21) (Vec v2_5 v2_21))))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (Vec 2 2) (VecMul (Vec v1_6 v1_22) (Vec v2_6 v2_22)))) (VecMinus (VecAdd (Vec v1_7 v1_23) (Vec v2_7 v2_23)) (VecMul (Vec 2 2) (VecMul (Vec v1_7 v1_23) (Vec v2_7 v2_23))))))) (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (Vec 2 2) (VecMul (Vec v1_8 v1_24) (Vec v2_8 v2_24)))) (VecMinus (VecAdd (Vec v1_9 v1_25) (Vec v2_9 v2_25)) (VecMul (Vec 2 2) (VecMul (Vec v1_9 v1_25) (Vec v2_9 v2_25))))) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (Vec 2 2) (VecMul (Vec v1_10 v1_26) (Vec v2_10 v2_26)))) (VecMinus (VecAdd (Vec v1_11 v1_27) (Vec v2_11 v2_27)) (VecMul (Vec 2 2) (VecMul (Vec v1_11 v1_27) (Vec v2_11 v2_27)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec 2 2) (VecMul (Vec v1_12 v1_28) (Vec v2_12 v2_28)))) (VecMinus (VecAdd (Vec v1_13 v1_29) (Vec v2_13 v2_29)) (VecMul (Vec 2 2) (Vec (* v1_13 v2_13) (* v1_29 v2_29))))) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (Vec (* 2 (* v1_14 v2_14)) (* 2 (* v1_30 v2_30)))) (VecMinus (VecAdd (Vec v1_15 v1_31) (Vec v2_15 v2_31)) (Vec (* 2 (* v1_15 v2_15)) (* 2 (* v1_31 v2_31)))))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec (* v1_0 v2_0) 2) (Vec 2 (* v1_16 v2_16)))) (VecMinus (VecAdd (Vec v1_1 v1_17) (Vec v2_1 v2_17)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_17) (Vec v2_1 v2_17))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_18) (Vec v2_2 v2_18)))) (VecMinus (VecAdd (Vec v1_3 v1_19) (Vec v2_3 v2_19)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_19) (Vec v2_3 v2_19)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (Vec 2 2) (VecMul (Vec v1_4 v1_20) (Vec v2_4 v2_20)))) (VecMinus (VecAdd (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecMul (Vec 2 2) (VecMul (Vec v1_5 v1_21) (Vec v2_5 v2_21))))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (Vec 2 2) (VecMul (Vec v1_6 v1_22) (Vec v2_6 v2_22)))) (VecMinus (VecAdd (Vec v1_7 v1_23) (Vec v2_7 v2_23)) (VecMul (Vec 2 2) (VecMul (Vec v1_7 v1_23) (Vec v2_7 v2_23))))))) (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (Vec 2 2) (VecMul (Vec v1_8 v1_24) (Vec v2_8 v2_24)))) (VecMinus (VecAdd (Vec v1_9 v1_25) (Vec v2_9 v2_25)) (VecMul (Vec 2 2) (VecMul (Vec v1_9 v1_25) (Vec v2_9 v2_25))))) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (Vec 2 2) (VecMul (Vec v1_10 v1_26) (Vec v2_10 v2_26)))) (VecMinus (VecAdd (Vec v1_11 v1_27) (Vec v2_11 v2_27)) (VecMul (Vec 2 2) (VecMul (Vec v1_11 v1_27) (Vec v2_11 v2_27)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec 2 2) (VecMul (Vec v1_12 v1_28) (Vec v2_12 v2_28)))) (VecMinus (VecAdd (Vec v1_13 v1_29) (Vec v2_13 v2_29)) (VecMul (Vec 2 2) (Vec (* v1_13 v2_13) (* v1_29 v2_29))))) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (Vec (* 2 (* v1_14 v2_14)) (* 2 (* v1_30 v2_30)))) (VecMinus (VecAdd (Vec v1_15 v1_31) (Vec v2_15 v2_31)) (Vec (* 2 (* v1_15 v2_15)) (* 2 (* v1_31 v2_31)))))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec (* v1_0 v2_0) 2) (Vec 2 (* v1_16 v2_16)))) (VecMinus (VecAdd (Vec v1_1 v1_17) (Vec v2_1 v2_17)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_17) (Vec v2_1 v2_17))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_18) (Vec v2_2 v2_18)))) (VecMinus (VecAdd (Vec v1_3 v1_19) (Vec v2_3 v2_19)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_19) (Vec v2_3 v2_19)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (Vec 2 2) (VecMul (Vec v1_4 v1_20) (Vec v2_4 v2_20)))) (VecMinus (VecAdd (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecMul (Vec 2 2) (VecMul (Vec v1_5 v1_21) (Vec v2_5 v2_21))))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (Vec 2 2) (VecMul (Vec v1_6 v1_22) (Vec v2_6 v2_22)))) (VecMinus (VecAdd (Vec v1_7 v1_23) (Vec v2_7 v2_23)) (VecMul (Vec 2 2) (VecMul (Vec v1_7 v1_23) (Vec v2_7 v2_23))))))) (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (Vec 2 2) (VecMul (Vec v1_8 v1_24) (Vec v2_8 v2_24)))) (VecMinus (VecAdd (Vec v1_9 v1_25) (Vec v2_9 v2_25)) (VecMul (Vec 2 2) (VecMul (Vec v1_9 v1_25) (Vec v2_9 v2_25))))) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (Vec 2 2) (VecMul (Vec v1_10 v1_26) (Vec v2_10 v2_26)))) (VecMinus (VecAdd (Vec v1_11 v1_27) (Vec v2_11 v2_27)) (VecMul (Vec 2 2) (VecMul (Vec v1_11 v1_27) (Vec v2_11 v2_27)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec 2 2) (VecMul (Vec v1_12 v1_28) (Vec v2_12 v2_28)))) (VecMinus (VecAdd (Vec v1_13 v1_29) (Vec v2_13 v2_29)) (VecMul (Vec 2 2) (VecMul (Vec v1_13 v1_29) (Vec v2_13 v2_29))))) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (VecMul (Vec 2 2) (Vec (* v1_14 v2_14) (* v1_30 v2_30)))) (Vec (- (+ v1_15 v2_15) (* 2 (* v1_15 v2_15))) (- (+ v1_31 v2_31) (* 2 (* v1_31 v2_31)))))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec (* v1_0 v2_0) 2) (Vec 2 (* v1_16 v2_16)))) (VecMinus (VecAdd (Vec v1_1 v1_17) (Vec v2_1 v2_17)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_17) (Vec v2_1 v2_17))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_18) (Vec v2_2 v2_18)))) (VecMinus (VecAdd (Vec v1_3 v1_19) (Vec v2_3 v2_19)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_19) (Vec v2_3 v2_19)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (Vec 2 2) (VecMul (Vec v1_4 v1_20) (Vec v2_4 v2_20)))) (VecMinus (VecAdd (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecMul (Vec 2 2) (VecMul (Vec v1_5 v1_21) (Vec v2_5 v2_21))))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (Vec 2 2) (VecMul (Vec v1_6 v1_22) (Vec v2_6 v2_22)))) (VecMinus (VecAdd (Vec v1_7 v1_23) (Vec v2_7 v2_23)) (VecMul (Vec 2 2) (VecMul (Vec v1_7 v1_23) (Vec v2_7 v2_23))))))) (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (Vec 2 2) (VecMul (Vec v1_8 v1_24) (Vec v2_8 v2_24)))) (VecMinus (VecAdd (Vec v1_9 v1_25) (Vec v2_9 v2_25)) (VecMul (Vec 2 2) (VecMul (Vec v1_9 v1_25) (Vec v2_9 v2_25))))) (VecAdd (VecMinus (VecAdd (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (Vec 2 2) (VecMul (Vec v1_10 v1_26) (Vec v2_10 v2_26)))) (VecMinus (VecAdd (Vec v1_11 v1_27) (Vec v2_11 v2_27)) (VecMul (Vec 2 2) (VecMul (Vec v1_11 v1_27) (Vec v2_11 v2_27)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec 2 2) (VecMul (Vec v1_12 v1_28) (Vec v2_12 v2_28)))) (VecMinus (VecAdd (Vec v1_13 v1_29) (Vec v2_13 v2_29)) (VecMul (Vec 2 2) (VecMul (Vec v1_13 v1_29) (Vec v2_13 v2_29))))) (VecAdd (VecMinus (VecAdd (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (VecMul (Vec 2 2) (Vec (* v1_14 v2_14) (* v1_30 v2_30)))) (Vec (- (+ v1_15 v2_15) (* 2 (* v1_15 v2_15))) (- (+ v1_31 v2_31) (* 2 (* v1_31 v2_31)))))))) 1))</t>
         </is>
       </c>
       <c r="E94" t="n">
         <v>39762</v>
       </c>
       <c r="F94" t="n">
-        <v>5712</v>
+        <v>5910</v>
       </c>
       <c r="G94" t="n">
-        <v>85.63</v>
+        <v>85.14</v>
       </c>
       <c r="H94" t="n">
         <v>78.75</v>
@@ -4411,17 +4411,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>(VecAdd (Vec c1_0 c1_1 c1_2 c1_3 c1_4 c1_5 c1_6 c1_7) (VecAdd (Vec c2_0 c2_1 c2_2 c2_3 c2_4 c2_5 c2_6 c2_7) (VecMul (Vec c0_0 c0_1 c0_2 c0_3 c0_4 c0_5 c0_6 c0_7) (VecAdd (Vec c3_0 c3_1 c3_2 c3_3 c3_4 c3_5 c3_6 c3_7) (Vec (* c0_0 c4_0) (* c0_1 c4_1) (* c0_2 c4_2) (* c0_3 c4_3) (* c0_4 c4_4) (* c0_5 c4_5) (* c0_6 c4_6) (* c0_7 c4_7))))))</t>
+          <t>(VecAdd (Vec c1_0 c1_1 c1_2 c1_3 c1_4 c1_5 c1_6 c1_7) (VecAdd (Vec c2_0 c2_1 c2_2 c2_3 c2_4 c2_5 c2_6 c2_7) (VecMul (Vec c0_0 c0_1 c0_2 c0_3 c0_4 c0_5 c0_6 c0_7) (VecAdd (Vec c3_0 c3_1 c3_2 c3_3 c3_4 c3_5 c3_6 c3_7) (VecMul (Vec c0_0 c0_1 c0_2 c0_3 c0_4 c0_5 c0_6 c0_7) (Vec c4_0 c4_1 c4_2 c4_3 c4_4 c4_5 c4_6 c4_7))))))</t>
         </is>
       </c>
       <c r="E95" t="n">
         <v>10009</v>
       </c>
       <c r="F95" t="n">
-        <v>2112</v>
+        <v>212</v>
       </c>
       <c r="G95" t="n">
-        <v>78.90000000000001</v>
+        <v>97.88</v>
       </c>
       <c r="H95" t="n">
         <v>75.15000000000001</v>
@@ -4436,7 +4436,7 @@
         <v>8999924.85</v>
       </c>
       <c r="L95" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96">
@@ -4495,32 +4495,32 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( + ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ( * ( - c2_3 c1_3 ) ( - c2_3 c1_3 ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2) (Vec c1_0 c1_2)) (VecMinus (Vec c2_0 c2_2) (Vec c1_0 c1_2))) (VecMul (VecMinus (Vec c2_1 c2_3) (Vec c1_1 c1_3)) (VecMinus (Vec c2_1 c2_3) (Vec c1_1 c1_3)))) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2) (Vec c1_0 c1_2)) (VecMinus (Vec c2_0 c2_2) (Vec c1_0 c1_2))) (VecMul (VecMinus (Vec c2_1 c2_3) (Vec c1_1 c1_3)) (VecMinus (Vec c2_1 c2_3) (Vec c1_1 c1_3)))) 1))</t>
         </is>
       </c>
       <c r="E97" t="n">
         <v>3757</v>
       </c>
       <c r="F97" t="n">
-        <v>3757</v>
+        <v>265</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>92.95</v>
       </c>
       <c r="H97" t="n">
         <v>40.57</v>
       </c>
       <c r="I97" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="J97" t="b">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>8999959.43</v>
+        <v>8999958.23</v>
       </c>
       <c r="L97" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98">
@@ -4537,32 +4537,32 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( + ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ( * ( - c2_3 c1_3 ) ( - c2_3 c1_3 ) ) ) ) ( + ( + ( * ( - c2_4 c1_4 ) ( - c2_4 c1_4 ) ) ( * ( - c2_5 c1_5 ) ( - c2_5 c1_5 ) ) ) ( + ( * ( - c2_6 c1_6 ) ( - c2_6 c1_6 ) ) ( * ( - c2_7 c1_7 ) ( - c2_7 c1_7 ) ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4) (Vec c1_0 c1_4)) (VecMinus (Vec c2_0 c2_4) (Vec c1_0 c1_4))) (VecMul (VecMinus (Vec c2_1 c2_5) (Vec c1_1 c1_5)) (VecMinus (Vec c2_1 c2_5) (Vec c1_1 c1_5)))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6) (Vec c1_2 c1_6)) (VecMinus (Vec c2_2 c2_6) (Vec c1_2 c1_6))) (VecMul (VecMinus (Vec c2_3 c2_7) (Vec c1_3 c1_7)) (VecMinus (Vec c2_3 c2_7) (Vec c1_3 c1_7))))) (&lt;&lt; (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_4) (Vec c1_0 c1_4)) (VecMinus (Vec c2_0 c2_4) (Vec c1_0 c1_4))) (VecMul (VecMinus (Vec c2_1 c2_5) (Vec c1_1 c1_5)) (VecMinus (Vec c2_1 c2_5) (Vec c1_1 c1_5)))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_6) (Vec c1_2 c1_6)) (VecMinus (Vec c2_2 c2_6) (Vec c1_2 c1_6))) (VecMul (VecMinus (Vec c2_3 c2_7) (Vec c1_3 c1_7)) (VecMinus (Vec c2_3 c2_7) (Vec c1_3 c1_7))))) 1))</t>
         </is>
       </c>
       <c r="E98" t="n">
         <v>7758</v>
       </c>
       <c r="F98" t="n">
-        <v>7758</v>
+        <v>472</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>93.92</v>
       </c>
       <c r="H98" t="n">
         <v>41.77</v>
       </c>
       <c r="I98" t="n">
-        <v>41.77</v>
+        <v>42.97</v>
       </c>
       <c r="J98" t="b">
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>8999958.23</v>
+        <v>8999957.029999999</v>
       </c>
       <c r="L98" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="99">
@@ -4579,29 +4579,29 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16) (Vec c1_0 c1_16)) (VecMinus (Vec c2_0 c2_16) (Vec c1_0 c1_16))) (VecMul (VecMinus (Vec c2_1 c2_17) (Vec c1_1 c1_17)) (VecMinus (Vec c2_1 c2_17) (Vec c1_1 c1_17)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18) (Vec c1_2 c1_18)) (VecMinus (Vec c2_2 c2_18) (Vec c1_2 c1_18))) (VecMul (VecMinus (Vec c2_3 c2_19) (Vec c1_3 c1_19)) (VecMinus (Vec c2_3 c2_19) (Vec c1_3 c1_19)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_20) (Vec c1_4 c1_20)) (VecMinus (Vec c2_4 c2_20) (Vec c1_4 c1_20))) (VecMul (VecMinus (Vec c2_5 c2_21) (Vec c1_5 c1_21)) (VecMinus (Vec c2_5 c2_21) (Vec c1_5 c1_21)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22) (Vec c1_6 c1_22)) (VecMinus (Vec c2_6 c2_22) (Vec c1_6 c1_22))) (VecMul (VecMinus (Vec c2_7 c2_23) (Vec c1_7 c1_23)) (VecMinus (Vec c2_7 c2_23) (Vec c1_7 c1_23)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_8 c2_24) (Vec c1_8 c1_24)) (VecMinus (Vec c2_8 c2_24) (Vec c1_8 c1_24))) (VecMul (VecMinus (Vec c2_9 c2_25) (Vec c1_9 c1_25)) (VecMinus (Vec c2_9 c2_25) (Vec c1_9 c1_25)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26) (Vec c1_10 c1_26)) (VecMinus (Vec c2_10 c2_26) (Vec c1_10 c1_26))) (VecMul (VecMinus (Vec c2_11 c2_27) (Vec c1_11 c1_27)) (VecMinus (Vec c2_11 c2_27) (Vec c1_11 c1_27)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28) (Vec c1_12 c1_28)) (VecMinus (Vec c2_12 c2_28) (Vec c1_12 c1_28))) (VecMul (VecMinus (Vec c2_13 c2_29) (Vec c1_13 c1_29)) (VecMinus (Vec c2_13 c2_29) (Vec c1_13 c1_29)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30) (Vec c1_14 c1_30)) (VecMinus (Vec c2_14 c2_30) (Vec c1_14 c1_30))) (VecMul (VecMinus (Vec c2_15 c2_31) (Vec c1_15 c1_31)) (VecMinus (Vec c2_15 c2_31) (Vec c1_15 c1_31)))) (&lt;&lt; (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16) (Vec c1_0 c1_16)) (VecMinus (Vec c2_0 c2_16) (Vec c1_0 c1_16))) (VecMul (VecMinus (Vec c2_1 c2_17) (Vec c1_1 c1_17)) (VecMinus (Vec c2_1 c2_17) (Vec c1_1 c1_17)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18) (Vec c1_2 c1_18)) (VecMinus (Vec c2_2 c2_18) (Vec c1_2 c1_18))) (VecMul (VecMinus (Vec c2_3 c2_19) (Vec c1_3 c1_19)) (VecMinus (Vec c2_3 c2_19) (Vec c1_3 c1_19)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_20) (Vec c1_4 c1_20)) (VecMinus (Vec c2_4 c2_20) (Vec c1_4 c1_20))) (VecMul (VecMinus (Vec c2_5 c2_21) (Vec c1_5 c1_21)) (VecMinus (Vec c2_5 c2_21) (Vec c1_5 c1_21)))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22) (Vec c1_6 c1_22)) (VecMinus (Vec c2_6 c2_22) (Vec c1_6 c1_22))) (VecMul (VecMinus (Vec c2_7 c2_23) (Vec c1_7 c1_23)) (VecMinus (Vec c2_7 c2_23) (Vec c1_7 c1_23)))) (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_8 c2_24) (Vec c1_8 c1_24)) (VecMinus (Vec c2_8 c2_24) (Vec c1_8 c1_24))) (VecMul (VecMinus (Vec c2_9 c2_25) (Vec c1_9 c1_25)) (VecMinus (Vec c2_9 c2_25) (Vec c1_9 c1_25)))) (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26) (Vec c1_10 c1_26)) (VecMinus (Vec c2_10 c2_26) (Vec c1_10 c1_26))) (VecMul (VecMinus (Vec c2_11 c2_27) (Vec c1_11 c1_27)) (VecMinus (Vec c2_11 c2_27) (Vec c1_11 c1_27))))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28) (Vec c1_12 c1_28)) (VecMinus (Vec c2_12 c2_28) (Vec c1_12 c1_28))) (VecMul (VecMinus (Vec c2_13 c2_29) (Vec c1_13 c1_29)) (VecMinus (Vec c2_13 c2_29) (Vec c1_13 c1_29)))) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30) (Vec c1_14 c1_30)) (VecMinus (Vec c2_14 c2_30) (Vec c1_14 c1_30))) (VecMul (VecMinus (Vec c2_15 c2_31) (Vec c1_15 c1_31)) (VecMinus (Vec c2_15 c2_31) (Vec c1_15 c1_31)))))))))) 1)))))))))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16) (Vec c1_0 c1_16)) (VecMinus (Vec c2_0 c2_16) (Vec c1_0 c1_16))) (VecMul (VecMinus (Vec c2_1 c2_17) (Vec c1_1 c1_17)) (VecMinus (Vec c2_1 c2_17) (Vec c1_1 c1_17)))) (VecMul (VecMinus (Vec c2_2 c2_18) (Vec c1_2 c1_18)) (VecMinus (Vec c2_2 c2_18) (Vec c1_2 c1_18)))) (VecMul (VecMinus (Vec c2_3 c2_19) (Vec c1_3 c1_19)) (VecMinus (Vec c2_3 c2_19) (Vec c1_3 c1_19)))) (VecAdd (VecMul (VecMinus (Vec c2_4 c2_20) (Vec c1_4 c1_20)) (VecMinus (Vec c2_4 c2_20) (Vec c1_4 c1_20))) (VecMul (VecMinus (Vec c2_5 c2_21) (Vec c1_5 c1_21)) (VecMinus (Vec c2_5 c2_21) (Vec c1_5 c1_21))))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22) (Vec c1_6 c1_22)) (VecMinus (Vec c2_6 c2_22) (Vec c1_6 c1_22))) (VecAdd (VecMul (VecMinus (Vec c2_7 c2_23) (Vec c1_7 c1_23)) (VecMinus (Vec c2_7 c2_23) (Vec c1_7 c1_23))) (VecAdd (VecMul (VecMinus (Vec c2_8 c2_24) (Vec c1_8 c1_24)) (VecMinus (Vec c2_8 c2_24) (Vec c1_8 c1_24))) (VecAdd (VecMul (VecMinus (Vec c2_9 c2_25) (Vec c1_9 c1_25)) (VecMinus (Vec c2_9 c2_25) (Vec c1_9 c1_25))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26) (Vec c1_10 c1_26)) (VecMinus (Vec c2_10 c2_26) (Vec c1_10 c1_26))) (VecMul (VecMinus (Vec c2_11 c2_27) (Vec c1_11 c1_27)) (VecMinus (Vec c2_11 c2_27) (Vec c1_11 c1_27)))) (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28) (Vec c1_12 c1_28)) (VecMinus (Vec c2_12 c2_28) (Vec c1_12 c1_28))) (VecMul (VecMinus (Vec c2_13 c2_29) (Vec c1_13 c1_29)) (VecMinus (Vec c2_13 c2_29) (Vec c1_13 c1_29)))) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30) (Vec c1_14 c1_30)) (VecMinus (Vec c2_14 c2_30) (Vec c1_14 c1_30))) (VecMul (VecMinus (Vec c2_15 c2_31) (Vec c1_15 c1_31)) (VecMinus (Vec c2_15 c2_31) (Vec c1_15 c1_31))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_16) (Vec c1_0 c1_16)) (VecMinus (Vec c2_0 c2_16) (Vec c1_0 c1_16))) (VecMul (VecMinus (Vec c2_1 c2_17) (Vec c1_1 c1_17)) (VecMinus (Vec c2_1 c2_17) (Vec c1_1 c1_17)))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_18) (Vec c1_2 c1_18)) (VecMinus (Vec c2_2 c2_18) (Vec c1_2 c1_18))) (VecMul (VecMinus (Vec c2_3 c2_19) (Vec c1_3 c1_19)) (VecMinus (Vec c2_3 c2_19) (Vec c1_3 c1_19))))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_20) (Vec c1_4 c1_20)) (VecMinus (Vec c2_4 c2_20) (Vec c1_4 c1_20))) (VecMul (VecMinus (Vec c2_5 c2_21) (Vec c1_5 c1_21)) (VecMinus (Vec c2_5 c2_21) (Vec c1_5 c1_21)))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_22) (Vec c1_6 c1_22)) (VecMinus (Vec c2_6 c2_22) (Vec c1_6 c1_22))) (VecMul (VecMinus (Vec c2_7 c2_23) (Vec c1_7 c1_23)) (VecMinus (Vec c2_7 c2_23) (Vec c1_7 c1_23)))))) (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_8 c2_24) (Vec c1_8 c1_24)) (VecMinus (Vec c2_8 c2_24) (Vec c1_8 c1_24))) (VecMul (VecMinus (Vec c2_9 c2_25) (Vec c1_9 c1_25)) (VecMinus (Vec c2_9 c2_25) (Vec c1_9 c1_25)))) (VecAdd (VecMul (VecMinus (Vec c2_10 c2_26) (Vec c1_10 c1_26)) (VecMinus (Vec c2_10 c2_26) (Vec c1_10 c1_26))) (VecMul (VecMinus (Vec c2_11 c2_27) (Vec c1_11 c1_27)) (VecMinus (Vec c2_11 c2_27) (Vec c1_11 c1_27))))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_12 c2_28) (Vec c1_12 c1_28)) (VecMinus (Vec c2_12 c2_28) (Vec c1_12 c1_28))) (VecMul (VecMinus (Vec c2_13 c2_29) (Vec c1_13 c1_29)) (VecMinus (Vec c2_13 c2_29) (Vec c1_13 c1_29)))) (VecAdd (VecMul (VecMinus (Vec c2_14 c2_30) (Vec c1_14 c1_30)) (VecMinus (Vec c2_14 c2_30) (Vec c1_14 c1_30))) (VecMul (VecMinus (Vec c2_15 c2_31) (Vec c1_15 c1_31)) (VecMinus (Vec c2_15 c2_31) (Vec c1_15 c1_31))))))) 1))))))))</t>
         </is>
       </c>
       <c r="E99" t="n">
         <v>31760</v>
       </c>
       <c r="F99" t="n">
-        <v>1720</v>
+        <v>1716</v>
       </c>
       <c r="G99" t="n">
-        <v>94.58</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H99" t="n">
         <v>44.16</v>
       </c>
       <c r="I99" t="n">
-        <v>57.34</v>
+        <v>52.55</v>
       </c>
       <c r="J99" t="b">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>8999942.66</v>
+        <v>8999947.449999999</v>
       </c>
       <c r="L99" t="n">
         <v>75</v>
@@ -4621,32 +4621,32 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( + ( * v1_2 v2_2 ) ( * v1_3 v2_3 ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMul (Vec v1_0 v1_2) (Vec v2_0 v2_2)) (VecMul (Vec v1_1 v1_3) (Vec v2_1 v2_3))) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_2) (Vec v2_0 v2_2)) (VecMul (Vec v1_1 v1_3) (Vec v2_1 v2_3))) 1))</t>
         </is>
       </c>
       <c r="E100" t="n">
         <v>1756</v>
       </c>
       <c r="F100" t="n">
-        <v>1756</v>
+        <v>260</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>85.19</v>
       </c>
       <c r="H100" t="n">
         <v>39.37</v>
       </c>
       <c r="I100" t="n">
-        <v>39.37</v>
+        <v>40.57</v>
       </c>
       <c r="J100" t="b">
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>8999960.630000001</v>
+        <v>8999959.43</v>
       </c>
       <c r="L100" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
@@ -4663,32 +4663,32 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( + ( * v1_2 v2_2 ) ( * v1_3 v2_3 ) ) ) ( + ( + ( * v1_4 v2_4 ) ( * v1_5 v2_5 ) ) ( + ( * v1_6 v2_6 ) ( * v1_7 v2_7 ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (Vec v1_1 v1_5) (Vec v2_1 v2_5))) (VecAdd (VecMul (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (Vec v1_3 v1_7) (Vec v2_3 v2_7)))) (&lt;&lt; (VecAdd (VecAdd (VecMul (Vec v1_0 v1_4) (Vec v2_0 v2_4)) (VecMul (Vec v1_1 v1_5) (Vec v2_1 v2_5))) (VecAdd (VecMul (Vec v1_2 v1_6) (Vec v2_2 v2_6)) (VecMul (Vec v1_3 v1_7) (Vec v2_3 v2_7)))) 1))</t>
         </is>
       </c>
       <c r="E101" t="n">
         <v>3757</v>
       </c>
       <c r="F101" t="n">
-        <v>3757</v>
+        <v>463</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="H101" t="n">
         <v>40.57</v>
       </c>
       <c r="I101" t="n">
-        <v>40.57</v>
+        <v>41.77</v>
       </c>
       <c r="J101" t="b">
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>8999959.43</v>
+        <v>8999958.23</v>
       </c>
       <c r="L101" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102">
@@ -4705,32 +4705,32 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMul (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec v1_1 v1_17) (Vec v2_1 v2_17))) (VecAdd (VecAdd (VecMul (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (Vec v1_3 v1_19) (Vec v2_3 v2_19))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (Vec v1_5 v1_21) (Vec v2_5 v2_21))) (VecAdd (VecAdd (VecMul (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (Vec v1_7 v1_23) (Vec v2_7 v2_23))) (VecAdd (VecAdd (VecMul (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (Vec v1_9 v1_25) (Vec v2_9 v2_25))) (VecAdd (VecAdd (VecMul (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (Vec v1_11 v1_27) (Vec v2_11 v2_27))) (VecAdd (VecAdd (VecMul (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec v1_13 v1_29) (Vec v2_13 v2_29))) (VecAdd (VecAdd (VecMul (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (VecMul (Vec v1_15 v1_31) (Vec v2_15 v2_31))) (&lt;&lt; (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec v1_1 v1_17) (Vec v2_1 v2_17))) (VecAdd (VecAdd (VecMul (Vec v1_2 v1_18) (Vec v2_2 v2_18)) (VecMul (Vec v1_3 v1_19) (Vec v2_3 v2_19))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecMul (Vec v1_5 v1_21) (Vec v2_5 v2_21))) (VecAdd (VecAdd (VecMul (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (Vec v1_7 v1_23) (Vec v2_7 v2_23))) (VecAdd (VecAdd (VecMul (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (Vec v1_9 v1_25) (Vec v2_9 v2_25))) (VecAdd (VecAdd (VecMul (Vec v1_10 v1_26) (Vec v2_10 v2_26)) (VecMul (Vec v1_11 v1_27) (Vec v2_11 v2_27))) (VecAdd (VecAdd (VecMul (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec v1_13 v1_29) (Vec v2_13 v2_29))) (VecAdd (VecMul (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (VecMul (Vec v1_15 v1_31) (Vec v2_15 v2_31)))))))))) 1)))))))))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec v1_1 v1_17) (Vec v2_1 v2_17))) (VecMul (Vec v1_2 v1_18) (Vec v2_2 v2_18))) (VecMul (Vec v1_3 v1_19) (Vec v2_3 v2_19))) (VecMul (Vec v1_4 v1_20) (Vec v2_4 v2_20))) (VecAdd (VecAdd (VecMul (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecMul (Vec v1_6 v1_22) (Vec v2_6 v2_22))) (VecAdd (VecMul (Vec v1_7 v1_23) (Vec v2_7 v2_23)) (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (Vec v1_9 v1_25) (Vec v2_9 v2_25))) (VecMul (Vec v1_10 v1_26) (Vec v2_10 v2_26))) (VecMul (Vec v1_11 v1_27) (Vec v2_11 v2_27))) (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec v1_13 v1_29) (Vec v2_13 v2_29))) (VecMul (Vec v1_14 v1_30) (Vec v2_14 v2_30))) (VecAdd (VecMul (Vec v1_15 v1_31) (Vec v2_15 v2_31)) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_16) (Vec v2_0 v2_16)) (VecMul (Vec v1_1 v1_17) (Vec v2_1 v2_17))) (VecMul (Vec v1_2 v1_18) (Vec v2_2 v2_18))) (VecMul (Vec v1_3 v1_19) (Vec v2_3 v2_19))) (VecAdd (VecMul (Vec v1_4 v1_20) (Vec v2_4 v2_20)) (VecAdd (VecMul (Vec v1_5 v1_21) (Vec v2_5 v2_21)) (VecAdd (VecAdd (VecMul (Vec v1_6 v1_22) (Vec v2_6 v2_22)) (VecMul (Vec v1_7 v1_23) (Vec v2_7 v2_23))) (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_8 v1_24) (Vec v2_8 v2_24)) (VecMul (Vec v1_9 v1_25) (Vec v2_9 v2_25))) (VecMul (Vec v1_10 v1_26) (Vec v2_10 v2_26))) (VecAdd (VecMul (Vec v1_11 v1_27) (Vec v2_11 v2_27)) (VecAdd (VecAdd (VecMul (Vec v1_12 v1_28) (Vec v2_12 v2_28)) (VecMul (Vec v1_13 v1_29) (Vec v2_13 v2_29))) (VecAdd (VecMul (Vec v1_14 v1_30) (Vec v2_14 v2_30)) (VecMul (Vec v1_15 v1_31) (Vec v2_15 v2_31)))))))))) 1)))))))</t>
         </is>
       </c>
       <c r="E102" t="n">
         <v>15759</v>
       </c>
       <c r="F102" t="n">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="G102" t="n">
-        <v>89.29000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="H102" t="n">
         <v>42.97</v>
       </c>
       <c r="I102" t="n">
-        <v>57.34</v>
+        <v>54.95</v>
       </c>
       <c r="J102" t="b">
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>8999942.66</v>
+        <v>8999945.050000001</v>
       </c>
       <c r="L102" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="103">
@@ -4747,32 +4747,32 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 0 in_2_2 in_2_3 0 0 in_3_2 in_3_3 0 0 in_2_2 in_2_3 0) (Vec in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2))) (VecAdd (VecAdd (Vec 0 0 0 0 0 in_0_2 in_0_3 0 0 in_1_2 in_1_3 0 0 0 0 0) (Vec 0 (* in_0_2 2) (* in_0_3 2) 0 in_0_1 (- in_0_0) (- in_0_1) (- in_0_2) in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) 0 (* in_3_2 2) (* in_3_3 2) 0)) (VecAdd (Vec 0 0 0 0 0 (* in_1_2 2) (* in_1_3 2) 0 0 (* in_2_2 2) (* in_2_3 2) 0 0 0 0 0) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2) (Vec 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2)))))</t>
+          <t>(VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 0 in_2_2 in_2_3 0 0 in_3_2 in_3_3 0 0 in_2_2 in_2_3 0) (VecMinus (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_2_1 in_2_0 in_2_1 in_2_2 0 in_1_0 in_1_1 in_1_2 0 in_2_0 in_2_1 in_2_2 0 in_3_0 in_3_1 in_3_2 0 in_2_0 in_2_1 in_2_2) (&lt;&lt; (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_2_1 in_2_0 in_2_1 in_2_2 0 in_1_0 in_1_1 in_1_2 0 in_2_0 in_2_1 in_2_2 0 in_3_0 in_3_1 in_3_2 0 in_2_0 in_2_1 in_2_2) 16))) (VecAdd (VecAdd (Vec 0 0 0 0 0 in_0_2 in_0_3 0 0 in_1_2 in_1_3 0 0 0 0 0) (VecMul (Vec 1 in_0_2 in_0_3 1 1 1 1 1 1 1 1 1 1 in_3_2 in_3_3 1) (VecMinus (Vec 0 2 2 0 in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 0 2 2 0 0 0 0 0 0 in_0_0 in_0_1 in_0_2 0 in_1_0 in_1_1 in_1_2 0 0 0 0) (&lt;&lt; (Vec 0 2 2 0 in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 0 2 2 0 0 0 0 0 0 in_0_0 in_0_1 in_0_2 0 in_1_0 in_1_1 in_1_2 0 0 0 0) 16)))) (VecAdd (VecMul (Vec 1 1 1 1 1 in_1_2 in_1_3 1 1 in_2_2 in_2_3 1 1 1 1 1) (Vec 0 0 0 0 0 2 2 0 0 2 2 0 0 0 0 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_1_1 in_1_0 in_1_1 in_1_2 in_2_1 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2) (Vec 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2 2 -2 -2 -2)))))</t>
         </is>
       </c>
       <c r="E103" t="n">
         <v>21507</v>
       </c>
       <c r="F103" t="n">
-        <v>6612</v>
+        <v>448</v>
       </c>
       <c r="G103" t="n">
-        <v>69.26000000000001</v>
+        <v>97.92</v>
       </c>
       <c r="H103" t="n">
         <v>40.57</v>
       </c>
       <c r="I103" t="n">
-        <v>40.57</v>
+        <v>42.97</v>
       </c>
       <c r="J103" t="b">
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>8999959.43</v>
+        <v>8999957.029999999</v>
       </c>
       <c r="L103" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="104">
@@ -4789,17 +4789,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMul (Vec a_0_0 a_0_0 a_0_0 a_1_0 a_1_0 a_1_0 a_2_0 a_2_0 a_2_0) (Vec b_0_0 b_0_1 b_0_2 b_0_0 b_0_1 b_0_2 b_0_0 b_0_1 b_0_2)) (VecMul (Vec a_0_1 a_0_1 a_0_1 a_1_1 a_1_1 a_1_1 a_2_1 a_2_1 a_2_1) (Vec b_1_0 b_1_1 b_1_2 b_1_0 b_1_1 b_1_2 b_1_0 b_1_1 b_1_2))) (Vec (* a_0_2 b_2_0) (* a_0_2 b_2_1) (* a_0_2 b_2_2) (* a_1_2 b_2_0) (* a_1_2 b_2_1) (* a_1_2 b_2_2) (* a_2_2 b_2_0) (* a_2_2 b_2_1) (* a_2_2 b_2_2)))</t>
+          <t>(VecAdd (VecAdd (VecMul (Vec a_0_0 a_0_0 a_0_0 a_1_0 a_1_0 a_1_0 a_2_0 a_2_0 a_2_0) (Vec b_0_0 b_0_1 b_0_2 b_0_0 b_0_1 b_0_2 b_0_0 b_0_1 b_0_2)) (VecMul (Vec a_0_1 a_0_1 a_0_1 a_1_1 a_1_1 a_1_1 a_2_1 a_2_1 a_2_1) (Vec b_1_0 b_1_1 b_1_2 b_1_0 b_1_1 b_1_2 b_1_0 b_1_1 b_1_2))) (VecMul (Vec a_0_2 a_0_2 a_0_2 a_1_2 a_1_2 a_1_2 a_2_2 a_2_2 a_2_2) (Vec b_2_0 b_2_1 b_2_2 b_2_0 b_2_1 b_2_2 b_2_0 b_2_1 b_2_2)))</t>
         </is>
       </c>
       <c r="E104" t="n">
         <v>11256</v>
       </c>
       <c r="F104" t="n">
-        <v>2458</v>
+        <v>308</v>
       </c>
       <c r="G104" t="n">
-        <v>78.16</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="H104" t="n">
         <v>39.37</v>
@@ -4814,7 +4814,7 @@
         <v>8999960.630000001</v>
       </c>
       <c r="L104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105">
@@ -4831,32 +4831,32 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>(Vec ( + ( * ( + ( * o3 ( - 1 c23 ) ) ( * c23 o2 ) ) ( - 1 c12 ) ) ( * c12 ( + ( * o3 ( - 1 c13 ) ) ( * c13 o1 ) ) ) ) )</t>
+          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec o3 1 c23 1) (Vec (- 1 c23) c12 o2 0)) (&lt;&lt; (VecMul (Vec o3 1 c23 1) (Vec (- 1 c23) c12 o2 0)) 2)) (VecAdd (VecMul (Vec 1 o3 1 c13) (VecMinus (Vec 1 1 0 o1) (Vec c12 c13 0 0))) (&lt;&lt; (VecMul (Vec 1 o3 1 c13) (VecMinus (Vec 1 1 0 o1) (Vec c12 c13 0 0))) 2))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec o3 1 c23 1) (Vec (- 1 c23) c12 o2 0)) (&lt;&lt; (VecMul (Vec o3 1 c23 1) (Vec (- 1 c23) c12 o2 0)) 2)) (VecAdd (VecMul (Vec 1 o3 1 c13) (VecMinus (Vec 1 1 0 o1) (Vec c12 c13 0 0))) (&lt;&lt; (VecMul (Vec 1 o3 1 c13) (VecMinus (Vec 1 1 0 o1) (Vec c12 c13 0 0))) 2))) 1))</t>
         </is>
       </c>
       <c r="E105" t="n">
         <v>3009</v>
       </c>
       <c r="F105" t="n">
-        <v>3009</v>
+        <v>724</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>75.94</v>
       </c>
       <c r="H105" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I105" t="n">
-        <v>75.15000000000001</v>
+        <v>77.55</v>
       </c>
       <c r="J105" t="b">
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>8999924.85</v>
+        <v>8999922.449999999</v>
       </c>
       <c r="L105" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106">
@@ -4873,32 +4873,32 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>(Vec ( + ( * ( + ( * ( + ( * o321 ( - 1 c23 ) ) ( * c23 o231 ) ) ( - 1 c13 ) ) ( * c13 o213 ) ) ( - 1 c12 ) ) ( * c12 ( + ( * ( - 1 c23 ) ( + ( * o312 ( - 1 c13 ) ) ( * c13 o132 ) ) ) ( * c23 o123 ) ) ) ) )</t>
+          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 c13 1) (Vec (- 1 c13) c12 o213 0)) (&lt;&lt; (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 c13 1) (Vec (- 1 c13) c12 o213 0)) 2)) (VecAdd (VecMul (Vec 1 (- 1 c23) 1 c23) (Vec (- 1 c12) (+ (* o312 (- 1 c13)) (* c13 o132)) 0 o123)) (&lt;&lt; (VecMul (Vec 1 (- 1 c23) 1 c23) (Vec (- 1 c12) (+ (* o312 (- 1 c13)) (* c13 o132)) 0 o123)) 2))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 c13 1) (Vec (- 1 c13) c12 o213 0)) (&lt;&lt; (VecMul (Vec (+ (* o321 (- 1 c23)) (* c23 o231)) 1 c13 1) (Vec (- 1 c13) c12 o213 0)) 2)) (VecAdd (VecMul (Vec 1 (- 1 c23) 1 c23) (Vec (- 1 c12) (+ (* o312 (- 1 c13)) (* c13 o132)) 0 o123)) (&lt;&lt; (VecMul (Vec 1 (- 1 c23) 1 c23) (Vec (- 1 c12) (+ (* o312 (- 1 c13)) (* c13 o132)) 0 o123)) 2))) 1))</t>
         </is>
       </c>
       <c r="E106" t="n">
         <v>5012</v>
       </c>
       <c r="F106" t="n">
-        <v>5012</v>
+        <v>3226</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>35.63</v>
       </c>
       <c r="H106" t="n">
         <v>110.93</v>
       </c>
       <c r="I106" t="n">
-        <v>110.93</v>
+        <v>113.33</v>
       </c>
       <c r="J106" t="b">
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>8999889.07</v>
+        <v>8999886.67</v>
       </c>
       <c r="L106" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
     </row>
     <row r="107">
@@ -4915,32 +4915,32 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>(Vec ( * ( + x9602 x9604 ) ( + ( + x9608 x9610 ) ( + ( * x9613 x9615 ) x9617 ) ) ) )</t>
+          <t>(VecMul (VecAdd (VecAdd (Vec x9602 x9608 0 x9610) (&lt;&lt; (Vec x9602 x9608 0 x9610) 2)) (VecAdd (Vec x9604 (* x9613 x9615) 0 x9617) (&lt;&lt; (Vec x9604 (* x9613 x9615) 0 x9617) 2))) (&lt;&lt; (VecAdd (VecAdd (Vec x9602 x9608 0 x9610) (&lt;&lt; (Vec x9602 x9608 0 x9610) 2)) (VecAdd (Vec x9604 (* x9613 x9615) 0 x9617) (&lt;&lt; (Vec x9604 (* x9613 x9615) 0 x9617) 2))) 1))</t>
         </is>
       </c>
       <c r="E107" t="n">
         <v>1508</v>
       </c>
       <c r="F107" t="n">
-        <v>1508</v>
+        <v>522</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>65.38</v>
       </c>
       <c r="H107" t="n">
         <v>73.95</v>
       </c>
       <c r="I107" t="n">
-        <v>73.95</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="J107" t="b">
         <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>8999926.050000001</v>
+        <v>8999923.65</v>
       </c>
       <c r="L107" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
@@ -4957,32 +4957,32 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * ( + ( * x9604 x9605 ) ( + x9607 x9608 ) ) ( + ( + x9611 x9612 ) ( + x9614 x9615 ) ) ) ( * ( * ( * x9619 x9620 ) ( * x9622 x9623 ) ) ( * ( + x9626 x9627 ) ( * x9629 x9630 ) ) ) ) ( * ( + ( + ( * x9634 x9635 ) ( + x9637 x9638 ) ) ( + ( * x9641 x9642 ) ( * x9644 x9645 ) ) ) ( + ( * ( + x9649 x9650 ) ( + x9652 x9653 ) ) ( + ( * x9656 x9657 ) ( * x9659 x9660 ) ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMul (VecAdd (VecAdd (VecMul (Vec 1 x9634 1 1 1 x9641 1 1) (Vec 0 x9635 0 0 x9607 x9642 0 0)) (VecMul (Vec x9604 1 (* x9619 x9620) 1 1 x9644 1 1) (Vec x9605 (+ x9637 x9638) (* x9622 x9623) 1 x9608 x9645 0 0))) (&lt;&lt; (VecAdd (VecMul (Vec 1 x9634 1 1 1 x9641 1 1) (Vec 0 x9635 0 0 x9607 x9642 0 0)) (VecMul (Vec x9604 1 (* x9619 x9620) 1 1 x9644 1 1) (Vec x9605 (+ x9637 x9638) (* x9622 x9623) 1 x9608 x9645 0 0))) 4)) (VecAdd (Vec (+ x9611 x9612) (* (+ x9649 x9650) (+ x9652 x9653)) 0 0) (VecAdd (Vec x9614 (* x9656 x9657) 0 0) (VecMul (Vec 1 x9659 (+ x9626 x9627) 1) (Vec x9615 x9660 (* x9629 x9630) 0))))) (&lt;&lt; (VecMul (VecAdd (VecAdd (VecMul (Vec 1 x9634 1 1 1 x9641 1 1) (Vec 0 x9635 0 0 x9607 x9642 0 0)) (VecMul (Vec x9604 1 (* x9619 x9620) 1 1 x9644 1 1) (Vec x9605 (+ x9637 x9638) (* x9622 x9623) 1 x9608 x9645 0 0))) (&lt;&lt; (VecAdd (VecMul (Vec 1 x9634 1 1 1 x9641 1 1) (Vec 0 x9635 0 0 x9607 x9642 0 0)) (VecMul (Vec x9604 1 (* x9619 x9620) 1 1 x9644 1 1) (Vec x9605 (+ x9637 x9638) (* x9622 x9623) 1 x9608 x9645 0 0))) 4)) (VecAdd (Vec (+ x9611 x9612) (* (+ x9649 x9650) (+ x9652 x9653)) 0 0) (VecAdd (Vec x9614 (* x9656 x9657) 0 0) (VecMul (Vec 1 x9659 (+ x9626 x9627) 1) (Vec x9615 x9660 (* x9629 x9630) 0))))) 2)) (&lt;&lt; (VecAdd (VecMul (VecAdd (VecAdd (VecMul (Vec 1 x9634 1 1 1 x9641 1 1) (Vec 0 x9635 0 0 x9607 x9642 0 0)) (VecMul (Vec x9604 1 (* x9619 x9620) 1 1 x9644 1 1) (Vec x9605 (+ x9637 x9638) (* x9622 x9623) 1 x9608 x9645 0 0))) (&lt;&lt; (VecAdd (VecMul (Vec 1 x9634 1 1 1 x9641 1 1) (Vec 0 x9635 0 0 x9607 x9642 0 0)) (VecMul (Vec x9604 1 (* x9619 x9620) 1 1 x9644 1 1) (Vec x9605 (+ x9637 x9638) (* x9622 x9623) 1 x9608 x9645 0 0))) 4)) (VecAdd (Vec (+ x9611 x9612) (* (+ x9649 x9650) (+ x9652 x9653)) 0 0) (VecAdd (Vec x9614 (* x9656 x9657) 0 0) (VecMul (Vec 1 x9659 (+ x9626 x9627) 1) (Vec x9615 x9660 (* x9629 x9630) 0))))) (&lt;&lt; (VecMul (VecAdd (VecAdd (VecMul (Vec 1 x9634 1 1 1 x9641 1 1) (Vec 0 x9635 0 0 x9607 x9642 0 0)) (VecMul (Vec x9604 1 (* x9619 x9620) 1 1 x9644 1 1) (Vec x9605 (+ x9637 x9638) (* x9622 x9623) 1 x9608 x9645 0 0))) (&lt;&lt; (VecAdd (VecMul (Vec 1 x9634 1 1 1 x9641 1 1) (Vec 0 x9635 0 0 x9607 x9642 0 0)) (VecMul (Vec x9604 1 (* x9619 x9620) 1 1 x9644 1 1) (Vec x9605 (+ x9637 x9638) (* x9622 x9623) 1 x9608 x9645 0 0))) 4)) (VecAdd (Vec (+ x9611 x9612) (* (+ x9649 x9650) (+ x9652 x9653)) 0 0) (VecAdd (Vec x9614 (* x9656 x9657) 0 0) (VecMul (Vec 1 x9659 (+ x9626 x9627) 1) (Vec x9615 x9660 (* x9629 x9630) 0))))) 2)) 1))</t>
         </is>
       </c>
       <c r="E108" t="n">
         <v>7760</v>
       </c>
       <c r="F108" t="n">
-        <v>7760</v>
+        <v>3092</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>60.15</v>
       </c>
       <c r="H108" t="n">
         <v>108.53</v>
       </c>
       <c r="I108" t="n">
-        <v>108.53</v>
+        <v>114.52</v>
       </c>
       <c r="J108" t="b">
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>8999891.470000001</v>
+        <v>8999885.48</v>
       </c>
       <c r="L108" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="109">
@@ -4999,29 +4999,29 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c23 1) (VecMinus (VecMinus (Vec 1 c12 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))) 0) (Vec c23 0 0 0)) (VecMinus (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)))))))))))))) (&lt;&lt; (VecMul (Vec (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c23 1) (VecMinus (VecMinus (Vec 1 c12 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))) 0) (Vec c23 0 0 0)) (VecMinus (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)))))))))))))) 2)) (Vec (- 1 c12) (+ (* (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) (- 1 c13)) (* c13 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (+ (* o5 (- 1 c15)) (* c15 o1)))))))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c23 1) (VecMinus (VecMinus (Vec 1 c12 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))) 0) (Vec c23 0 0 0)) (VecMinus (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)))))))))))))) (&lt;&lt; (VecMul (Vec (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c23 1) (VecMinus (VecMinus (Vec 1 c12 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))) 0) (Vec c23 0 0 0)) (VecMinus (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)))))))))))))) 2)) (Vec (- 1 c12) (+ (* (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) (- 1 c13)) (* c13 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (+ (* o5 (- 1 c15)) (* c15 o1)))))))) 1))</t>
+          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))) 0)) (&lt;&lt; (VecMul (Vec (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))) 0)) 2)) (VecAdd (VecMul (Vec 1 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- c13 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)) (VecMinus (Vec 1 1 0 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (+ (* o5 (- 1 c15)) (* c15 o1))))) (Vec c12 c13 0 0))) (&lt;&lt; (VecMul (Vec 1 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- c13 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)) (VecMinus (Vec 1 1 0 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (+ (* o5 (- 1 c15)) (* c15 o1))))) (Vec c12 c13 0 0))) 2))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))) 0)) (&lt;&lt; (VecMul (Vec (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c24)) (* c24 (+ (* o5 (- 1 c25)) (* c25 o2)))) 0)) 2)) (VecAdd (VecMul (Vec 1 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- c13 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)) (VecMinus (Vec 1 1 0 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (+ (* o5 (- 1 c15)) (* c15 o1))))) (Vec c12 c13 0 0))) (&lt;&lt; (VecMul (Vec 1 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c34)) (* c34 (+ (* o5 (- 1 c35)) (* c35 o3)))) 1 (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- (- c13 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0) 0)) (VecMinus (Vec 1 1 0 (+ (* (+ (* o5 (- 1 c45)) (* c45 o4)) (- 1 c14)) (* c14 (+ (* o5 (- 1 c15)) (* c15 o1))))) (Vec c12 c13 0 0))) 2))) 1))</t>
         </is>
       </c>
       <c r="E109" t="n">
         <v>15015</v>
       </c>
       <c r="F109" t="n">
-        <v>13595</v>
+        <v>29542</v>
       </c>
       <c r="G109" t="n">
-        <v>9.460000000000001</v>
+        <v>-96.75</v>
       </c>
       <c r="H109" t="n">
         <v>146.71</v>
       </c>
       <c r="I109" t="n">
-        <v>157.49</v>
+        <v>223.38</v>
       </c>
       <c r="J109" t="b">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>8999842.51</v>
+        <v>8999776.619999999</v>
       </c>
       <c r="L109" t="n">
         <v>75</v>
@@ -5041,17 +5041,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (Vec in_1_1 (+ in_1_2 in_1_1) (+ in_1_3 in_1_2) in_1_3 (+ in_2_1 in_2_0) (+ in_2_2 (+ in_2_1 in_2_0)) (+ in_2_3 (+ in_2_2 in_2_1)) (+ in_2_3 in_2_2) in_3_1 (+ in_3_2 (+ in_3_1 in_3_0)) (+ in_3_3 (+ in_3_2 in_3_1)) (+ in_3_3 in_3_2) in_3_1 (+ in_3_2 in_3_1) (+ in_3_3 in_3_2) in_3_3) (Vec in_1_0 (+ in_1_0 in_0_2) (+ in_1_1 in_0_3) in_1_2 (+ in_1_1 in_1_0) (+ in_1_2 in_1_1) (+ in_1_3 in_1_2) (+ in_1_3 in_1_2) in_3_0 (+ in_2_2 in_2_1) (+ in_2_3 in_2_2) (+ in_2_3 in_2_2) in_3_0 (+ in_3_0 in_2_2) (+ in_3_1 in_2_3) in_3_2)) (VecAdd (Vec in_0_1 in_0_1 in_0_2 in_0_3 in_0_1 (+ in_1_0 in_0_2) (+ in_1_1 in_0_3) in_0_3 (+ in_2_1 in_2_0) (+ in_2_0 in_1_2) (+ in_2_1 in_1_3) in_1_3 in_2_1 in_2_1 in_2_2 in_2_3) (VecAdd (Vec 0 0 0 0 0 in_0_1 in_0_2 0 in_1_1 in_1_1 in_1_2 0 0 0 0 0) (Vec in_0_0 in_0_0 in_0_1 in_0_2 in_0_0 in_0_0 in_0_1 in_0_2 in_1_0 in_1_0 in_1_1 in_1_2 in_2_0 in_2_0 in_2_1 in_2_2))))</t>
+          <t>(VecAdd (VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 0 in_2_1 in_2_2 in_2_3 in_2_3 0 in_3_2 in_3_3 in_3_3 0 in_3_2 in_3_3 0) (VecAdd (Vec 0 0 0 0 0 in_2_1 in_2_2 0 0 in_3_1 in_3_2 0 0 0 0 0) (Vec in_1_1 in_1_1 in_1_2 in_1_3 in_2_0 in_2_0 in_2_1 in_2_2 in_3_1 in_3_0 in_3_1 in_3_2 in_3_1 in_3_1 in_3_2 in_3_3))) (VecAdd (Vec 0 in_1_0 in_1_1 0 in_1_1 in_1_2 in_1_3 in_1_3 0 in_2_2 in_2_3 in_2_3 0 in_3_0 in_3_1 0) (Vec in_1_0 in_0_2 in_0_3 in_1_2 in_1_0 in_1_1 in_1_2 in_1_2 in_3_0 in_2_1 in_2_2 in_2_2 in_3_0 in_2_2 in_2_3 in_3_2))) (VecAdd (VecAdd (Vec 0 0 0 0 0 in_1_0 in_1_1 0 in_2_1 in_2_0 in_2_1 0 0 0 0 0) (Vec in_0_1 in_0_1 in_0_2 in_0_3 in_0_1 in_0_2 in_0_3 in_0_3 in_2_0 in_1_2 in_1_3 in_1_3 in_2_1 in_2_1 in_2_2 in_2_3)) (VecAdd (Vec 0 0 0 0 0 in_0_1 in_0_2 0 in_1_1 in_1_1 in_1_2 0 0 0 0 0) (Vec in_0_0 in_0_0 in_0_1 in_0_2 in_0_0 in_0_0 in_0_1 in_0_2 in_1_0 in_1_0 in_1_1 in_1_2 in_2_0 in_2_0 in_2_1 in_2_2))))</t>
         </is>
       </c>
       <c r="E110" t="n">
         <v>21006</v>
       </c>
       <c r="F110" t="n">
-        <v>7760</v>
+        <v>14</v>
       </c>
       <c r="G110" t="n">
-        <v>63.06</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="H110" t="n">
         <v>7.19</v>
@@ -5066,7 +5066,7 @@
         <v>8999992.810000001</v>
       </c>
       <c r="L110" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111">
@@ -5083,17 +5083,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3) (VecAdd (Vec 2 2 2 2) (Vec (* v1_0 5) (* v1_1 5) (* v1_2 5) (* v1_3 5))))</t>
+          <t>(VecAdd (Vec v2_0 v2_1 v2_2 v2_3) (VecAdd (Vec 2 2 2 2) (VecMul (Vec v1_0 v1_1 v1_2 v1_3) (Vec 5 5 5 5))))</t>
         </is>
       </c>
       <c r="E111" t="n">
         <v>3006</v>
       </c>
       <c r="F111" t="n">
-        <v>1008</v>
+        <v>108</v>
       </c>
       <c r="G111" t="n">
-        <v>66.47</v>
+        <v>96.41</v>
       </c>
       <c r="H111" t="n">
         <v>39.37</v>
@@ -5108,7 +5108,7 @@
         <v>8999960.630000001</v>
       </c>
       <c r="L111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112">
@@ -5167,32 +5167,32 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( - ( + v1_0 v2_0 ) ( * ( * v1_0 v2_0 ) 2 ) ) ( - ( + v1_1 v2_1 ) ( * 2 ( * v1_1 v2_1 ) ) ) ) ( - ( + v1_2 v2_2 ) ( * 2 ( * v1_2 v2_2 ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2 v1_1 0 v2_0 v2_2 v2_1 0) (&lt;&lt; (Vec v1_0 v1_2 v1_1 0 v2_0 v2_2 v2_1 0) 4)) (VecMul (Vec (* v1_0 v2_0) 2 2 1) (VecMul (Vec 1 v1_2 v1_1 1) (Vec 2 v2_2 v2_1 0)))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_2 v1_1 0 v2_0 v2_2 v2_1 0) (&lt;&lt; (Vec v1_0 v1_2 v1_1 0 v2_0 v2_2 v2_1 0) 4)) (VecMul (Vec (* v1_0 v2_0) 2 2 1) (VecMul (Vec 1 v1_2 v1_1 1) (Vec 2 v2_2 v2_1 0)))) 2)) (&lt;&lt; (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2 v1_1 0 v2_0 v2_2 v2_1 0) (&lt;&lt; (Vec v1_0 v1_2 v1_1 0 v2_0 v2_2 v2_1 0) 4)) (VecMul (Vec (* v1_0 v2_0) 2 2 1) (VecMul (Vec 1 v1_2 v1_1 1) (Vec 2 v2_2 v2_1 0)))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_2 v1_1 0 v2_0 v2_2 v2_1 0) (&lt;&lt; (Vec v1_0 v1_2 v1_1 0 v2_0 v2_2 v2_1 0) 4)) (VecMul (Vec (* v1_0 v2_0) 2 2 1) (VecMul (Vec 1 v1_2 v1_1 1) (Vec 2 v2_2 v2_1 0)))) 2)) 1))</t>
         </is>
       </c>
       <c r="E113" t="n">
         <v>3509</v>
       </c>
       <c r="F113" t="n">
-        <v>3509</v>
+        <v>636</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>81.88</v>
       </c>
       <c r="H113" t="n">
         <v>75.15000000000001</v>
       </c>
       <c r="I113" t="n">
-        <v>75.15000000000001</v>
+        <v>77.55</v>
       </c>
       <c r="J113" t="b">
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>8999924.85</v>
+        <v>8999922.449999999</v>
       </c>
       <c r="L113" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114">
@@ -5209,32 +5209,32 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( - ( + v1_0 v2_0 ) ( * ( * v1_0 v2_0 ) 2 ) ) ( - ( + v1_1 v2_1 ) ( * 2 ( * v1_1 v2_1 ) ) ) ) ( + ( + ( - ( + v1_2 v2_2 ) ( * 2 ( * v1_2 v2_2 ) ) ) ( - ( + v1_3 v2_3 ) ( * 2 ( * v1_3 v2_3 ) ) ) ) ( - ( + v1_4 v2_4 ) ( * 2 ( * v1_4 v2_4 ) ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2 0 v1_3) (Vec v2_0 v2_2 0 v2_3)) (VecMul (Vec (* v1_0 v2_0) 2 1 2) (VecMul (Vec 1 v1_2 1 v1_3) (Vec 2 v2_2 0 v2_3)))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_2 0 v1_3) (Vec v2_0 v2_2 0 v2_3)) (VecMul (Vec (* v1_0 v2_0) 2 1 2) (VecMul (Vec 1 v1_2 1 v1_3) (Vec 2 v2_2 0 v2_3)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4) (Vec v2_1 v2_4)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_4) (Vec v2_1 v2_4))))) (&lt;&lt; (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_2 0 v1_3) (Vec v2_0 v2_2 0 v2_3)) (VecMul (Vec (* v1_0 v2_0) 2 1 2) (VecMul (Vec 1 v1_2 1 v1_3) (Vec 2 v2_2 0 v2_3)))) (&lt;&lt; (VecMinus (VecAdd (Vec v1_0 v1_2 0 v1_3) (Vec v2_0 v2_2 0 v2_3)) (VecMul (Vec (* v1_0 v2_0) 2 1 2) (VecMul (Vec 1 v1_2 1 v1_3) (Vec 2 v2_2 0 v2_3)))) 2)) (VecMinus (VecAdd (Vec v1_1 v1_4) (Vec v2_1 v2_4)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_4) (Vec v2_1 v2_4))))) 1))</t>
         </is>
       </c>
       <c r="E114" t="n">
         <v>6010</v>
       </c>
       <c r="F114" t="n">
-        <v>6010</v>
+        <v>774</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>87.12</v>
       </c>
       <c r="H114" t="n">
         <v>76.34999999999999</v>
       </c>
       <c r="I114" t="n">
-        <v>76.34999999999999</v>
+        <v>78.75</v>
       </c>
       <c r="J114" t="b">
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>8999923.65</v>
+        <v>8999921.25</v>
       </c>
       <c r="L114" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115">
@@ -5251,32 +5251,32 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (Vec (* v1_0 v2_0) 2) (Vec 2 (* v1_8 v2_8)))) (VecMinus (VecAdd (Vec v1_1 v1_9) (Vec v2_1 v2_9)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_9) (Vec v2_1 v2_9))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_10) (Vec v2_2 v2_10)))) (VecMinus (VecAdd (Vec v1_3 v1_11) (Vec v2_3 v2_11)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_11) (Vec v2_3 v2_11)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (Vec 2 2) (VecMul (Vec v1_4 v1_12) (Vec v2_4 v2_12)))) (VecMinus (VecAdd (Vec v1_5 v1_13) (Vec v2_5 v2_13)) (VecMul (Vec 2 2) (VecMul (Vec v1_5 v1_13) (Vec v2_5 v2_13))))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (Vec 2 2) (VecMul (Vec v1_6 v1_14) (Vec v2_6 v2_14)))) (VecMinus (VecAdd (Vec v1_7 v1_15) (Vec v2_7 v2_15)) (VecMul (Vec 2 2) (VecMul (Vec v1_7 v1_15) (Vec v2_7 v2_15))))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (Vec (* v1_0 v2_0) 2) (Vec 2 (* v1_8 v2_8)))) (VecMinus (VecAdd (Vec v1_1 v1_9) (Vec v2_1 v2_9)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_9) (Vec v2_1 v2_9))))) (VecAdd (VecMinus (VecAdd (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_10) (Vec v2_2 v2_10)))) (VecMinus (VecAdd (Vec v1_3 v1_11) (Vec v2_3 v2_11)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_11) (Vec v2_3 v2_11)))))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (Vec 2 2) (VecMul (Vec v1_4 v1_12) (Vec v2_4 v2_12)))) (VecMinus (VecAdd (Vec v1_5 v1_13) (Vec v2_5 v2_13)) (VecMul (Vec 2 2) (VecMul (Vec v1_5 v1_13) (Vec v2_5 v2_13))))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (Vec 2 2) (VecMul (Vec v1_6 v1_14) (Vec v2_6 v2_14)))) (VecMinus (VecAdd (Vec v1_7 v1_15) (Vec v2_7 v2_15)) (VecMul (Vec 2 2) (VecMul (Vec v1_7 v1_15) (Vec v2_7 v2_15))))))) 1))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (VecMul (Vec v1_0 2 v2_0 1) (&lt;&lt; (Vec v1_0 2 v2_0 1) 2)) (VecMul (Vec 2 v1_8 1 v2_8) (&lt;&lt; (Vec 2 v1_8 1 v2_8) 2)))) (VecMinus (VecAdd (Vec v1_1 v1_9) (Vec v2_1 v2_9)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_9) (Vec v2_1 v2_9))))) (VecMinus (VecAdd (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_10) (Vec v2_2 v2_10))))) (VecMinus (VecAdd (Vec v1_3 v1_11) (Vec v2_3 v2_11)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_11) (Vec v2_3 v2_11))))) (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (Vec 2 2) (VecMul (Vec v1_4 v1_12) (Vec v2_4 v2_12)))) (VecAdd (VecMinus (VecAdd (Vec v1_5 v1_13) (Vec v2_5 v2_13)) (VecMul (Vec 2 2) (VecMul (Vec v1_5 v1_13) (Vec v2_5 v2_13)))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (Vec 2 2) (VecMul (Vec v1_6 v1_14) (Vec v2_6 v2_14)))) (VecMinus (VecAdd (Vec v1_7 v1_15) (Vec v2_7 v2_15)) (VecMul (Vec 2 2) (VecMul (Vec v1_7 v1_15) (Vec v2_7 v2_15))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (VecMul (Vec v1_0 2 v2_0 1) (&lt;&lt; (Vec v1_0 2 v2_0 1) 2)) (VecMul (Vec 2 v1_8 1 v2_8) (&lt;&lt; (Vec 2 v1_8 1 v2_8) 2)))) (VecMinus (VecAdd (Vec v1_1 v1_9) (Vec v2_1 v2_9)) (VecMul (Vec 2 2) (VecMul (Vec v1_1 v1_9) (Vec v2_1 v2_9))))) (VecMinus (VecAdd (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (Vec 2 2) (VecMul (Vec v1_2 v1_10) (Vec v2_2 v2_10))))) (VecAdd (VecMinus (VecAdd (Vec v1_3 v1_11) (Vec v2_3 v2_11)) (VecMul (Vec 2 2) (VecMul (Vec v1_3 v1_11) (Vec v2_3 v2_11)))) (VecAdd (VecAdd (VecMinus (VecAdd (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (Vec 2 2) (VecMul (Vec v1_4 v1_12) (Vec v2_4 v2_12)))) (VecMinus (VecAdd (Vec v1_5 v1_13) (Vec v2_5 v2_13)) (VecMul (Vec 2 2) (VecMul (Vec v1_5 v1_13) (Vec v2_5 v2_13))))) (VecAdd (VecMinus (VecAdd (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (Vec 2 2) (VecMul (Vec v1_6 v1_14) (Vec v2_6 v2_14)))) (VecMinus (VecAdd (Vec v1_7 v1_15) (Vec v2_7 v2_15)) (VecMul (Vec 2 2) (VecMul (Vec v1_7 v1_15) (Vec v2_7 v2_15)))))))) 1)))))</t>
         </is>
       </c>
       <c r="E115" t="n">
         <v>19761</v>
       </c>
       <c r="F115" t="n">
-        <v>2087</v>
+        <v>1899</v>
       </c>
       <c r="G115" t="n">
-        <v>89.44</v>
+        <v>90.39</v>
       </c>
       <c r="H115" t="n">
         <v>77.55</v>
       </c>
       <c r="I115" t="n">
-        <v>78.75</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="J115" t="b">
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>8999921.25</v>
+        <v>8999916.460000001</v>
       </c>
       <c r="L115" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="116">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>(VecAdd (Vec c1_0 c1_1 c1_2 c1_3) (VecAdd (Vec c2_0 c2_1 c2_2 c2_3) (Vec (* c0_0 (+ c3_0 (* c0_0 c4_0))) (* c0_1 (+ c3_1 (* c0_1 c4_1))) (* c0_2 (+ c3_2 (* c0_2 c4_2))) (* c0_3 (+ c3_3 (* c0_3 c4_3))))))</t>
+          <t>(VecAdd (Vec c1_0 c1_1 c1_2 c1_3) (VecAdd (Vec c2_0 c2_1 c2_2 c2_3) (VecMul (Vec c0_0 c0_1 c0_2 c0_3) (VecAdd (Vec c3_0 c3_1 c3_2 c3_3) (VecMul (Vec c0_0 c0_1 c0_2 c0_3) (Vec c4_0 c4_1 c4_2 c4_3))))))</t>
         </is>
       </c>
       <c r="E116" t="n">
         <v>5009</v>
       </c>
       <c r="F116" t="n">
-        <v>3011</v>
+        <v>212</v>
       </c>
       <c r="G116" t="n">
-        <v>39.89</v>
+        <v>95.77</v>
       </c>
       <c r="H116" t="n">
         <v>75.15000000000001</v>
@@ -5318,7 +5318,7 @@
         <v>8999924.85</v>
       </c>
       <c r="L116" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="117">
@@ -5377,32 +5377,32 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2 c2_1 1) (Vec c1_0 c1_2 c1_1 0)) (VecMinus (Vec c2_0 c2_2 c2_1 0) (Vec c1_0 c1_2 c1_1 0))) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_2 c2_1 1) (Vec c1_0 c1_2 c1_1 0)) (VecMinus (Vec c2_0 c2_2 c2_1 0) (Vec c1_0 c1_2 c1_1 0))) 2)) (&lt;&lt; (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2 c2_1 1) (Vec c1_0 c1_2 c1_1 0)) (VecMinus (Vec c2_0 c2_2 c2_1 0) (Vec c1_0 c1_2 c1_1 0))) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_2 c2_1 1) (Vec c1_0 c1_2 c1_1 0)) (VecMinus (Vec c2_0 c2_2 c2_1 0) (Vec c1_0 c1_2 c1_1 0))) 2)) 1))</t>
         </is>
       </c>
       <c r="E118" t="n">
         <v>2757</v>
       </c>
       <c r="F118" t="n">
-        <v>2757</v>
+        <v>218</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>92.09</v>
       </c>
       <c r="H118" t="n">
         <v>40.57</v>
       </c>
       <c r="I118" t="n">
-        <v>40.57</v>
+        <v>42.97</v>
       </c>
       <c r="J118" t="b">
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>8999959.43</v>
+        <v>8999957.029999999</v>
       </c>
       <c r="L118" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="119">
@@ -5419,32 +5419,32 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * ( - c2_0 c1_0 ) ( - c2_0 c1_0 ) ) ( * ( - c2_1 c1_1 ) ( - c2_1 c1_1 ) ) ) ( + ( + ( * ( - c2_2 c1_2 ) ( - c2_2 c1_2 ) ) ( * ( - c2_3 c1_3 ) ( - c2_3 c1_3 ) ) ) ( * ( - c2_4 c1_4 ) ( - c2_4 c1_4 ) ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2 1 c2_3) (Vec c1_0 c1_2 0 c1_3)) (VecMinus (Vec c2_0 c2_2 0 c2_3) (Vec c1_0 c1_2 0 c1_3))) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_2 1 c2_3) (Vec c1_0 c1_2 0 c1_3)) (VecMinus (Vec c2_0 c2_2 0 c2_3) (Vec c1_0 c1_2 0 c1_3))) 2)) (VecMul (VecMinus (Vec c2_1 c2_4) (Vec c1_1 c1_4)) (VecMinus (Vec c2_1 c2_4) (Vec c1_1 c1_4)))) (&lt;&lt; (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_2 1 c2_3) (Vec c1_0 c1_2 0 c1_3)) (VecMinus (Vec c2_0 c2_2 0 c2_3) (Vec c1_0 c1_2 0 c1_3))) (&lt;&lt; (VecMul (VecMinus (Vec c2_0 c2_2 1 c2_3) (Vec c1_0 c1_2 0 c1_3)) (VecMinus (Vec c2_0 c2_2 0 c2_3) (Vec c1_0 c1_2 0 c1_3))) 2)) (VecMul (VecMinus (Vec c2_1 c2_4) (Vec c1_1 c1_4)) (VecMinus (Vec c2_1 c2_4) (Vec c1_1 c1_4)))) 1))</t>
         </is>
       </c>
       <c r="E119" t="n">
         <v>4758</v>
       </c>
       <c r="F119" t="n">
-        <v>4758</v>
+        <v>322</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>93.23</v>
       </c>
       <c r="H119" t="n">
         <v>41.77</v>
       </c>
       <c r="I119" t="n">
-        <v>41.77</v>
+        <v>44.16</v>
       </c>
       <c r="J119" t="b">
         <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>8999958.23</v>
+        <v>8999955.84</v>
       </c>
       <c r="L119" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="120">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8) (Vec c1_0 c1_8)) (VecMinus (Vec c2_0 c2_8) (Vec c1_0 c1_8))) (VecMul (VecMinus (Vec c2_1 c2_9) (Vec c1_1 c1_9)) (VecMinus (Vec c2_1 c2_9) (Vec c1_1 c1_9)))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_10) (Vec c1_2 c1_10)) (VecMinus (Vec c2_2 c2_10) (Vec c1_2 c1_10))) (VecMul (VecMinus (Vec c2_3 c2_11) (Vec c1_3 c1_11)) (VecMinus (Vec c2_3 c2_11) (Vec c1_3 c1_11))))) (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_12) (Vec c1_4 c1_12)) (VecMinus (Vec c2_4 c2_12) (Vec c1_4 c1_12))) (VecMul (VecMinus (Vec c2_5 c2_13) (Vec c1_5 c1_13)) (VecMinus (Vec c2_5 c2_13) (Vec c1_5 c1_13)))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14) (Vec c1_6 c1_14)) (VecMinus (Vec c2_6 c2_14) (Vec c1_6 c1_14))) (VecMul (VecMinus (Vec c2_7 c2_15) (Vec c1_7 c1_15)) (VecMinus (Vec c2_7 c2_15) (Vec c1_7 c1_15))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8) (Vec c1_0 c1_8)) (VecMinus (Vec c2_0 c2_8) (Vec c1_0 c1_8))) (VecMul (VecMinus (Vec c2_1 c2_9) (Vec c1_1 c1_9)) (VecMinus (Vec c2_1 c2_9) (Vec c1_1 c1_9)))) (VecAdd (VecMul (VecMinus (Vec c2_2 c2_10) (Vec c1_2 c1_10)) (VecMinus (Vec c2_2 c2_10) (Vec c1_2 c1_10))) (VecMul (VecMinus (Vec c2_3 c2_11) (Vec c1_3 c1_11)) (VecMinus (Vec c2_3 c2_11) (Vec c1_3 c1_11))))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_12) (Vec c1_4 c1_12)) (VecMinus (Vec c2_4 c2_12) (Vec c1_4 c1_12))) (VecMul (VecMinus (Vec c2_5 c2_13) (Vec c1_5 c1_13)) (VecMinus (Vec c2_5 c2_13) (Vec c1_5 c1_13)))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14) (Vec c1_6 c1_14)) (VecMinus (Vec c2_6 c2_14) (Vec c1_6 c1_14))) (VecMul (VecMinus (Vec c2_7 c2_15) (Vec c1_7 c1_15)) (VecMinus (Vec c2_7 c2_15) (Vec c1_7 c1_15)))))) 1)))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8) (Vec c1_0 c1_8)) (VecMinus (Vec c2_0 c2_8) (Vec c1_0 c1_8))) (VecMul (VecMinus (Vec c2_1 c2_9) (Vec c1_1 c1_9)) (VecMinus (Vec c2_1 c2_9) (Vec c1_1 c1_9)))) (VecMul (VecMinus (Vec c2_2 c2_10) (Vec c1_2 c1_10)) (VecMinus (Vec c2_2 c2_10) (Vec c1_2 c1_10)))) (VecMul (VecMinus (Vec c2_3 c2_11) (Vec c1_3 c1_11)) (VecMinus (Vec c2_3 c2_11) (Vec c1_3 c1_11)))) (VecAdd (VecMul (VecMinus (Vec c2_4 c2_12) (Vec c1_4 c1_12)) (VecMinus (Vec c2_4 c2_12) (Vec c1_4 c1_12))) (VecAdd (VecMul (VecMinus (Vec c2_5 c2_13) (Vec c1_5 c1_13)) (VecMinus (Vec c2_5 c2_13) (Vec c1_5 c1_13))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14) (Vec c1_6 c1_14)) (VecMinus (Vec c2_6 c2_14) (Vec c1_6 c1_14))) (VecMul (VecMinus (Vec c2_7 c2_15) (Vec c1_7 c1_15)) (VecMinus (Vec c2_7 c2_15) (Vec c1_7 c1_15)))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_0 c2_8) (Vec c1_0 c1_8)) (VecMinus (Vec c2_0 c2_8) (Vec c1_0 c1_8))) (VecMul (VecMinus (Vec c2_1 c2_9) (Vec c1_1 c1_9)) (VecMinus (Vec c2_1 c2_9) (Vec c1_1 c1_9)))) (VecMul (VecMinus (Vec c2_2 c2_10) (Vec c1_2 c1_10)) (VecMinus (Vec c2_2 c2_10) (Vec c1_2 c1_10)))) (VecAdd (VecMul (VecMinus (Vec c2_3 c2_11) (Vec c1_3 c1_11)) (VecMinus (Vec c2_3 c2_11) (Vec c1_3 c1_11))) (VecAdd (VecAdd (VecMul (VecMinus (Vec c2_4 c2_12) (Vec c1_4 c1_12)) (VecMinus (Vec c2_4 c2_12) (Vec c1_4 c1_12))) (VecMul (VecMinus (Vec c2_5 c2_13) (Vec c1_5 c1_13)) (VecMinus (Vec c2_5 c2_13) (Vec c1_5 c1_13)))) (VecAdd (VecMul (VecMinus (Vec c2_6 c2_14) (Vec c1_6 c1_14)) (VecMinus (Vec c2_6 c2_14) (Vec c1_6 c1_14))) (VecMul (VecMinus (Vec c2_7 c2_15) (Vec c1_7 c1_15)) (VecMinus (Vec c2_7 c2_15) (Vec c1_7 c1_15))))))) 1)))))</t>
         </is>
       </c>
       <c r="E120" t="n">
         <v>15759</v>
       </c>
       <c r="F120" t="n">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="G120" t="n">
-        <v>94.38</v>
+        <v>94.36</v>
       </c>
       <c r="H120" t="n">
         <v>42.97</v>
       </c>
       <c r="I120" t="n">
-        <v>45.36</v>
+        <v>48.96</v>
       </c>
       <c r="J120" t="b">
         <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>8999954.640000001</v>
+        <v>8999951.039999999</v>
       </c>
       <c r="L120" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="121">
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( * v1_2 v2_2 ) ) )</t>
+          <t>(VecAdd (VecAdd (VecMul (Vec v1_0 v1_2 v1_1 1) (Vec v2_0 v2_2 v2_1 0)) (&lt;&lt; (VecMul (Vec v1_0 v1_2 v1_1 1) (Vec v2_0 v2_2 v2_1 0)) 2)) (&lt;&lt; (VecAdd (VecMul (Vec v1_0 v1_2 v1_1 1) (Vec v2_0 v2_2 v2_1 0)) (&lt;&lt; (VecMul (Vec v1_0 v1_2 v1_1 1) (Vec v2_0 v2_2 v2_1 0)) 2)) 1))</t>
         </is>
       </c>
       <c r="E121" t="n">
         <v>1256</v>
       </c>
       <c r="F121" t="n">
-        <v>1256</v>
+        <v>215</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>82.88</v>
       </c>
       <c r="H121" t="n">
         <v>39.37</v>
       </c>
       <c r="I121" t="n">
-        <v>39.37</v>
+        <v>41.77</v>
       </c>
       <c r="J121" t="b">
         <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>8999960.630000001</v>
+        <v>8999958.23</v>
       </c>
       <c r="L121" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122">
@@ -5545,32 +5545,32 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>(Vec ( + ( + ( * v1_0 v2_0 ) ( * v1_1 v2_1 ) ) ( + ( + ( * v1_2 v2_2 ) ( * v1_3 v2_3 ) ) ( * v1_4 v2_4 ) ) ) )</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_2 1 v1_3) (Vec v2_0 v2_2 0 v2_3)) (&lt;&lt; (VecMul (Vec v1_0 v1_2 1 v1_3) (Vec v2_0 v2_2 0 v2_3)) 2)) (VecMul (Vec v1_1 v1_4) (Vec v2_1 v2_4))) (&lt;&lt; (VecAdd (VecAdd (VecMul (Vec v1_0 v1_2 1 v1_3) (Vec v2_0 v2_2 0 v2_3)) (&lt;&lt; (VecMul (Vec v1_0 v1_2 1 v1_3) (Vec v2_0 v2_2 0 v2_3)) 2)) (VecMul (Vec v1_1 v1_4) (Vec v2_1 v2_4))) 1))</t>
         </is>
       </c>
       <c r="E122" t="n">
         <v>2257</v>
       </c>
       <c r="F122" t="n">
-        <v>2257</v>
+        <v>317</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>85.95</v>
       </c>
       <c r="H122" t="n">
         <v>40.57</v>
       </c>
       <c r="I122" t="n">
-        <v>40.57</v>
+        <v>42.97</v>
       </c>
       <c r="J122" t="b">
         <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>8999959.43</v>
+        <v>8999957.029999999</v>
       </c>
       <c r="L122" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123">
@@ -5587,32 +5587,32 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (VecMul (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (Vec v1_1 v1_9) (Vec v2_1 v2_9))) (VecAdd (VecAdd (VecMul (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (Vec v1_3 v1_11) (Vec v2_3 v2_11))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (Vec v1_5 v1_13) (Vec v2_5 v2_13))) (VecAdd (VecAdd (VecMul (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (Vec v1_7 v1_15) (Vec v2_7 v2_15))) (&lt;&lt; (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (Vec v1_1 v1_9) (Vec v2_1 v2_9))) (VecAdd (VecAdd (VecMul (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (Vec v1_3 v1_11) (Vec v2_3 v2_11))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (Vec v1_5 v1_13) (Vec v2_5 v2_13))) (VecAdd (VecMul (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (Vec v1_7 v1_15) (Vec v2_7 v2_15)))))) 1)))))</t>
+          <t>(VecAdd (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (Vec v1_1 v1_9) (Vec v2_1 v2_9))) (VecAdd (VecMul (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (Vec v1_3 v1_11) (Vec v2_3 v2_11)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (Vec v1_5 v1_13) (Vec v2_5 v2_13))) (VecAdd (VecMul (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (Vec v1_7 v1_15) (Vec v2_7 v2_15))))) (&lt;&lt; (VecAdd (VecAdd (VecAdd (VecMul (Vec v1_0 v1_8) (Vec v2_0 v2_8)) (VecMul (Vec v1_1 v1_9) (Vec v2_1 v2_9))) (VecAdd (VecMul (Vec v1_2 v1_10) (Vec v2_2 v2_10)) (VecMul (Vec v1_3 v1_11) (Vec v2_3 v2_11)))) (VecAdd (VecAdd (VecMul (Vec v1_4 v1_12) (Vec v2_4 v2_12)) (VecMul (Vec v1_5 v1_13) (Vec v2_5 v2_13))) (VecAdd (VecMul (Vec v1_6 v1_14) (Vec v2_6 v2_14)) (VecMul (Vec v1_7 v1_15) (Vec v2_7 v2_15))))) 1))</t>
         </is>
       </c>
       <c r="E123" t="n">
         <v>7758</v>
       </c>
       <c r="F123" t="n">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="G123" t="n">
-        <v>88.76000000000001</v>
+        <v>88.81</v>
       </c>
       <c r="H123" t="n">
         <v>41.77</v>
       </c>
       <c r="I123" t="n">
-        <v>47.76</v>
+        <v>42.97</v>
       </c>
       <c r="J123" t="b">
         <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>8999952.24</v>
+        <v>8999957.029999999</v>
       </c>
       <c r="L123" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="124">
@@ -5629,32 +5629,32 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (Vec 0 in_1_2 0 0 in_2_2 0 0 in_1_2 0) (Vec in_1_1 (- in_1_0) (- in_1_1) in_2_1 (- in_2_0) (- in_2_1) in_1_1 (- in_1_0) (- in_1_1))) (VecAdd (Vec 0 (* in_0_2 2) 0 in_0_1 (+ in_0_2 (- in_0_0)) (- in_0_1) 0 (* in_2_2 2) 0) (Vec (* in_0_1 2) (* in_0_0 -2) (* in_0_1 -2) (* in_1_1 2) (+ (* in_1_2 2) (* in_1_0 -2)) (* in_1_1 -2) (* in_2_1 2) (* in_2_0 -2) (* in_2_1 -2))))</t>
+          <t>(VecAdd (VecAdd (Vec 0 in_1_2 0 0 in_2_2 0 0 in_1_2 0) (VecMinus (Vec in_1_1 in_1_0 in_1_1 in_2_1 in_2_0 in_2_1 in_1_1 in_1_0 in_1_1 0 in_1_0 in_1_1 0 in_2_0 in_2_1 0 in_1_0 in_1_1) (&lt;&lt; (Vec in_1_1 in_1_0 in_1_1 in_2_1 in_2_0 in_2_1 in_1_1 in_1_0 in_1_1 0 in_1_0 in_1_1 0 in_2_0 in_2_1 0 in_1_0 in_1_1) 9))) (VecAdd (VecMul (Vec 1 in_0_2 1 1 1 1 1 in_2_2 1) (Vec 0 2 0 in_0_1 (+ in_0_2 (- in_0_0)) (- in_0_1) 0 2 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_1_1 1 in_1_1 in_2_1 in_2_0 in_2_1) (Vec 2 -2 -2 2 (+ (* in_1_2 2) (* in_1_0 -2)) -2 2 -2 -2))))</t>
         </is>
       </c>
       <c r="E124" t="n">
         <v>9757</v>
       </c>
       <c r="F124" t="n">
-        <v>5510</v>
+        <v>1772</v>
       </c>
       <c r="G124" t="n">
-        <v>43.53</v>
+        <v>81.84</v>
       </c>
       <c r="H124" t="n">
         <v>40.57</v>
       </c>
       <c r="I124" t="n">
-        <v>40.57</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J124" t="b">
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>8999959.43</v>
+        <v>8999924.85</v>
       </c>
       <c r="L124" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125">
@@ -5671,32 +5671,32 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>(VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 in_3_2 in_3_3 in_3_4 0 0 in_4_2 in_4_3 in_4_4 0 0 in_3_2 in_3_3 in_3_4 0) (Vec in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) (- in_1_3) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) (- in_2_3) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) (- in_3_3) in_4_1 (- in_4_0) (- in_4_1) (- in_4_2) (- in_4_3) in_3_1 (- in_3_0) (- in_3_1) (- in_3_2) (- in_3_3))) (VecAdd (VecAdd (Vec 0 0 0 0 0 0 in_0_2 in_0_3 in_0_4 0 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 0 0 0 0) (VecMul (Vec 1 in_0_2 in_0_3 in_0_4 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_4_2 in_4_3 in_4_4 1) (Vec 0 2 2 2 0 in_0_1 (- in_0_0) (- in_0_1) (- in_0_2) (- in_0_3) in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) (- in_1_3) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) (- in_2_3) 0 2 2 2 0))) (VecAdd (Vec 0 0 0 0 0 0 (* in_1_2 2) (* in_1_3 2) (* in_1_4 2) 0 0 (* in_2_2 2) (* in_2_3 2) (* in_2_4 2) 0 0 (* in_3_2 2) (* in_3_3 2) (* in_3_4 2) 0 0 0 0 0 0) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_0_3 in_1_1 in_1_0 in_1_1 in_1_2 in_1_3 in_2_1 in_2_0 in_2_1 in_2_2 in_2_3 in_3_1 in_3_0 in_3_1 in_3_2 in_3_3 in_4_1 in_4_0 in_4_1 in_4_2 in_4_3) (Vec 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2)))))</t>
+          <t>(VecAdd (VecAdd (Vec 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 in_3_2 in_3_3 in_3_4 0 0 in_4_2 in_4_3 in_4_4 0 0 in_3_2 in_3_3 in_3_4 0) (VecNeg (Vec in_1_1 in_1_0 in_1_1 in_1_2 in_1_3 in_2_1 in_2_0 in_2_1 in_2_2 in_2_3 in_3_1 in_3_0 in_3_1 in_3_2 in_3_3 in_4_1 in_4_0 in_4_1 in_4_2 in_4_3 in_3_1 in_3_0 in_3_1 in_3_2 in_3_3))) (VecAdd (VecAdd (Vec 0 0 0 0 0 0 in_0_2 in_0_3 in_0_4 0 0 in_1_2 in_1_3 in_1_4 0 0 in_2_2 in_2_3 in_2_4 0 0 0 0 0 0) (VecMul (Vec 1 in_0_2 in_0_3 in_0_4 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 1 in_4_2 in_4_3 in_4_4 1) (Vec 0 2 2 2 0 in_0_1 (- in_0_0) (- in_0_1) (- in_0_2) (- in_0_3) in_1_1 (- in_1_0) (- in_1_1) (- in_1_2) (- in_1_3) in_2_1 (- in_2_0) (- in_2_1) (- in_2_2) (- in_2_3) 0 2 2 2 0))) (VecAdd (VecMul (Vec 1 1 1 1 1 1 in_1_2 in_1_3 in_1_4 1 1 in_2_2 in_2_3 in_2_4 1 1 in_3_2 in_3_3 in_3_4 1 1 1 1 1 1) (Vec 0 0 0 0 0 0 2 2 2 0 0 2 2 2 0 0 2 2 2 0 0 0 0 0 0)) (VecMul (Vec in_0_1 in_0_0 in_0_1 in_0_2 in_0_3 in_1_1 in_1_0 in_1_1 in_1_2 in_1_3 in_2_1 in_2_0 in_2_1 in_2_2 in_2_3 in_3_1 in_3_0 in_3_1 in_3_2 in_3_3 in_4_1 in_4_0 in_4_1 in_4_2 in_4_3) (Vec 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2 2 -2 -2 -2 -2)))))</t>
         </is>
       </c>
       <c r="E125" t="n">
         <v>37757</v>
       </c>
       <c r="F125" t="n">
-        <v>10463</v>
+        <v>3314</v>
       </c>
       <c r="G125" t="n">
-        <v>72.29000000000001</v>
+        <v>91.22</v>
       </c>
       <c r="H125" t="n">
         <v>40.57</v>
       </c>
       <c r="I125" t="n">
-        <v>41.77</v>
+        <v>42.8</v>
       </c>
       <c r="J125" t="b">
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>8999958.23</v>
+        <v>8999957.199999999</v>
       </c>
       <c r="L125" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="126">
@@ -5755,32 +5755,32 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>(Vec ( + ( * ( + ( * ( + ( * o4 ( - 1 c34 ) ) ( * c34 o3 ) ) ( - 1 c23 ) ) ( * c23 ( + ( * o4 ( - 1 c24 ) ) ( * c24 o2 ) ) ) ) ( - 1 c12 ) ) ( * c12 ( + ( * ( + ( * o4 ( - 1 c34 ) ) ( * c34 o3 ) ) ( - 1 c13 ) ) ( * c13 ( + ( * o4 ( - 1 c14 ) ) ( * c14 o1 ) ) ) ) ) ) )</t>
+          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c23 1) (Vec (- 1 c23) c12 (* 1 (+ (* o4 (- 1 c24)) (* c24 o2))) 0)) (&lt;&lt; (VecMul (Vec (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c23 1) (Vec (- 1 c23) c12 (* 1 (+ (* o4 (- 1 c24)) (* c24 o2))) 0)) 2)) (VecAdd (VecMul (Vec 1 (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c13) (VecMinus (Vec 1 1 0 (+ (* o4 (- 1 c14)) (* c14 o1))) (Vec c12 c13 0 0))) (&lt;&lt; (VecMul (Vec 1 (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c13) (VecMinus (Vec 1 1 0 (+ (* o4 (- 1 c14)) (* c14 o1))) (Vec c12 c13 0 0))) 2))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c23 1) (Vec (- 1 c23) c12 (* 1 (+ (* o4 (- 1 c24)) (* c24 o2))) 0)) (&lt;&lt; (VecMul (Vec (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c23 1) (Vec (- 1 c23) c12 (* 1 (+ (* o4 (- 1 c24)) (* c24 o2))) 0)) 2)) (VecAdd (VecMul (Vec 1 (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c13) (VecMinus (Vec 1 1 0 (+ (* o4 (- 1 c14)) (* c14 o1))) (Vec c12 c13 0 0))) (&lt;&lt; (VecMul (Vec 1 (+ (* o4 (- 1 c34)) (* c34 o3)) 1 c13) (VecMinus (Vec 1 1 0 (+ (* o4 (- 1 c14)) (* c14 o1))) (Vec c12 c13 0 0))) 2))) 1))</t>
         </is>
       </c>
       <c r="E127" t="n">
         <v>7012</v>
       </c>
       <c r="F127" t="n">
-        <v>7012</v>
+        <v>4979</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>28.99</v>
       </c>
       <c r="H127" t="n">
         <v>110.93</v>
       </c>
       <c r="I127" t="n">
-        <v>110.93</v>
+        <v>147.91</v>
       </c>
       <c r="J127" t="b">
         <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>8999889.07</v>
+        <v>8999852.09</v>
       </c>
       <c r="L127" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
     </row>
     <row r="128">
@@ -5797,29 +5797,29 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) (- 1 c13)) (* c13 (+ (* o2134 (- 1 c24)) (* c24 (+ (* (- 1 c14) (+ (* o4213 (- 1 c24)) (* c24 o2413))) (* c14 (+ (* o2143 (- 1 c34)) (* c34 o2134)))))))) 0)) (&lt;&lt; (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) (- 1 c13)) (* c13 (+ (* o2134 (- 1 c24)) (* c24 (+ (* (- 1 c14) (+ (* o4213 (- 1 c24)) (* c24 o2413))) (* c14 (+ (* o2143 (- 1 c34)) (* c34 o2134)))))))) 0)) 2)) (VecAdd (VecMul (Vec 1 (- 1 c13) 1 c13) (VecAdd (VecMul (Vec 1 o3124 1 (- 1 c23)) (VecMinus (Vec 0 1 (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))) (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324))))))) (VecMinus (VecMinus (VecMinus (Vec 0 c34 0 0) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)))))))))))))) (VecMul (Vec 1 c34 1 c23) (VecAdd (VecMul (Vec 1 (- 1 c14) 1 o1234) (VecMinus (Vec 0 (+ (* o4312 (- 1 c34)) (* c34 o3412)) 0 1) (Vec 0 0 0 c14))) (VecMul (Vec 1 c14 1 c14) (VecAdd (VecMul (Vec 1 o3142 1 (- 1 c24)) (Vec 0 (- 1 c24) 0 (+ (* o4123 (- 1 c14)) (* c14 o1423)))) (VecMul (Vec 1 c24 1 c24) (Vec (- 1 c12) o3124 0 (+ (* o1243 (- 1 c34)) (* c34 o1234)))))))))) (&lt;&lt; (VecMul (Vec 1 (- 1 c13) 1 c13) (VecAdd (VecMul (Vec 1 o3124 1 (- 1 c23)) (VecMinus (Vec 0 1 (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))) (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324))))))) (VecMinus (VecMinus (VecMinus (Vec 0 c34 0 0) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)))))))))))))) (VecMul (Vec 1 c34 1 c23) (VecAdd (VecMul (Vec 1 (- 1 c14) 1 o1234) (VecMinus (Vec 0 (+ (* o4312 (- 1 c34)) (* c34 o3412)) 0 1) (Vec 0 0 0 c14))) (VecMul (Vec 1 c14 1 c14) (VecAdd (VecMul (Vec 1 o3142 1 (- 1 c24)) (Vec 0 (- 1 c24) 0 (+ (* o4123 (- 1 c14)) (* c14 o1423)))) (VecMul (Vec 1 c24 1 c24) (Vec (- 1 c12) o3124 0 (+ (* o1243 (- 1 c34)) (* c34 o1234)))))))))) 2))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) (- 1 c13)) (* c13 (+ (* o2134 (- 1 c24)) (* c24 (+ (* (- 1 c14) (+ (* o4213 (- 1 c24)) (* c24 o2413))) (* c14 (+ (* o2143 (- 1 c34)) (* c34 o2134)))))))) 0)) (&lt;&lt; (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (+ (* o4231 (- 1 c24)) (* c24 o2431))) (* c34 (+ (* o2341 (- 1 c14)) (* c14 o2314)))))) (- 1 c13)) (* c13 (+ (* o2134 (- 1 c24)) (* c24 (+ (* (- 1 c14) (+ (* o4213 (- 1 c24)) (* c24 o2413))) (* c14 (+ (* o2143 (- 1 c34)) (* c34 o2134)))))))) 0)) 2)) (VecAdd (VecMul (Vec 1 (- 1 c13) 1 c13) (VecAdd (VecMul (Vec 1 o3124 1 (- 1 c23)) (VecMinus (Vec 0 1 (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))) (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324))))))) (VecMinus (VecMinus (VecMinus (Vec 0 c34 0 0) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)))))))))))))) (VecMul (Vec 1 c34 1 c23) (VecAdd (VecMul (Vec 1 (- 1 c14) 1 o1234) (VecMinus (Vec 0 (+ (* o4312 (- 1 c34)) (* c34 o3412)) 0 1) (Vec 0 0 0 c14))) (VecMul (Vec 1 c14 1 c14) (VecAdd (VecMul (Vec 1 o3142 1 (- 1 c24)) (Vec 0 (- 1 c24) 0 (+ (* o4123 (- 1 c14)) (* c14 o1423)))) (VecMul (Vec 1 c24 1 c24) (Vec (- 1 c12) o3124 0 (+ (* o1243 (- 1 c34)) (* c34 o1234)))))))))) (&lt;&lt; (VecMul (Vec 1 (- 1 c13) 1 c13) (VecAdd (VecMul (Vec 1 o3124 1 (- 1 c23)) (VecMinus (Vec 0 1 (- (- (- 0 0) (- 0 0)) (- (- 0 0) (- 0 0))) (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (+ (* o4132 (- 1 c14)) (* c14 o1432))) (* c34 (+ (* o1342 (- 1 c24)) (* c24 o1324))))))) (VecMinus (VecMinus (VecMinus (Vec 0 c34 0 0) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (VecMinus (Vec 0 0 0 0) (Vec 0 0 0 0)))))))))))))) (VecMul (Vec 1 c34 1 c23) (VecAdd (VecMul (Vec 1 (- 1 c14) 1 o1234) (VecMinus (Vec 0 (+ (* o4312 (- 1 c34)) (* c34 o3412)) 0 1) (Vec 0 0 0 c14))) (VecMul (Vec 1 c14 1 c14) (VecAdd (VecMul (Vec 1 o3142 1 (- 1 c24)) (Vec 0 (- 1 c24) 0 (+ (* o4123 (- 1 c14)) (* c14 o1423)))) (VecMul (Vec 1 c24 1 c24) (Vec (- 1 c12) o3124 0 (+ (* o1243 (- 1 c34)) (* c34 o1234)))))))))) 2))) 1))</t>
+          <t>(VecAdd (VecMul (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4231 (- 1 c24)) (* c24 o2431)))))))))) (* c34 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o2341 (- 1 c14)) (* c14 o2314))))))))))))) (- 1 c13)) (* c13 (+ (* o2134 (- 1 c24)) (* c24 (+ (* (- 1 c14) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4213 (- 1 c24)) (* c24 o2413)))))))))) (* c14 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o2143 (- 1 c34)) (* c34 o2134)))))))))))))) 0)) (&lt;&lt; (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4231 (- 1 c24)) (* c24 o2431)))))))))) (* c34 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o2341 (- 1 c14)) (* c14 o2314))))))))))))) (- 1 c13)) (* c13 (+ (* o2134 (- 1 c24)) (* c24 (+ (* (- 1 c14) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4213 (- 1 c24)) (* c24 o2413)))))))))) (* c14 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o2143 (- 1 c34)) (* c34 o2134)))))))))))))) 0)) 2)) (VecAdd (VecMul (Vec 1 (- 1 c13) 1 c13) (VecAdd (VecMul (Vec 1 o3124 1 (- 1 c23)) (Vec 0 (- 1 c34) 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4132 (- 1 c14)) (* c14 o1432))))))))) (* c34 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))))))))) (VecMul (Vec 1 c34 1 c23) (VecAdd (VecMul (Vec 1 (- 1 c14) 1 o1234) (Vec 0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4312 (- 1 c34)) (* c34 o3412)))))))))) 0 (- 1 c14))) (VecMul (Vec 1 c14 1 c14) (VecAdd (VecMul (Vec 1 o3142 1 (- 1 c24)) (Vec 0 (- 1 c24) 0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4123 (- 1 c14)) (* c14 o1423)))))))))) (VecMul (Vec 1 c24 1 c24) (Vec (- 1 c12) o3124 0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o1243 (- 1 c34)) (* c34 o1234)))))))))))))))) (&lt;&lt; (VecMul (Vec 1 (- 1 c13) 1 c13) (VecAdd (VecMul (Vec 1 o3124 1 (- 1 c23)) (Vec 0 (- 1 c34) 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4132 (- 1 c14)) (* c14 o1432))))))))) (* c34 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))))))))) (VecMul (Vec 1 c34 1 c23) (VecAdd (VecMul (Vec 1 (- 1 c14) 1 o1234) (Vec 0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4312 (- 1 c34)) (* c34 o3412)))))))))) 0 (- 1 c14))) (VecMul (Vec 1 c14 1 c14) (VecAdd (VecMul (Vec 1 o3142 1 (- 1 c24)) (Vec 0 (- 1 c24) 0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4123 (- 1 c14)) (* c14 o1423)))))))))) (VecMul (Vec 1 c24 1 c24) (Vec (- 1 c12) o3124 0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o1243 (- 1 c34)) (* c34 o1234)))))))))))))))) 2))) (&lt;&lt; (VecMul (VecAdd (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4231 (- 1 c24)) (* c24 o2431)))))))))) (* c34 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o2341 (- 1 c14)) (* c14 o2314))))))))))))) (- 1 c13)) (* c13 (+ (* o2134 (- 1 c24)) (* c24 (+ (* (- 1 c14) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4213 (- 1 c24)) (* c24 o2413)))))))))) (* c14 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o2143 (- 1 c34)) (* c34 o2134)))))))))))))) 0)) (&lt;&lt; (VecMul (Vec (+ (* o3214 (- 1 c34)) (* c34 (+ (* (+ (* o4321 (- 1 c34)) (* c34 o3421)) (- 1 c24)) (* c24 (+ (* o3241 (- 1 c14)) (* c14 o3214)))))) 1 c23 1) (Vec (- 1 c23) c12 (+ (* (+ (* o2314 (- 1 c24)) (* c24 (+ (* (- 1 c34) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4231 (- 1 c24)) (* c24 o2431)))))))))) (* c34 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o2341 (- 1 c14)) (* c14 o2314))))))))))))) (- 1 c13)) (* c13 (+ (* o2134 (- 1 c24)) (* c24 (+ (* (- 1 c14) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4213 (- 1 c24)) (* c24 o2413)))))))))) (* c14 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o2143 (- 1 c34)) (* c34 o2134)))))))))))))) 0)) 2)) (VecAdd (VecMul (Vec 1 (- 1 c13) 1 c13) (VecAdd (VecMul (Vec 1 o3124 1 (- 1 c23)) (Vec 0 (- 1 c34) 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4132 (- 1 c14)) (* c14 o1432))))))))) (* c34 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))))))))) (VecMul (Vec 1 c34 1 c23) (VecAdd (VecMul (Vec 1 (- 1 c14) 1 o1234) (Vec 0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4312 (- 1 c34)) (* c34 o3412)))))))))) 0 (- 1 c14))) (VecMul (Vec 1 c14 1 c14) (VecAdd (VecMul (Vec 1 o3142 1 (- 1 c24)) (Vec 0 (- 1 c24) 0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4123 (- 1 c14)) (* c14 o1423)))))))))) (VecMul (Vec 1 c24 1 c24) (Vec (- 1 c12) o3124 0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o1243 (- 1 c34)) (* c34 o1234)))))))))))))))) (&lt;&lt; (VecMul (Vec 1 (- 1 c13) 1 c13) (VecAdd (VecMul (Vec 1 o3124 1 (- 1 c23)) (Vec 0 (- 1 c34) 0 (+ (* o1324 (- 1 c14)) (* c14 (+ (* (- 1 c34) (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4132 (- 1 c14)) (* c14 o1432))))))))) (* c34 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o1342 (- 1 c24)) (* c24 o1324)))))))))))))) (VecMul (Vec 1 c34 1 c23) (VecAdd (VecMul (Vec 1 (- 1 c14) 1 o1234) (Vec 0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4312 (- 1 c34)) (* c34 o3412)))))))))) 0 (- 1 c14))) (VecMul (Vec 1 c14 1 c14) (VecAdd (VecMul (Vec 1 o3142 1 (- 1 c24)) (Vec 0 (- 1 c24) 0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o4123 (- 1 c14)) (* c14 o1423)))))))))) (VecMul (Vec 1 c24 1 c24) (Vec (- 1 c12) o3124 0 (* 1 (* 1 (* 1 (* 1 (* 1 (* 1 (+ (* o1243 (- 1 c34)) (* c34 o1234)))))))))))))))) 2))) 1))</t>
         </is>
       </c>
       <c r="E128" t="n">
         <v>29021</v>
       </c>
       <c r="F128" t="n">
-        <v>24608</v>
+        <v>38102</v>
       </c>
       <c r="G128" t="n">
-        <v>15.21</v>
+        <v>-31.29</v>
       </c>
       <c r="H128" t="n">
         <v>218.27</v>
       </c>
       <c r="I128" t="n">
-        <v>226.65</v>
+        <v>462.73</v>
       </c>
       <c r="J128" t="b">
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>8999773.35</v>
+        <v>8999537.27</v>
       </c>
       <c r="L128" t="n">
         <v>75</v>
@@ -5839,29 +5839,29 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>(VecMul (VecAdd (VecAdd (Vec 0 x10121 0 x10181) (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) x10125 1 1) (Vec (* x10117 x10119) (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))) 0 x10183))) (&lt;&lt; (VecAdd (Vec 0 x10121 0 x10181) (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) x10125 1 1) (Vec (* x10117 x10119) (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))) 0 x10183))) 2)) (&lt;&lt; (VecAdd (VecAdd (Vec 0 x10121 0 x10181) (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) x10125 1 1) (Vec (* x10117 x10119) (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))) 0 x10183))) (&lt;&lt; (VecAdd (Vec 0 x10121 0 x10181) (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) x10125 1 1) (Vec (* x10117 x10119) (+ (+ (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) (* (* x10146 x10147) (* (+ x10149 x10150) x10152))) (+ (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) (+ (+ x10170 x10173) (+ x10176 x10178)))) 0 x10183))) 2)) 1))</t>
+          <t>(VecMul (VecAdd (VecAdd (Vec 0 x10121 0 x10181) (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) x10125 1 1) (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (Vec 0 0 0 0) (Vec 0 (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (VecAdd (Vec 0 0 0 0) (Vec 0 0 0 (+ 0 0)))) (Vec 0 (* (* x10146 x10147) (* (+ x10149 x10150) x10152)) 0 (+ (+ 0 0) (+ 0 0)))) (VecAdd (Vec 0 (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) 0 0) (Vec (* x10117 x10119) (+ (+ x10170 x10173) (+ x10176 x10178)) 0 x10183))))) (&lt;&lt; (VecAdd (Vec 0 x10121 0 x10181) (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) x10125 1 1) (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (Vec 0 0 0 0) (Vec 0 (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (VecAdd (Vec 0 0 0 0) (Vec 0 0 0 (+ 0 0)))) (Vec 0 (* (* x10146 x10147) (* (+ x10149 x10150) x10152)) 0 (+ (+ 0 0) (+ 0 0)))) (VecAdd (Vec 0 (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) 0 0) (Vec (* x10117 x10119) (+ (+ x10170 x10173) (+ x10176 x10178)) 0 x10183))))) 2)) (&lt;&lt; (VecAdd (VecAdd (Vec 0 x10121 0 x10181) (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) x10125 1 1) (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (Vec 0 0 0 0) (Vec 0 (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (VecAdd (Vec 0 0 0 0) (Vec 0 0 0 (+ 0 0)))) (Vec 0 (* (* x10146 x10147) (* (+ x10149 x10150) x10152)) 0 (+ (+ 0 0) (+ 0 0)))) (VecAdd (Vec 0 (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) 0 0) (Vec (* x10117 x10119) (+ (+ x10170 x10173) (+ x10176 x10178)) 0 x10183))))) (&lt;&lt; (VecAdd (Vec 0 x10121 0 x10181) (VecMul (Vec (* (+ (* (* x10106 x10108) x10110) x10112) x10115) x10125 1 1) (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (VecAdd (Vec 0 0 0 0) (Vec 0 (* (* (* x10132 x10133) (+ x10135 x10136)) (+ (* x10139 x10140) x10142)) 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (Vec 0 0 0 0)) (VecAdd (Vec 0 0 0 0) (Vec 0 0 0 (+ 0 0)))) (Vec 0 (* (* x10146 x10147) (* (+ x10149 x10150) x10152)) 0 (+ (+ 0 0) (+ 0 0)))) (VecAdd (Vec 0 (+ x10154 (* (* x10159 (+ (+ x10162 x10163) x10165)) x10167)) 0 0) (Vec (* x10117 x10119) (+ (+ x10170 x10173) (+ x10176 x10178)) 0 x10183))))) 2)) 1))</t>
         </is>
       </c>
       <c r="E129" t="n">
         <v>8018</v>
       </c>
       <c r="F129" t="n">
-        <v>6827</v>
+        <v>7097</v>
       </c>
       <c r="G129" t="n">
-        <v>14.85</v>
+        <v>11.49</v>
       </c>
       <c r="H129" t="n">
         <v>182.49</v>
       </c>
       <c r="I129" t="n">
-        <v>184.88</v>
+        <v>193.27</v>
       </c>
       <c r="J129" t="b">
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>8999815.119999999</v>
+        <v>8999806.73</v>
       </c>
       <c r="L129" t="n">
         <v>75</v>
@@ -5881,32 +5881,32 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>(VecMul (VecAdd (VecMul (VecMul (VecMul (Vec x9604 x9634) (Vec x9605 x9635)) (VecMul (Vec x9607 x9637) (Vec x9608 x9638))) (VecMul (VecMul (Vec x9611 x9641) (Vec x9612 x9642)) (VecMul (Vec x9614 x9644) (Vec x9615 x9645)))) (VecMul (VecMul (VecMul (Vec x9619 x9649) (Vec x9620 x9650)) (VecMul (Vec x9622 x9652) (Vec x9623 x9653))) (VecMul (VecMul (Vec x9626 x9656) (Vec x9627 x9657)) (VecMul (Vec x9629 x9659) (Vec x9630 x9660))))) (&lt;&lt; (VecAdd (VecMul (VecMul (VecMul (Vec x9604 x9634) (Vec x9605 x9635)) (VecMul (Vec x9607 x9637) (Vec x9608 x9638))) (VecMul (VecMul (Vec x9611 x9641) (Vec x9612 x9642)) (VecMul (Vec x9614 x9644) (Vec x9615 x9645)))) (VecMul (VecMul (VecMul (Vec x9619 x9649) (Vec x9620 x9650)) (VecMul (Vec x9622 x9652) (Vec x9623 x9653))) (VecMul (VecMul (Vec x9626 x9656) (Vec x9627 x9657)) (VecMul (Vec x9629 x9659) (Vec x9630 x9660))))) 1))</t>
+          <t>(VecMul (VecAdd (VecMul (VecMul (VecMul (VecMul (Vec x9604 x9634) (Vec x9605 x9635)) (VecMul (Vec x9607 x9637) (Vec x9608 x9638))) (Vec x9611 x9641)) (VecMul (Vec x9612 x9642) (VecMul (Vec x9614 x9644) (Vec x9615 x9645)))) (VecMul (VecMul (VecMul (VecMul (Vec x9619 x9649) (Vec x9620 x9650)) (VecMul (Vec x9622 x9652) (Vec x9623 x9653))) (Vec x9626 x9656)) (VecMul (Vec x9627 x9657) (VecMul (Vec x9629 x9659) (Vec x9630 x9660))))) (&lt;&lt; (VecAdd (VecMul (VecMul (VecMul (VecMul (Vec x9604 x9634) (Vec x9605 x9635)) (VecMul (Vec x9607 x9637) (Vec x9608 x9638))) (Vec x9611 x9641)) (VecMul (Vec x9612 x9642) (VecMul (Vec x9614 x9644) (Vec x9615 x9645)))) (VecMul (VecMul (VecMul (VecMul (Vec x9619 x9649) (Vec x9620 x9650)) (VecMul (Vec x9622 x9652) (Vec x9623 x9653))) (Vec x9626 x9656)) (VecMul (Vec x9627 x9657) (VecMul (Vec x9629 x9659) (Vec x9630 x9660))))) 1))</t>
         </is>
       </c>
       <c r="E130" t="n">
         <v>7761</v>
       </c>
       <c r="F130" t="n">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="G130" t="n">
-        <v>79.84999999999999</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="H130" t="n">
         <v>141.92</v>
       </c>
       <c r="I130" t="n">
-        <v>143.12</v>
+        <v>177.7</v>
       </c>
       <c r="J130" t="b">
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>8999856.880000001</v>
+        <v>8999822.300000001</v>
       </c>
       <c r="L130" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -5973,22 +5973,22 @@
         <v>43</v>
       </c>
       <c r="C2" t="n">
-        <v>39.98</v>
+        <v>72.34</v>
       </c>
       <c r="D2" t="n">
-        <v>71.83</v>
+        <v>134.04</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>168.17</v>
+        <v>105.96</v>
       </c>
       <c r="H2" t="n">
-        <v>15.4</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="3">
@@ -5999,22 +5999,22 @@
         <v>43</v>
       </c>
       <c r="C3" t="n">
-        <v>45.73</v>
+        <v>74.52</v>
       </c>
       <c r="D3" t="n">
-        <v>67.2</v>
+        <v>124.92</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G3" t="n">
-        <v>232.8</v>
+        <v>175.08</v>
       </c>
       <c r="H3" t="n">
-        <v>17</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="4">
@@ -6025,10 +6025,10 @@
         <v>43</v>
       </c>
       <c r="C4" t="n">
-        <v>45.98</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>66.7</v>
+        <v>77.22</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -6037,10 +6037,10 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>8999933.300000001</v>
+        <v>8999922.779999999</v>
       </c>
       <c r="H4" t="n">
-        <v>15.1</v>
+        <v>21.8</v>
       </c>
     </row>
   </sheetData>
